--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -9,15 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7160"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$103</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$109</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="281">
   <si>
     <t>Grupo</t>
   </si>
@@ -820,6 +820,54 @@
   </si>
   <si>
     <t>21770-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO </t>
+  </si>
+  <si>
+    <t>Ricardo de Albuquerque</t>
+  </si>
+  <si>
+    <t>21620-610</t>
+  </si>
+  <si>
+    <t>UBATUBA</t>
+  </si>
+  <si>
+    <t>21715-310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRIGUI </t>
+  </si>
+  <si>
+    <t>BIGUAÇU</t>
+  </si>
+  <si>
+    <t>21765-440</t>
+  </si>
+  <si>
+    <t>ITACAVA</t>
+  </si>
+  <si>
+    <t>21775-510</t>
+  </si>
+  <si>
+    <t>DR. ORELY</t>
+  </si>
+  <si>
+    <t>IMPERATRIZ</t>
+  </si>
+  <si>
+    <t>21710-330</t>
+  </si>
+  <si>
+    <t>21710-320</t>
+  </si>
+  <si>
+    <t>OCAIBI</t>
+  </si>
+  <si>
+    <t>21765-570</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1154,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
@@ -1128,18 +1176,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1361,7 +1397,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1001"/>
+  <dimension ref="A1:H1008"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1447,7 +1483,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f t="shared" ref="H3:H66" si="0">A3=C3</f>
+        <f>A3=C3</f>
         <v>1</v>
       </c>
     </row>
@@ -1475,7 +1511,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A4=C4</f>
         <v>1</v>
       </c>
     </row>
@@ -1503,7 +1539,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A5=C5</f>
         <v>1</v>
       </c>
     </row>
@@ -1531,7 +1567,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A6=C6</f>
         <v>1</v>
       </c>
     </row>
@@ -1559,7 +1595,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A7=C7</f>
         <v>1</v>
       </c>
     </row>
@@ -1587,7 +1623,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A8=C8</f>
         <v>1</v>
       </c>
     </row>
@@ -1615,7 +1651,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A9=C9</f>
         <v>1</v>
       </c>
     </row>
@@ -1643,7 +1679,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A10=C10</f>
         <v>1</v>
       </c>
     </row>
@@ -1671,36 +1707,36 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A11=C11</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
+      <c r="A12" s="26">
         <v>15</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="37">
-        <v>17</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="E12" s="36" t="s">
+      <c r="B12" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="28">
+        <v>15</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="35" t="s">
-        <v>76</v>
+      <c r="F12" s="26" t="s">
+        <v>74</v>
       </c>
       <c r="G12" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B12),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E12),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F12),0)&gt;0), MAX($G$1:G11)+1, ""))</f>
         <v/>
       </c>
-      <c r="H12" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H12" s="21" t="b">
+        <f>A12=C12</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1708,55 +1744,55 @@
         <v>15</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C13" s="28">
         <v>15</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G13" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B13),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E13),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F13),0)&gt;0), MAX($G$1:G12)+1, ""))</f>
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A13=C13</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="35">
+      <c r="A14" s="26">
         <v>15</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="37">
-        <v>17</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="E14" s="36" t="s">
+      <c r="B14" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="28">
+        <v>15</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="35" t="s">
-        <v>72</v>
+      <c r="F14" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="G14" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B14),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E14),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F14),0)&gt;0), MAX($G$1:G13)+1, ""))</f>
         <v/>
       </c>
-      <c r="H14" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H14" s="21" t="b">
+        <f>A14=C14</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1764,26 +1800,26 @@
         <v>15</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>69</v>
+        <v>275</v>
       </c>
       <c r="C15" s="28">
         <v>15</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>234</v>
+        <v>7</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A15=C15</f>
         <v>1</v>
       </c>
     </row>
@@ -1792,83 +1828,83 @@
         <v>15</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C16" s="28">
         <v>15</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A16=C16</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="35">
+      <c r="A17" s="26">
         <v>15</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="37">
-        <v>17</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="E17" s="36" t="s">
+      <c r="B17" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="28">
+        <v>15</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="35" t="s">
-        <v>66</v>
+      <c r="F17" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="G17" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F17),0)&gt;0), MAX($G$1:G16)+1, ""))</f>
         <v/>
       </c>
-      <c r="H17" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H17" s="21" t="b">
+        <f>A17=C17</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="35">
+      <c r="A18" s="26">
         <v>15</v>
       </c>
-      <c r="B18" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="37">
-        <v>17</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>64</v>
+      <c r="B18" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="28">
+        <v>15</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="G18" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F18),0)&gt;0), MAX($G$1:G17)+1, ""))</f>
         <v/>
       </c>
-      <c r="H18" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H18" s="21" t="b">
+        <f>A18=C18</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1876,26 +1912,26 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>60</v>
+        <v>276</v>
       </c>
       <c r="C19" s="28">
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>61</v>
+        <v>278</v>
       </c>
       <c r="G19" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F19),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A19=C19</f>
         <v>1</v>
       </c>
     </row>
@@ -1904,26 +1940,26 @@
         <v>15</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C20" s="28">
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G20" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A20=C20</f>
         <v>1</v>
       </c>
     </row>
@@ -1932,55 +1968,55 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A21=C21</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="35">
+      <c r="A22" s="26">
         <v>15</v>
       </c>
-      <c r="B22" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="37">
-        <v>17</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="E22" s="36" t="s">
+      <c r="B22" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="28">
+        <v>15</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E22" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="35" t="s">
-        <v>55</v>
+      <c r="F22" s="26" t="s">
+        <v>47</v>
       </c>
       <c r="G22" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
         <v/>
       </c>
-      <c r="H22" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H22" s="21" t="b">
+        <f>A22=C22</f>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1988,55 +2024,55 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A23=C23</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="35">
+      <c r="A24" s="26">
         <v>15</v>
       </c>
-      <c r="B24" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="37">
-        <v>17</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="E24" s="36" t="s">
+      <c r="B24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="28">
+        <v>15</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E24" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="35" t="s">
-        <v>51</v>
+      <c r="F24" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
         <v/>
       </c>
-      <c r="H24" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H24" s="21" t="b">
+        <f>A24=C24</f>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -2044,26 +2080,26 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>248</v>
+      <c r="D25" s="26">
+        <v>2.1</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>8</v>
+        <v>261</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A25=C25</f>
         <v>1</v>
       </c>
     </row>
@@ -2072,26 +2108,26 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A26=C26</f>
         <v>1</v>
       </c>
     </row>
@@ -2100,26 +2136,26 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A27=C27</f>
         <v>1</v>
       </c>
     </row>
@@ -2128,203 +2164,203 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A28=C28</f>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="26">
-        <v>15</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="C29" s="28">
-        <v>15</v>
-      </c>
-      <c r="D29" s="26">
-        <v>2.1</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>217</v>
+      <c r="A29" s="35">
+        <v>17</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="37">
+        <v>17</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
         <v/>
       </c>
-      <c r="H29" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H29" s="41" t="b">
+        <f>A29=C29</f>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="26">
-        <v>15</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="28">
-        <v>15</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E30" s="27" t="s">
+      <c r="A30" s="35">
+        <v>17</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="37">
+        <v>17</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="26" t="s">
-        <v>41</v>
+      <c r="F30" s="35" t="s">
+        <v>72</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
         <v/>
       </c>
-      <c r="H30" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H30" s="41" t="b">
+        <f>A30=C30</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C31" s="37">
         <v>17</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
         <v/>
       </c>
       <c r="H31" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>A31=C31</f>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="26">
-        <v>15</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="28">
-        <v>15</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>37</v>
+      <c r="A32" s="35">
+        <v>17</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="37">
+        <v>17</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>64</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
         <v/>
       </c>
-      <c r="H32" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H32" s="41" t="b">
+        <f>A32=C32</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="26">
-        <v>15</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="28">
-        <v>15</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="27" t="s">
+      <c r="A33" s="38">
+        <v>17</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="40">
+        <v>17</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="26" t="s">
-        <v>35</v>
+      <c r="F33" s="38" t="s">
+        <v>117</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
         <v/>
       </c>
-      <c r="H33" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H33" s="41" t="b">
+        <f>A33=C33</f>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="35">
-        <v>15</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="37">
+      <c r="A34" s="38">
         <v>17</v>
       </c>
-      <c r="D34" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="E34" s="36" t="s">
+      <c r="B34" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="40">
+        <v>17</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="35" t="s">
-        <v>33</v>
+      <c r="F34" s="38" t="s">
+        <v>115</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
         <v/>
       </c>
       <c r="H34" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>A34=C34</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C35" s="37">
         <v>17</v>
@@ -2336,210 +2372,210 @@
         <v>8</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
         <v/>
       </c>
       <c r="H35" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>A35=C35</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="32">
-        <v>20</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" s="34">
-        <v>20</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E36" s="33" t="s">
+      <c r="A36" s="35">
+        <v>17</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="37">
+        <v>17</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="32" t="s">
-        <v>160</v>
+      <c r="F36" s="35" t="s">
+        <v>51</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
         <v/>
       </c>
-      <c r="H36" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H36" s="41" t="b">
+        <f>A36=C36</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="32">
-        <v>20</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37" s="34">
-        <v>20</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E37" s="33" t="s">
+      <c r="A37" s="38">
+        <v>17</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="40">
+        <v>17</v>
+      </c>
+      <c r="D37" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="E37" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="32" t="s">
-        <v>158</v>
+      <c r="F37" s="38" t="s">
+        <v>105</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
         <v/>
       </c>
-      <c r="H37" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H37" s="41" t="b">
+        <f>A37=C37</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="32">
-        <v>20</v>
-      </c>
-      <c r="B38" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" s="34">
-        <v>20</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E38" s="33" t="s">
+      <c r="A38" s="38">
+        <v>17</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="40">
+        <v>17</v>
+      </c>
+      <c r="D38" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="32" t="s">
-        <v>156</v>
+      <c r="F38" s="38" t="s">
+        <v>101</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
         <v/>
       </c>
-      <c r="H38" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H38" s="41" t="b">
+        <f>A38=C38</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="32">
-        <v>20</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="34">
-        <v>20</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="E39" s="33" t="s">
+      <c r="A39" s="35">
+        <v>17</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="37">
+        <v>17</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="E39" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="32" t="s">
-        <v>154</v>
+      <c r="F39" s="35" t="s">
+        <v>39</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
         <v/>
       </c>
-      <c r="H39" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H39" s="41" t="b">
+        <f>A39=C39</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="32">
-        <v>20</v>
-      </c>
-      <c r="B40" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C40" s="34">
-        <v>20</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="E40" s="33" t="s">
+      <c r="A40" s="38">
+        <v>17</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="40">
+        <v>17</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="E40" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="32" t="s">
-        <v>152</v>
+      <c r="F40" s="38" t="s">
+        <v>89</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
         <v/>
       </c>
-      <c r="H40" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H40" s="41" t="b">
+        <f>A40=C40</f>
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="32">
-        <v>20</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="C41" s="34">
-        <v>20</v>
-      </c>
-      <c r="D41" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E41" s="33" t="s">
+      <c r="A41" s="35">
+        <v>17</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="37">
+        <v>17</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="E41" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="32" t="s">
-        <v>150</v>
+      <c r="F41" s="35" t="s">
+        <v>33</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
         <v/>
       </c>
-      <c r="H41" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H41" s="41" t="b">
+        <f>A41=C41</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="32">
-        <v>20</v>
-      </c>
-      <c r="B42" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" s="34">
-        <v>20</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="E42" s="33" t="s">
+      <c r="A42" s="35">
+        <v>17</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="37">
+        <v>17</v>
+      </c>
+      <c r="D42" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="E42" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="32" t="s">
-        <v>148</v>
+      <c r="F42" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
         <v/>
       </c>
-      <c r="H42" s="21" t="b">
-        <f t="shared" si="0"/>
+      <c r="H42" s="41" t="b">
+        <f>A42=C42</f>
         <v>1</v>
       </c>
     </row>
@@ -2548,26 +2584,26 @@
         <v>20</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C43" s="34">
         <v>20</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E43" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A43=C43</f>
         <v>1</v>
       </c>
     </row>
@@ -2576,26 +2612,26 @@
         <v>20</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C44" s="34">
         <v>20</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="F44" s="32" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A44=C44</f>
         <v>1</v>
       </c>
     </row>
@@ -2604,26 +2640,26 @@
         <v>20</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C45" s="34">
         <v>20</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E45" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A45=C45</f>
         <v>1</v>
       </c>
     </row>
@@ -2632,26 +2668,26 @@
         <v>20</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C46" s="34">
         <v>20</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E46" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="32" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A46=C46</f>
         <v>1</v>
       </c>
     </row>
@@ -2660,26 +2696,26 @@
         <v>20</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C47" s="34">
         <v>20</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E47" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
@@ -2688,26 +2724,26 @@
         <v>20</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>134</v>
+        <v>271</v>
       </c>
       <c r="C48" s="34">
         <v>20</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E48" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="32" t="s">
-        <v>135</v>
+        <v>272</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
@@ -2716,26 +2752,26 @@
         <v>20</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>132</v>
+        <v>270</v>
       </c>
       <c r="C49" s="34">
         <v>20</v>
       </c>
-      <c r="D49" s="32" t="s">
-        <v>238</v>
+      <c r="D49" s="32">
+        <v>4.2</v>
       </c>
       <c r="E49" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="32" t="s">
-        <v>133</v>
+      <c r="F49" s="32">
+        <v>21765430</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A49=C49</f>
         <v>1</v>
       </c>
     </row>
@@ -2744,26 +2780,26 @@
         <v>20</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C50" s="34">
         <v>20</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E50" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A50=C50</f>
         <v>1</v>
       </c>
     </row>
@@ -2772,26 +2808,26 @@
         <v>20</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C51" s="34">
         <v>20</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E51" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
@@ -2800,26 +2836,26 @@
         <v>20</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C52" s="34">
         <v>20</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E52" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F52" s="32" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A52=C52</f>
         <v>1</v>
       </c>
     </row>
@@ -2828,26 +2864,26 @@
         <v>20</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C53" s="34">
         <v>20</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="F53" s="32" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A53=C53</f>
         <v>1</v>
       </c>
     </row>
@@ -2856,26 +2892,26 @@
         <v>20</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C54" s="34">
         <v>20</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
@@ -2884,26 +2920,26 @@
         <v>20</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C55" s="34">
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
@@ -2912,83 +2948,83 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="38">
+      <c r="A57" s="32">
         <v>20</v>
       </c>
-      <c r="B57" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="40">
-        <v>17</v>
-      </c>
-      <c r="D57" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="E57" s="39" t="s">
+      <c r="B57" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="34">
+        <v>20</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="38" t="s">
-        <v>117</v>
+      <c r="F57" s="32" t="s">
+        <v>135</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
         <v/>
       </c>
-      <c r="H57" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H57" s="21" t="b">
+        <f>A57=C57</f>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="38">
+      <c r="A58" s="32">
         <v>20</v>
       </c>
-      <c r="B58" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="40">
-        <v>17</v>
-      </c>
-      <c r="D58" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="E58" s="39" t="s">
+      <c r="B58" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="34">
+        <v>20</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="38" t="s">
-        <v>115</v>
+      <c r="F58" s="32" t="s">
+        <v>133</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
         <v/>
       </c>
-      <c r="H58" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H58" s="21" t="b">
+        <f>A58=C58</f>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -2996,26 +3032,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
@@ -3024,26 +3060,26 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>110</v>
+        <v>273</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
@@ -3052,26 +3088,26 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
@@ -3080,55 +3116,55 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="38">
+      <c r="A63" s="32">
         <v>20</v>
       </c>
-      <c r="B63" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C63" s="40">
-        <v>17</v>
-      </c>
-      <c r="D63" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="E63" s="39" t="s">
+      <c r="B63" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="34">
+        <v>20</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="E63" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="38" t="s">
-        <v>105</v>
+      <c r="F63" s="32" t="s">
+        <v>125</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
-      <c r="H63" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H63" s="21" t="b">
+        <f>A63=C63</f>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -3136,55 +3172,55 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="38">
+      <c r="A65" s="32">
         <v>20</v>
       </c>
-      <c r="B65" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C65" s="40">
-        <v>17</v>
-      </c>
-      <c r="D65" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="E65" s="39" t="s">
+      <c r="B65" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="34">
+        <v>20</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="E65" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="38" t="s">
-        <v>101</v>
+      <c r="F65" s="32" t="s">
+        <v>121</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
-      <c r="H65" s="41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H65" s="21" t="b">
+        <f>A65=C65</f>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -3192,7 +3228,7 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
@@ -3204,14 +3240,14 @@
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3220,26 +3256,26 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f t="shared" ref="H67:H102" si="1">A67=C67</f>
+        <f>A67=C67</f>
         <v>1</v>
       </c>
     </row>
@@ -3248,26 +3284,26 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A68=C68</f>
         <v>1</v>
       </c>
     </row>
@@ -3276,26 +3312,26 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>92</v>
+        <v>279</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
-      <c r="D69" s="32" t="s">
-        <v>236</v>
+      <c r="D69" s="32">
+        <v>6.2</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>93</v>
+        <v>280</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
@@ -3304,55 +3340,55 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="38">
+      <c r="A71" s="32">
         <v>20</v>
       </c>
-      <c r="B71" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C71" s="40">
-        <v>17</v>
-      </c>
-      <c r="D71" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="E71" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" s="38" t="s">
-        <v>89</v>
+      <c r="B71" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="34">
+        <v>20</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E71" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F71" s="32" t="s">
+        <v>107</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
         <v/>
       </c>
-      <c r="H71" s="41" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="H71" s="21" t="b">
+        <f>A71=C71</f>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -3360,26 +3396,26 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
@@ -3388,26 +3424,26 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3416,194 +3452,194 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="26">
-        <v>25</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C75" s="28">
-        <v>25</v>
-      </c>
-      <c r="D75" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="E75" s="27" t="s">
+      <c r="A75" s="32">
+        <v>20</v>
+      </c>
+      <c r="B75" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75" s="34">
+        <v>20</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="E75" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="26" t="s">
-        <v>194</v>
+      <c r="F75" s="32" t="s">
+        <v>95</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="26">
-        <v>25</v>
-      </c>
-      <c r="B76" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="C76" s="28">
-        <v>25</v>
-      </c>
-      <c r="D76" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="E76" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F76" s="26" t="s">
-        <v>192</v>
+      <c r="A76" s="32">
+        <v>20</v>
+      </c>
+      <c r="B76" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76" s="34">
+        <v>20</v>
+      </c>
+      <c r="D76" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E76" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>93</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A76=C76</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="26">
-        <v>25</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="C77" s="28">
-        <v>25</v>
-      </c>
-      <c r="D77" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="E77" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F77" s="26" t="s">
-        <v>190</v>
+      <c r="A77" s="32">
+        <v>20</v>
+      </c>
+      <c r="B77" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" s="34">
+        <v>20</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A77=C77</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="26">
-        <v>25</v>
-      </c>
-      <c r="B78" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="C78" s="28">
-        <v>25</v>
-      </c>
-      <c r="D78" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E78" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F78" s="26" t="s">
-        <v>188</v>
+      <c r="A78" s="32">
+        <v>20</v>
+      </c>
+      <c r="B78" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C78" s="34">
+        <v>20</v>
+      </c>
+      <c r="D78" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E78" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F78" s="32" t="s">
+        <v>87</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="26">
-        <v>25</v>
-      </c>
-      <c r="B79" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C79" s="28">
-        <v>25</v>
-      </c>
-      <c r="D79" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="E79" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F79" s="26" t="s">
-        <v>186</v>
+      <c r="A79" s="32">
+        <v>20</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="34">
+        <v>20</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="26">
-        <v>25</v>
-      </c>
-      <c r="B80" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C80" s="28">
-        <v>25</v>
-      </c>
-      <c r="D80" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E80" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F80" s="26" t="s">
-        <v>184</v>
+      <c r="A80" s="32">
+        <v>20</v>
+      </c>
+      <c r="B80" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="34">
+        <v>20</v>
+      </c>
+      <c r="D80" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="32" t="s">
+        <v>82</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
@@ -3612,26 +3648,26 @@
         <v>25</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C81" s="28">
         <v>25</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E81" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A81=C81</f>
         <v>1</v>
       </c>
     </row>
@@ -3640,26 +3676,26 @@
         <v>25</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C82" s="28">
         <v>25</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="E82" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A82=C82</f>
         <v>1</v>
       </c>
     </row>
@@ -3668,26 +3704,26 @@
         <v>25</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C83" s="28">
         <v>25</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E83" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A83=C83</f>
         <v>1</v>
       </c>
     </row>
@@ -3696,26 +3732,26 @@
         <v>25</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C84" s="28">
         <v>25</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E84" s="27" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A84=C84</f>
         <v>1</v>
       </c>
     </row>
@@ -3724,26 +3760,26 @@
         <v>25</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C85" s="28">
         <v>25</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E85" s="27" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A85=C85</f>
         <v>1</v>
       </c>
     </row>
@@ -3752,26 +3788,26 @@
         <v>25</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C86" s="28">
         <v>25</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E86" s="27" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
@@ -3780,26 +3816,26 @@
         <v>25</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C87" s="28">
         <v>25</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E87" s="27" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A87=C87</f>
         <v>1</v>
       </c>
     </row>
@@ -3808,26 +3844,26 @@
         <v>25</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C88" s="28">
         <v>25</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E88" s="27" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A88=C88</f>
         <v>1</v>
       </c>
     </row>
@@ -3836,26 +3872,26 @@
         <v>25</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C89" s="28">
         <v>25</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E89" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A89=C89</f>
         <v>1</v>
       </c>
     </row>
@@ -3864,26 +3900,26 @@
         <v>25</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C90" s="28">
         <v>25</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A90=C90</f>
         <v>1</v>
       </c>
     </row>
@@ -3892,26 +3928,26 @@
         <v>25</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>263</v>
+        <v>173</v>
       </c>
       <c r="C91" s="28">
         <v>25</v>
       </c>
-      <c r="D91" s="42" t="s">
-        <v>244</v>
+      <c r="D91" s="26" t="s">
+        <v>251</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>264</v>
+        <v>174</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A91=C91</f>
         <v>1</v>
       </c>
     </row>
@@ -3920,222 +3956,222 @@
         <v>25</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C92" s="28">
         <v>25</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E92" s="27" t="s">
         <v>86</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A92=C92</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="32">
-        <v>30</v>
-      </c>
-      <c r="B93" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="C93" s="34">
-        <v>30</v>
-      </c>
-      <c r="D93" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="E93" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F93" s="32" t="s">
-        <v>208</v>
+      <c r="A93" s="26">
+        <v>25</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" s="28">
+        <v>25</v>
+      </c>
+      <c r="D93" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F93" s="26" t="s">
+        <v>170</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A93=C93</f>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="32">
-        <v>30</v>
-      </c>
-      <c r="B94" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C94" s="34">
-        <v>30</v>
-      </c>
-      <c r="D94" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="E94" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F94" s="32" t="s">
-        <v>205</v>
+      <c r="A94" s="26">
+        <v>25</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C94" s="28">
+        <v>25</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="26" t="s">
+        <v>168</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A94=C94</f>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="32">
-        <v>30</v>
-      </c>
-      <c r="B95" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C95" s="34">
-        <v>30</v>
-      </c>
-      <c r="D95" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="E95" s="33" t="s">
+      <c r="A95" s="26">
+        <v>25</v>
+      </c>
+      <c r="B95" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C95" s="28">
+        <v>25</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="E95" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="F95" s="32" t="s">
-        <v>205</v>
+      <c r="F95" s="26" t="s">
+        <v>166</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A95=C95</f>
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="32">
-        <v>30</v>
-      </c>
-      <c r="B96" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="C96" s="34">
-        <v>30</v>
-      </c>
-      <c r="D96" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E96" s="33" t="s">
+      <c r="A96" s="26">
+        <v>25</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C96" s="28">
+        <v>25</v>
+      </c>
+      <c r="D96" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="E96" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="32" t="s">
-        <v>203</v>
+      <c r="F96" s="26" t="s">
+        <v>264</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A96=C96</f>
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="32">
-        <v>30</v>
-      </c>
-      <c r="B97" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C97" s="34">
-        <v>30</v>
-      </c>
-      <c r="D97" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="E97" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" s="32" t="s">
-        <v>202</v>
+      <c r="A97" s="26">
+        <v>25</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C97" s="28">
+        <v>25</v>
+      </c>
+      <c r="D97" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>164</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="32">
-        <v>30</v>
-      </c>
-      <c r="B98" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="C98" s="34">
-        <v>30</v>
-      </c>
-      <c r="D98" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="E98" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="F98" s="32" t="s">
-        <v>200</v>
+      <c r="A98" s="26">
+        <v>25</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C98" s="28">
+        <v>25</v>
+      </c>
+      <c r="D98" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E98" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>269</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A98=C98</f>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="32">
-        <v>30</v>
-      </c>
-      <c r="B99" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="C99" s="34">
-        <v>30</v>
-      </c>
-      <c r="D99" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E99" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>198</v>
+      <c r="A99" s="26">
+        <v>25</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C99" s="28">
+        <v>25</v>
+      </c>
+      <c r="D99" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E99" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>162</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A99=C99</f>
         <v>1</v>
       </c>
     </row>
@@ -4144,158 +4180,308 @@
         <v>30</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C100" s="34">
         <v>30</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E100" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F100" s="32" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="26">
-        <v>40</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="C101" s="28">
-        <v>40</v>
-      </c>
-      <c r="D101" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>214</v>
+      <c r="A101" s="32">
+        <v>30</v>
+      </c>
+      <c r="B101" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C101" s="34">
+        <v>30</v>
+      </c>
+      <c r="D101" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E101" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F101" s="32" t="s">
+        <v>205</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
-        <v>40</v>
-      </c>
-      <c r="B102" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C102" s="28">
-        <v>40</v>
-      </c>
-      <c r="D102" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>211</v>
+      <c r="A102" s="32">
+        <v>30</v>
+      </c>
+      <c r="B102" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" s="34">
+        <v>30</v>
+      </c>
+      <c r="D102" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="E102" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F102" s="32" t="s">
+        <v>205</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A102=C102</f>
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="30">
-        <v>25</v>
-      </c>
-      <c r="B103" s="31"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="31"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="31"/>
+      <c r="A103" s="32">
+        <v>30</v>
+      </c>
+      <c r="B103" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C103" s="34">
+        <v>30</v>
+      </c>
+      <c r="D103" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E103" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="G103" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H103" s="21" t="b">
+        <f>A103=C103</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="30"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="31"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="31"/>
+      <c r="A104" s="32">
+        <v>30</v>
+      </c>
+      <c r="B104" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C104" s="34">
+        <v>30</v>
+      </c>
+      <c r="D104" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E104" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="G104" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H104" s="21" t="b">
+        <f>A104=C104</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="30"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="30"/>
-      <c r="D105" s="30"/>
-      <c r="E105" s="31"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="31"/>
+      <c r="A105" s="32">
+        <v>30</v>
+      </c>
+      <c r="B105" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="C105" s="34">
+        <v>30</v>
+      </c>
+      <c r="D105" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F105" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="G105" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H105" s="21" t="b">
+        <f>A105=C105</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="30"/>
-      <c r="B106" s="31"/>
-      <c r="C106" s="30"/>
-      <c r="D106" s="30"/>
-      <c r="E106" s="31"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="31"/>
+      <c r="A106" s="32">
+        <v>30</v>
+      </c>
+      <c r="B106" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C106" s="34">
+        <v>30</v>
+      </c>
+      <c r="D106" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="E106" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F106" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G106" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H106" s="21" t="b">
+        <f>A106=C106</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="30"/>
-      <c r="B107" s="31"/>
-      <c r="C107" s="30"/>
-      <c r="D107" s="30"/>
-      <c r="E107" s="31"/>
-      <c r="F107" s="30"/>
-      <c r="G107" s="31"/>
+      <c r="A107" s="32">
+        <v>30</v>
+      </c>
+      <c r="B107" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C107" s="34">
+        <v>30</v>
+      </c>
+      <c r="D107" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="E107" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F107" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="G107" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H107" s="21" t="b">
+        <f>A107=C107</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="30"/>
-      <c r="B108" s="31"/>
-      <c r="C108" s="30"/>
-      <c r="D108" s="30"/>
-      <c r="E108" s="31"/>
-      <c r="F108" s="30"/>
-      <c r="G108" s="31"/>
+      <c r="A108" s="26">
+        <v>40</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" s="28">
+        <v>40</v>
+      </c>
+      <c r="D108" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="G108" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H108" s="21" t="b">
+        <f>A108=C108</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="30"/>
-      <c r="B109" s="31"/>
-      <c r="C109" s="30"/>
-      <c r="D109" s="30"/>
-      <c r="E109" s="31"/>
-      <c r="F109" s="30"/>
-      <c r="G109" s="31"/>
+      <c r="A109" s="26">
+        <v>40</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C109" s="28">
+        <v>40</v>
+      </c>
+      <c r="D109" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="G109" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H109" s="21" t="b">
+        <f>A109=C109</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="30"/>
-      <c r="B110" s="31"/>
-      <c r="C110" s="30"/>
-      <c r="D110" s="30"/>
-      <c r="E110" s="31"/>
-      <c r="F110" s="30"/>
-      <c r="G110" s="31"/>
+      <c r="A110" s="26">
+        <v>40</v>
+      </c>
+      <c r="B110" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C110" s="28">
+        <v>40</v>
+      </c>
+      <c r="D110" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E110" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="F110" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G110" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H110" s="21" t="b">
+        <f>A110=C110</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A111" s="30"/>
@@ -4352,46 +4538,67 @@
       <c r="G116" s="31"/>
     </row>
     <row r="117" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="F117" s="1"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="30"/>
+      <c r="E117" s="31"/>
+      <c r="F117" s="30"/>
+      <c r="G117" s="31"/>
     </row>
     <row r="118" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="F118" s="1"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="31"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="31"/>
     </row>
     <row r="119" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="F119" s="1"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
+      <c r="E119" s="31"/>
+      <c r="F119" s="30"/>
+      <c r="G119" s="31"/>
     </row>
     <row r="120" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="F120" s="1"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="30"/>
+      <c r="D120" s="30"/>
+      <c r="E120" s="31"/>
+      <c r="F120" s="30"/>
+      <c r="G120" s="31"/>
     </row>
     <row r="121" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="F121" s="1"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="30"/>
+      <c r="D121" s="30"/>
+      <c r="E121" s="31"/>
+      <c r="F121" s="30"/>
+      <c r="G121" s="31"/>
     </row>
     <row r="122" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="F122" s="1"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="31"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="31"/>
     </row>
     <row r="123" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="F123" s="1"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="31"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="31"/>
     </row>
     <row r="124" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
@@ -9661,12 +9868,60 @@
       <c r="D1001" s="1"/>
       <c r="F1001" s="1"/>
     </row>
+    <row r="1002" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1002" s="1"/>
+      <c r="C1002" s="1"/>
+      <c r="D1002" s="1"/>
+      <c r="F1002" s="1"/>
+    </row>
+    <row r="1003" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1003" s="1"/>
+      <c r="C1003" s="1"/>
+      <c r="D1003" s="1"/>
+      <c r="F1003" s="1"/>
+    </row>
+    <row r="1004" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1004" s="1"/>
+      <c r="C1004" s="1"/>
+      <c r="D1004" s="1"/>
+      <c r="F1004" s="1"/>
+    </row>
+    <row r="1005" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1005" s="1"/>
+      <c r="C1005" s="1"/>
+      <c r="D1005" s="1"/>
+      <c r="F1005" s="1"/>
+    </row>
+    <row r="1006" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1006" s="1"/>
+      <c r="C1006" s="1"/>
+      <c r="D1006" s="1"/>
+      <c r="F1006" s="1"/>
+    </row>
+    <row r="1007" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1007" s="1"/>
+      <c r="C1007" s="1"/>
+      <c r="D1007" s="1"/>
+      <c r="F1007" s="1"/>
+    </row>
+    <row r="1008" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1008" s="1"/>
+      <c r="C1008" s="1"/>
+      <c r="D1008" s="1"/>
+      <c r="F1008" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H103"/>
-  <sortState ref="A2:F101">
-    <sortCondition ref="A2:A101"/>
-    <sortCondition ref="B2:B101"/>
-    <sortCondition ref="D2:D101"/>
+  <autoFilter ref="A1:H110">
+    <sortState ref="A2:H110">
+      <sortCondition ref="A2:A110"/>
+      <sortCondition ref="B2:B110"/>
+      <sortCondition ref="D2:D110"/>
+    </sortState>
+  </autoFilter>
+  <sortState ref="A2:H102">
+    <sortCondition ref="A2:A102"/>
+    <sortCondition ref="B2:B102"/>
+    <sortCondition ref="D2:D102"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -468,9 +468,6 @@
     <t>21750-210</t>
   </si>
   <si>
-    <t>CARIRANHA</t>
-  </si>
-  <si>
     <t>21750-220</t>
   </si>
   <si>
@@ -868,6 +865,9 @@
   </si>
   <si>
     <t>21765-570</t>
+  </si>
+  <si>
+    <t>CARIRANHANHA</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1428,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1455,7 +1455,7 @@
         <v/>
       </c>
       <c r="H2" s="21" t="b">
-        <f>A2=C2</f>
+        <f t="shared" ref="H2:H33" si="0">A2=C2</f>
         <v>1</v>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f>A3=C3</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f>A4=C4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E5" s="33" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f>A5=C5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f>A6=C6</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f>A7=C7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f>A8=C8</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f>A9=C9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>8</v>
@@ -1679,7 +1679,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f>A10=C10</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>8</v>
@@ -1707,7 +1707,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f>A11=C11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>8</v>
@@ -1735,7 +1735,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f>A12=C12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>8</v>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f>A13=C13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>8</v>
@@ -1791,7 +1791,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f>A14=C14</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C15" s="28">
         <v>15</v>
@@ -1812,14 +1812,14 @@
         <v>8</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f>A15=C15</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>8</v>
@@ -1847,7 +1847,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f>A16=C16</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>8</v>
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f>A17=C17</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f>A18=C18</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C19" s="28">
         <v>15</v>
@@ -1924,14 +1924,14 @@
         <v>8</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G19" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F19),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f>A19=C19</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
@@ -1959,7 +1959,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f>A20=C20</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
@@ -1987,7 +1987,7 @@
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f>A21=C21</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f>A22=C22</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>8</v>
@@ -2043,7 +2043,7 @@
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f>A23=C23</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>8</v>
@@ -2071,7 +2071,7 @@
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f>A24=C24</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
@@ -2089,17 +2089,17 @@
         <v>2.1</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f>A25=C25</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
@@ -2127,7 +2127,7 @@
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f>A26=C26</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>8</v>
@@ -2155,7 +2155,7 @@
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f>A27=C27</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
@@ -2183,7 +2183,7 @@
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f>A28=C28</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
         <v>17</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E29" s="36" t="s">
         <v>8</v>
@@ -2211,7 +2211,7 @@
         <v/>
       </c>
       <c r="H29" s="41" t="b">
-        <f>A29=C29</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>8</v>
@@ -2239,7 +2239,7 @@
         <v/>
       </c>
       <c r="H30" s="41" t="b">
-        <f>A30=C30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
         <v>17</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v/>
       </c>
       <c r="H31" s="41" t="b">
-        <f>A31=C31</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>17</v>
       </c>
       <c r="D32" s="35" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E32" s="36" t="s">
         <v>63</v>
@@ -2295,7 +2295,7 @@
         <v/>
       </c>
       <c r="H32" s="41" t="b">
-        <f>A32=C32</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
         <v>17</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E33" s="39" t="s">
         <v>8</v>
@@ -2323,7 +2323,7 @@
         <v/>
       </c>
       <c r="H33" s="41" t="b">
-        <f>A33=C33</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
         <v>17</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E34" s="39" t="s">
         <v>8</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="H34" s="41" t="b">
-        <f>A34=C34</f>
+        <f t="shared" ref="H34:H65" si="1">A34=C34</f>
         <v>1</v>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
         <v>17</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E35" s="36" t="s">
         <v>8</v>
@@ -2379,7 +2379,7 @@
         <v/>
       </c>
       <c r="H35" s="41" t="b">
-        <f>A35=C35</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
         <v>17</v>
       </c>
       <c r="D36" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E36" s="36" t="s">
         <v>8</v>
@@ -2407,7 +2407,7 @@
         <v/>
       </c>
       <c r="H36" s="41" t="b">
-        <f>A36=C36</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         <v>17</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E37" s="39" t="s">
         <v>8</v>
@@ -2435,7 +2435,7 @@
         <v/>
       </c>
       <c r="H37" s="41" t="b">
-        <f>A37=C37</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E38" s="39" t="s">
         <v>8</v>
@@ -2463,7 +2463,7 @@
         <v/>
       </c>
       <c r="H38" s="41" t="b">
-        <f>A38=C38</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
         <v>17</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E39" s="36" t="s">
         <v>8</v>
@@ -2491,7 +2491,7 @@
         <v/>
       </c>
       <c r="H39" s="41" t="b">
-        <f>A39=C39</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>17</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E40" s="39" t="s">
         <v>8</v>
@@ -2519,7 +2519,7 @@
         <v/>
       </c>
       <c r="H40" s="41" t="b">
-        <f>A40=C40</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         <v>17</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E41" s="36" t="s">
         <v>8</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H41" s="41" t="b">
-        <f>A41=C41</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>8</v>
@@ -2575,7 +2575,7 @@
         <v/>
       </c>
       <c r="H42" s="41" t="b">
-        <f>A42=C42</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2584,26 +2584,26 @@
         <v>20</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C43" s="34">
         <v>20</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E43" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f>A43=C43</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2612,26 +2612,26 @@
         <v>20</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C44" s="34">
         <v>20</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E44" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f>A44=C44</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2640,26 +2640,26 @@
         <v>20</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C45" s="34">
         <v>20</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E45" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f>A45=C45</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2668,26 +2668,26 @@
         <v>20</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="34">
         <v>20</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E46" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f>A46=C46</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2696,26 +2696,26 @@
         <v>20</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C47" s="34">
         <v>20</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E47" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f>A47=C47</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2724,26 +2724,26 @@
         <v>20</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C48" s="34">
         <v>20</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E48" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="32" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f>A48=C48</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C49" s="34">
         <v>20</v>
@@ -2771,7 +2771,7 @@
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f>A49=C49</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2780,26 +2780,26 @@
         <v>20</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C50" s="34">
         <v>20</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E50" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f>A50=C50</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2808,26 +2808,26 @@
         <v>20</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>147</v>
+        <v>280</v>
       </c>
       <c r="C51" s="34">
         <v>20</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E51" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f>A51=C51</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E52" s="33" t="s">
         <v>8</v>
@@ -2855,7 +2855,7 @@
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f>A52=C52</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v>20</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E53" s="33" t="s">
         <v>143</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f>A53=C53</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>20</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>8</v>
@@ -2911,7 +2911,7 @@
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f>A54=C54</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
@@ -2939,7 +2939,7 @@
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f>A55=C55</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
@@ -2967,7 +2967,7 @@
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f>A56=C56</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v/>
       </c>
       <c r="H57" s="21" t="b">
-        <f>A57=C57</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
@@ -3023,7 +3023,7 @@
         <v/>
       </c>
       <c r="H58" s="21" t="b">
-        <f>A58=C58</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         <v>20</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>8</v>
@@ -3051,7 +3051,7 @@
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f>A59=C59</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3060,26 +3060,26 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f>A60=C60</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>20</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
@@ -3107,7 +3107,7 @@
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f>A61=C61</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f>A62=C62</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>8</v>
@@ -3163,7 +3163,7 @@
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f>A63=C63</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
@@ -3191,7 +3191,7 @@
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f>A64=C64</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>8</v>
@@ -3219,7 +3219,7 @@
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f>A65=C65</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
@@ -3247,7 +3247,7 @@
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f>A66=C66</f>
+        <f t="shared" ref="H66:H97" si="2">A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>63</v>
@@ -3275,7 +3275,7 @@
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f>A67=C67</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
@@ -3303,7 +3303,7 @@
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f>A68=C68</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
@@ -3324,14 +3324,14 @@
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f>A69=C69</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f>A70=C70</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>86</v>
@@ -3387,7 +3387,7 @@
         <v/>
       </c>
       <c r="H71" s="21" t="b">
-        <f>A71=C71</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f>A72=C72</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
@@ -3443,7 +3443,7 @@
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f>A73=C73</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
@@ -3471,7 +3471,7 @@
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f>A74=C74</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
@@ -3499,7 +3499,7 @@
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f>A75=C75</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E76" s="33" t="s">
         <v>8</v>
@@ -3527,7 +3527,7 @@
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f>A76=C76</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E77" s="33" t="s">
         <v>8</v>
@@ -3555,7 +3555,7 @@
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f>A77=C77</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E78" s="33" t="s">
         <v>86</v>
@@ -3583,7 +3583,7 @@
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f>A78=C78</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E79" s="33" t="s">
         <v>8</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E80" s="33" t="s">
         <v>8</v>
@@ -3639,7 +3639,7 @@
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f>A80=C80</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3648,26 +3648,26 @@
         <v>25</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C81" s="28">
         <v>25</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E81" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f>A81=C81</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3676,26 +3676,26 @@
         <v>25</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="28">
         <v>25</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E82" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f>A82=C82</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3704,26 +3704,26 @@
         <v>25</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C83" s="28">
         <v>25</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E83" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f>A83=C83</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3732,26 +3732,26 @@
         <v>25</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C84" s="28">
         <v>25</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E84" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f>A84=C84</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3760,26 +3760,26 @@
         <v>25</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C85" s="28">
         <v>25</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E85" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f>A85=C85</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3788,26 +3788,26 @@
         <v>25</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C86" s="28">
         <v>25</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E86" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f>A86=C86</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3816,26 +3816,26 @@
         <v>25</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C87" s="28">
         <v>25</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E87" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f>A87=C87</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3844,26 +3844,26 @@
         <v>25</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C88" s="28">
         <v>25</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E88" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f>A88=C88</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3872,26 +3872,26 @@
         <v>25</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C89" s="28">
         <v>25</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E89" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f>A89=C89</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3900,26 +3900,26 @@
         <v>25</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C90" s="28">
         <v>25</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E90" s="27" t="s">
         <v>86</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f>A90=C90</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3928,26 +3928,26 @@
         <v>25</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C91" s="28">
         <v>25</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E91" s="27" t="s">
         <v>86</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f>A91=C91</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3956,26 +3956,26 @@
         <v>25</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C92" s="28">
         <v>25</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E92" s="27" t="s">
         <v>86</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f>A92=C92</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3984,26 +3984,26 @@
         <v>25</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C93" s="28">
         <v>25</v>
       </c>
       <c r="D93" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E93" s="27" t="s">
         <v>86</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f>A93=C93</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4012,26 +4012,26 @@
         <v>25</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C94" s="28">
         <v>25</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E94" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f>A94=C94</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4040,26 +4040,26 @@
         <v>25</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C95" s="28">
         <v>25</v>
       </c>
       <c r="D95" s="26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E95" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f>A95=C95</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4068,26 +4068,26 @@
         <v>25</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C96" s="28">
         <v>25</v>
       </c>
       <c r="D96" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E96" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f>A96=C96</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4096,26 +4096,26 @@
         <v>25</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C97" s="28">
         <v>25</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E97" s="27" t="s">
         <v>143</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f>A97=C97</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
@@ -4136,14 +4136,14 @@
         <v>143</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f>A98=C98</f>
+        <f t="shared" ref="H98:H110" si="3">A98=C98</f>
         <v>1</v>
       </c>
     </row>
@@ -4152,26 +4152,26 @@
         <v>25</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C99" s="28">
         <v>25</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E99" s="27" t="s">
         <v>86</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f>A99=C99</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4180,26 +4180,26 @@
         <v>30</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C100" s="34">
         <v>30</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E100" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F100" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f>A100=C100</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4208,26 +4208,26 @@
         <v>30</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C101" s="34">
         <v>30</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E101" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F101" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f>A101=C101</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4236,26 +4236,26 @@
         <v>30</v>
       </c>
       <c r="B102" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C102" s="34">
         <v>30</v>
       </c>
       <c r="D102" s="32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E102" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F102" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f>A102=C102</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4264,26 +4264,26 @@
         <v>30</v>
       </c>
       <c r="B103" s="33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C103" s="34">
         <v>30</v>
       </c>
       <c r="D103" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E103" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F103" s="32" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f>A103=C103</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4292,26 +4292,26 @@
         <v>30</v>
       </c>
       <c r="B104" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C104" s="34">
         <v>30</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E104" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f>A104=C104</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4320,26 +4320,26 @@
         <v>30</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C105" s="34">
         <v>30</v>
       </c>
       <c r="D105" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E105" s="33" t="s">
         <v>86</v>
       </c>
       <c r="F105" s="32" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f>A105=C105</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4348,26 +4348,26 @@
         <v>30</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C106" s="34">
         <v>30</v>
       </c>
       <c r="D106" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E106" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F106" s="32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
-        <f>A106=C106</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4376,26 +4376,26 @@
         <v>30</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C107" s="34">
         <v>30</v>
       </c>
       <c r="D107" s="32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E107" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F107" s="32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f>A107=C107</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4404,26 +4404,26 @@
         <v>40</v>
       </c>
       <c r="B108" s="27" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C108" s="28">
         <v>40</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E108" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F108" s="26" t="s">
         <v>213</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>214</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f>A108=C108</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4432,26 +4432,26 @@
         <v>40</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C109" s="28">
         <v>40</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E109" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F109" s="26" t="s">
         <v>210</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>211</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f>A109=C109</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
         <v>40</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C110" s="28">
         <v>40</v>
@@ -4469,17 +4469,17 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E110" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="F110" s="26" t="s">
         <v>266</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>267</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f>A110=C110</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -9958,7 +9958,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$110</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$118</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$117</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="288">
   <si>
     <t>Grupo</t>
   </si>
@@ -201,9 +201,6 @@
     <t>21740-150</t>
   </si>
   <si>
-    <t>GENERAL AZEVEDO</t>
-  </si>
-  <si>
     <t>21740-160</t>
   </si>
   <si>
@@ -303,12 +300,6 @@
     <t>21750-030</t>
   </si>
   <si>
-    <t>SILVA NETO APÓS VILA NOVA</t>
-  </si>
-  <si>
-    <t>21750-041</t>
-  </si>
-  <si>
     <t>SILVA NETO</t>
   </si>
   <si>
@@ -351,12 +342,6 @@
     <t>21720-010</t>
   </si>
   <si>
-    <t>OCAMBI</t>
-  </si>
-  <si>
-    <t>21750-100</t>
-  </si>
-  <si>
     <t>NOGUEIRA PARTE</t>
   </si>
   <si>
@@ -417,12 +402,6 @@
     <t>21750-170</t>
   </si>
   <si>
-    <t>GOVERNO APÓS VILA NOVA</t>
-  </si>
-  <si>
-    <t>21755-011</t>
-  </si>
-  <si>
     <t>GOVERNO</t>
   </si>
   <si>
@@ -868,6 +847,48 @@
   </si>
   <si>
     <t>CARIRANHANHA</t>
+  </si>
+  <si>
+    <t>CORREA TEIXEIRA</t>
+  </si>
+  <si>
+    <t>Ligth</t>
+  </si>
+  <si>
+    <t>GENERAL AZEREDO</t>
+  </si>
+  <si>
+    <t>ESPARDARTE</t>
+  </si>
+  <si>
+    <t>Cohab</t>
+  </si>
+  <si>
+    <t>PAULA NEI</t>
+  </si>
+  <si>
+    <t>GAZELA</t>
+  </si>
+  <si>
+    <t>BASALTO</t>
+  </si>
+  <si>
+    <t>CURIO</t>
+  </si>
+  <si>
+    <t>CIRANDA</t>
+  </si>
+  <si>
+    <t>CITARA</t>
+  </si>
+  <si>
+    <t>IMPERADOR</t>
+  </si>
+  <si>
+    <t>NOGUEIRA PARTE ALTA</t>
+  </si>
+  <si>
+    <t>DONA OLIMPIA</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1146,7 +1167,6 @@
     <xf numFmtId="2" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1397,7 +1417,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1008"/>
+  <dimension ref="A1:H1016"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1428,7 +1448,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1436,26 +1456,26 @@
         <v>13</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="C2" s="34">
         <v>13</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G2" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B2),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E2),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F2),0)&gt;0), MAX($G$1:G1)+1, ""))</f>
         <v/>
       </c>
       <c r="H2" s="21" t="b">
-        <f t="shared" ref="H2:H33" si="0">A2=C2</f>
+        <f>A2=C2</f>
         <v>1</v>
       </c>
     </row>
@@ -1464,26 +1484,26 @@
         <v>13</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="34">
         <v>13</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B3),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E3),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F3),0)&gt;0), MAX($G$1:G2)+1, ""))</f>
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A3=C3</f>
         <v>1</v>
       </c>
     </row>
@@ -1492,7 +1512,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="C4" s="34">
         <v>13</v>
@@ -1501,17 +1521,17 @@
         <v>22</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B4),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E4),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F4),0)&gt;0), MAX($G$1:G3)+1, ""))</f>
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A4=C4</f>
         <v>1</v>
       </c>
     </row>
@@ -1520,26 +1540,26 @@
         <v>13</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="C5" s="34">
         <v>13</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G5" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B5),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E5),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F5),0)&gt;0), MAX($G$1:G4)+1, ""))</f>
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A5=C5</f>
         <v>1</v>
       </c>
     </row>
@@ -1548,26 +1568,26 @@
         <v>13</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" s="34">
         <v>13</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G6" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B6),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E6),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F6),0)&gt;0), MAX($G$1:G5)+1, ""))</f>
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A6=C6</f>
         <v>1</v>
       </c>
     </row>
@@ -1576,26 +1596,26 @@
         <v>13</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>13</v>
+        <v>282</v>
       </c>
       <c r="C7" s="34">
         <v>13</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G7" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F7),0)&gt;0), MAX($G$1:G6)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F7),0)&gt;0), MAX($G$1:G5)+1, ""))</f>
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A7=C7</f>
         <v>1</v>
       </c>
     </row>
@@ -1604,26 +1624,26 @@
         <v>13</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>10</v>
+        <v>287</v>
       </c>
       <c r="C8" s="34">
         <v>13</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G8" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F8),0)&gt;0), MAX($G$1:G7)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F8),0)&gt;0), MAX($G$1:G6)+1, ""))</f>
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A8=C8</f>
         <v>1</v>
       </c>
     </row>
@@ -1632,250 +1652,250 @@
         <v>13</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C9" s="34">
         <v>13</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G9" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B9),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E9),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F9),0)&gt;0), MAX($G$1:G8)+1, ""))</f>
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A9=C9</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
-        <v>15</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="28">
-        <v>15</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>80</v>
+      <c r="A10" s="32">
+        <v>13</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="34">
+        <v>13</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="G10" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B10),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E10),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F10),0)&gt;0), MAX($G$1:G9)+1, ""))</f>
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A10=C10</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
-        <v>15</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="28">
-        <v>15</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="E11" s="27" t="s">
+      <c r="A11" s="32">
+        <v>13</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="34">
+        <v>13</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>78</v>
+      <c r="F11" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="G11" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F11),0)&gt;0), MAX($G$1:G10)+1, ""))</f>
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A11=C11</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
-        <v>15</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="28">
-        <v>15</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>74</v>
+      <c r="A12" s="32">
+        <v>13</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" s="34">
+        <v>13</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="G12" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B12),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E12),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F12),0)&gt;0), MAX($G$1:G11)+1, ""))</f>
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A12=C12</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
-        <v>15</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="28">
-        <v>15</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="E13" s="27" t="s">
+      <c r="A13" s="32">
+        <v>13</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="34">
+        <v>13</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>70</v>
+      <c r="F13" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="G13" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B13),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E13),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F13),0)&gt;0), MAX($G$1:G12)+1, ""))</f>
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A13=C13</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
-        <v>15</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="28">
-        <v>15</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>68</v>
+      <c r="A14" s="32">
+        <v>13</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="34">
+        <v>13</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="G14" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B14),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E14),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F14),0)&gt;0), MAX($G$1:G13)+1, ""))</f>
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A14=C14</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="32">
+        <v>13</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="34">
+        <v>13</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="32" t="s">
         <v>15</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="C15" s="28">
-        <v>15</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>276</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A15=C15</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
-        <v>15</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="28">
-        <v>15</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" s="27" t="s">
+      <c r="A16" s="32">
+        <v>13</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="34">
+        <v>13</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="26" t="s">
-        <v>61</v>
+      <c r="F16" s="32" t="s">
+        <v>12</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A16=C16</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
-        <v>15</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="28">
-        <v>15</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E17" s="27" t="s">
+      <c r="A17" s="32">
+        <v>13</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="34">
+        <v>13</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="26" t="s">
-        <v>59</v>
+      <c r="F17" s="32" t="s">
+        <v>9</v>
       </c>
       <c r="G17" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F17),0)&gt;0), MAX($G$1:G16)+1, ""))</f>
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A17=C17</f>
         <v>1</v>
       </c>
     </row>
@@ -1884,26 +1904,26 @@
         <v>15</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C18" s="28">
         <v>15</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G18" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F18),0)&gt;0), MAX($G$1:G17)+1, ""))</f>
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A18=C18</f>
         <v>1</v>
       </c>
     </row>
@@ -1912,26 +1932,26 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="C19" s="28">
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>22</v>
+        <v>216</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="G19" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F19),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A19=C19</f>
         <v>1</v>
       </c>
     </row>
@@ -1940,26 +1960,26 @@
         <v>15</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C20" s="28">
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G20" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A20=C20</f>
         <v>1</v>
       </c>
     </row>
@@ -1968,26 +1988,26 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A21=C21</f>
         <v>1</v>
       </c>
     </row>
@@ -1996,26 +2016,26 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G22" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A22=C22</f>
         <v>1</v>
       </c>
     </row>
@@ -2024,26 +2044,26 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>8</v>
+        <v>275</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A23=C23</f>
         <v>1</v>
       </c>
     </row>
@@ -2052,26 +2072,26 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>42</v>
+        <v>267</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>43</v>
+        <v>269</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A24=C24</f>
         <v>1</v>
       </c>
     </row>
@@ -2080,26 +2100,26 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>259</v>
+        <v>59</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
-      <c r="D25" s="26">
-        <v>2.1</v>
+      <c r="D25" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A25=C25</f>
         <v>1</v>
       </c>
     </row>
@@ -2108,26 +2128,26 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A26=C26</f>
         <v>1</v>
       </c>
     </row>
@@ -2136,26 +2156,26 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A27=C27</f>
         <v>1</v>
       </c>
     </row>
@@ -2164,306 +2184,306 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A28=C28</f>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="35">
-        <v>17</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="37">
-        <v>17</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="36" t="s">
+      <c r="A29" s="26">
+        <v>15</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="28">
+        <v>15</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="35" t="s">
-        <v>76</v>
+      <c r="F29" s="26" t="s">
+        <v>270</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
         <v/>
       </c>
-      <c r="H29" s="41" t="b">
-        <f t="shared" si="0"/>
+      <c r="H29" s="21" t="b">
+        <f>A29=C29</f>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="35">
-        <v>17</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="37">
-        <v>17</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="E30" s="36" t="s">
+      <c r="A30" s="26">
+        <v>15</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="28">
+        <v>15</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="35" t="s">
-        <v>72</v>
+      <c r="F30" s="26" t="s">
+        <v>53</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
         <v/>
       </c>
-      <c r="H30" s="41" t="b">
-        <f t="shared" si="0"/>
+      <c r="H30" s="21" t="b">
+        <f>A30=C30</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="35">
-        <v>17</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="37">
-        <v>17</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="E31" s="36" t="s">
+      <c r="A31" s="26">
+        <v>15</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="28">
+        <v>15</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="35" t="s">
-        <v>66</v>
+      <c r="F31" s="26" t="s">
+        <v>49</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
         <v/>
       </c>
-      <c r="H31" s="41" t="b">
-        <f t="shared" si="0"/>
+      <c r="H31" s="21" t="b">
+        <f>A31=C31</f>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="35">
-        <v>17</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="37">
-        <v>17</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>64</v>
+      <c r="A32" s="26">
+        <v>15</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="28">
+        <v>15</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>47</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
         <v/>
       </c>
-      <c r="H32" s="41" t="b">
-        <f t="shared" si="0"/>
+      <c r="H32" s="21" t="b">
+        <f>A32=C32</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="38">
-        <v>17</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="40">
-        <v>17</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="E33" s="39" t="s">
+      <c r="A33" s="26">
+        <v>15</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="28">
+        <v>15</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="38" t="s">
-        <v>117</v>
+      <c r="F33" s="26" t="s">
+        <v>45</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
         <v/>
       </c>
-      <c r="H33" s="41" t="b">
-        <f t="shared" si="0"/>
+      <c r="H33" s="21" t="b">
+        <f>A33=C33</f>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="38">
-        <v>17</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="40">
-        <v>17</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="E34" s="39" t="s">
+      <c r="A34" s="26">
+        <v>15</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="28">
+        <v>15</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="38" t="s">
-        <v>115</v>
+      <c r="F34" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
         <v/>
       </c>
-      <c r="H34" s="41" t="b">
-        <f t="shared" ref="H34:H65" si="1">A34=C34</f>
+      <c r="H34" s="21" t="b">
+        <f>A34=C34</f>
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="35">
-        <v>17</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="37">
-        <v>17</v>
-      </c>
-      <c r="D35" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="35" t="s">
-        <v>55</v>
+      <c r="A35" s="26">
+        <v>15</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C35" s="28">
+        <v>15</v>
+      </c>
+      <c r="D35" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
         <v/>
       </c>
-      <c r="H35" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H35" s="21" t="b">
+        <f>A35=C35</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="35">
-        <v>17</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="37">
-        <v>17</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="E36" s="36" t="s">
+      <c r="A36" s="26">
+        <v>15</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="28">
+        <v>15</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="35" t="s">
-        <v>51</v>
+      <c r="F36" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
         <v/>
       </c>
-      <c r="H36" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H36" s="21" t="b">
+        <f>A36=C36</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="38">
-        <v>17</v>
-      </c>
-      <c r="B37" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="40">
-        <v>17</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="E37" s="39" t="s">
+      <c r="A37" s="26">
+        <v>15</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="28">
+        <v>15</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="38" t="s">
-        <v>105</v>
+      <c r="F37" s="26" t="s">
+        <v>37</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
         <v/>
       </c>
-      <c r="H37" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H37" s="21" t="b">
+        <f>A37=C37</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="38">
-        <v>17</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" s="40">
-        <v>17</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="E38" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>101</v>
+      <c r="A38" s="26">
+        <v>15</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="28">
+        <v>15</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
         <v/>
       </c>
-      <c r="H38" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H38" s="21" t="b">
+        <f>A38=C38</f>
         <v>1</v>
       </c>
     </row>
@@ -2472,54 +2492,54 @@
         <v>17</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C39" s="37">
         <v>17</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E39" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
         <v/>
       </c>
-      <c r="H39" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H39" s="21" t="b">
+        <f>A39=C39</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="38">
+      <c r="A40" s="35">
         <v>17</v>
       </c>
-      <c r="B40" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="40">
+      <c r="B40" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="37">
         <v>17</v>
       </c>
-      <c r="D40" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="E40" s="39" t="s">
+      <c r="D40" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="38" t="s">
-        <v>89</v>
+      <c r="F40" s="35" t="s">
+        <v>71</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
         <v/>
       </c>
-      <c r="H40" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H40" s="21" t="b">
+        <f>A40=C40</f>
         <v>1</v>
       </c>
     </row>
@@ -2528,7 +2548,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C41" s="37">
         <v>17</v>
@@ -2540,14 +2560,14 @@
         <v>8</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
         <v/>
       </c>
-      <c r="H41" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H41" s="21" t="b">
+        <f>A41=C41</f>
         <v>1</v>
       </c>
     </row>
@@ -2556,306 +2576,306 @@
         <v>17</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C42" s="37">
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
         <v/>
       </c>
-      <c r="H42" s="41" t="b">
-        <f t="shared" si="1"/>
+      <c r="H42" s="21" t="b">
+        <f>A42=C42</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
-        <v>20</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="C43" s="34">
-        <v>20</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E43" s="33" t="s">
+      <c r="A43" s="38">
+        <v>17</v>
+      </c>
+      <c r="B43" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="40">
+        <v>17</v>
+      </c>
+      <c r="D43" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="E43" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="32" t="s">
-        <v>159</v>
+      <c r="F43" s="38" t="s">
+        <v>112</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A43=C43</f>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="32">
-        <v>20</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="C44" s="34">
-        <v>20</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="E44" s="33" t="s">
+      <c r="A44" s="38">
+        <v>17</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="40">
+        <v>17</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="32" t="s">
-        <v>157</v>
+      <c r="F44" s="38" t="s">
+        <v>110</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A44=C44</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="32">
-        <v>20</v>
-      </c>
-      <c r="B45" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" s="34">
-        <v>20</v>
-      </c>
-      <c r="D45" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E45" s="33" t="s">
+      <c r="A45" s="35">
+        <v>17</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="37">
+        <v>17</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E45" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="32" t="s">
-        <v>155</v>
+      <c r="F45" s="35" t="s">
+        <v>55</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A45=C45</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="32">
-        <v>20</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C46" s="34">
-        <v>20</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="E46" s="33" t="s">
+      <c r="A46" s="35">
+        <v>17</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="37">
+        <v>17</v>
+      </c>
+      <c r="D46" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E46" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="32" t="s">
-        <v>153</v>
+      <c r="F46" s="35" t="s">
+        <v>51</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A46=C46</f>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="32">
-        <v>20</v>
-      </c>
-      <c r="B47" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="34">
-        <v>20</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="E47" s="33" t="s">
+      <c r="A47" s="38">
+        <v>17</v>
+      </c>
+      <c r="B47" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="40">
+        <v>17</v>
+      </c>
+      <c r="D47" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="32" t="s">
-        <v>151</v>
+      <c r="F47" s="38" t="s">
+        <v>102</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="32">
-        <v>20</v>
-      </c>
-      <c r="B48" s="33" t="s">
-        <v>270</v>
-      </c>
-      <c r="C48" s="34">
-        <v>20</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="E48" s="33" t="s">
+      <c r="A48" s="38">
+        <v>17</v>
+      </c>
+      <c r="B48" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="40">
+        <v>17</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="32" t="s">
-        <v>271</v>
+      <c r="F48" s="38" t="s">
+        <v>98</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="32">
-        <v>20</v>
-      </c>
-      <c r="B49" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="C49" s="34">
-        <v>20</v>
-      </c>
-      <c r="D49" s="32">
-        <v>4.2</v>
-      </c>
-      <c r="E49" s="33" t="s">
+      <c r="A49" s="35">
+        <v>17</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="37">
+        <v>17</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="E49" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="32">
-        <v>21765430</v>
+      <c r="F49" s="35" t="s">
+        <v>39</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A49=C49</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="32">
-        <v>20</v>
-      </c>
-      <c r="B50" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" s="34">
-        <v>20</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E50" s="33" t="s">
+      <c r="A50" s="38">
+        <v>17</v>
+      </c>
+      <c r="B50" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="40">
+        <v>17</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="32" t="s">
-        <v>149</v>
+      <c r="F50" s="38" t="s">
+        <v>88</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A50=C50</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="32">
-        <v>20</v>
-      </c>
-      <c r="B51" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="C51" s="34">
-        <v>20</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E51" s="33" t="s">
+      <c r="A51" s="35">
+        <v>17</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="37">
+        <v>17</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E51" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="32" t="s">
-        <v>147</v>
+      <c r="F51" s="35" t="s">
+        <v>33</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="32">
-        <v>20</v>
-      </c>
-      <c r="B52" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" s="34">
-        <v>20</v>
-      </c>
-      <c r="D52" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="E52" s="33" t="s">
+      <c r="A52" s="35">
+        <v>17</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="37">
+        <v>17</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E52" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="32" t="s">
-        <v>146</v>
+      <c r="F52" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A52=C52</f>
         <v>1</v>
       </c>
     </row>
@@ -2864,26 +2884,26 @@
         <v>20</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C53" s="34">
         <v>20</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="F53" s="32" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A53=C53</f>
         <v>1</v>
       </c>
     </row>
@@ -2892,26 +2912,26 @@
         <v>20</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C54" s="34">
         <v>20</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
@@ -2920,26 +2940,26 @@
         <v>20</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C55" s="34">
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
@@ -2948,26 +2968,26 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
@@ -2976,26 +2996,26 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
         <v/>
       </c>
       <c r="H57" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A57=C57</f>
         <v>1</v>
       </c>
     </row>
@@ -3004,26 +3024,26 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>133</v>
+        <v>264</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
         <v/>
       </c>
       <c r="H58" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A58=C58</f>
         <v>1</v>
       </c>
     </row>
@@ -3032,26 +3052,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
-      <c r="D59" s="32" t="s">
-        <v>238</v>
+      <c r="D59" s="32">
+        <v>4.2</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="32" t="s">
-        <v>131</v>
+      <c r="F59" s="32">
+        <v>21765430</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
@@ -3060,26 +3080,26 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>273</v>
+        <v>142</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
@@ -3088,26 +3108,26 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
@@ -3116,26 +3136,26 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
@@ -3144,26 +3164,26 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
@@ -3172,26 +3192,26 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
@@ -3200,26 +3220,26 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A65=C65</f>
         <v>1</v>
       </c>
     </row>
@@ -3228,26 +3248,26 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f t="shared" ref="H66:H97" si="2">A66=C66</f>
+        <f>A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3256,26 +3276,26 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A67=C67</f>
         <v>1</v>
       </c>
     </row>
@@ -3284,26 +3304,26 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A68=C68</f>
         <v>1</v>
       </c>
     </row>
@@ -3312,26 +3332,26 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
-      <c r="D69" s="32">
-        <v>6.2</v>
+      <c r="D69" s="32" t="s">
+        <v>232</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
@@ -3340,26 +3360,26 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
@@ -3368,26 +3388,26 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
         <v/>
       </c>
       <c r="H71" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A71=C71</f>
         <v>1</v>
       </c>
     </row>
@@ -3396,26 +3416,26 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
@@ -3424,26 +3444,26 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3452,26 +3472,26 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
@@ -3480,26 +3500,26 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
@@ -3508,26 +3528,26 @@
         <v>20</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C76" s="34">
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F76" s="32" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A76=C76</f>
         <v>1</v>
       </c>
     </row>
@@ -3536,26 +3556,26 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E77" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A77=C77</f>
         <v>1</v>
       </c>
     </row>
@@ -3564,26 +3584,26 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
-      <c r="D78" s="32" t="s">
-        <v>232</v>
+      <c r="D78" s="32">
+        <v>6.2</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>87</v>
+        <v>272</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
@@ -3592,26 +3612,26 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3620,222 +3640,222 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E80" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="26">
-        <v>25</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="C81" s="28">
-        <v>25</v>
-      </c>
-      <c r="D81" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E81" s="27" t="s">
+      <c r="A81" s="32">
+        <v>20</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" s="34">
+        <v>20</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E81" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F81" s="26" t="s">
-        <v>193</v>
+      <c r="F81" s="32" t="s">
+        <v>96</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A81=C81</f>
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="26">
-        <v>25</v>
-      </c>
-      <c r="B82" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C82" s="28">
-        <v>25</v>
-      </c>
-      <c r="D82" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="E82" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F82" s="26" t="s">
-        <v>191</v>
+      <c r="A82" s="32">
+        <v>20</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82" s="34">
+        <v>20</v>
+      </c>
+      <c r="D82" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E82" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="32" t="s">
+        <v>94</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A82=C82</f>
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="26">
-        <v>25</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="C83" s="28">
-        <v>25</v>
-      </c>
-      <c r="D83" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E83" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F83" s="26" t="s">
-        <v>189</v>
+      <c r="A83" s="32">
+        <v>20</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="34">
+        <v>20</v>
+      </c>
+      <c r="D83" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="32" t="s">
+        <v>92</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A83=C83</f>
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="26">
-        <v>25</v>
-      </c>
-      <c r="B84" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="C84" s="28">
-        <v>25</v>
-      </c>
-      <c r="D84" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="E84" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F84" s="26" t="s">
-        <v>187</v>
+      <c r="A84" s="32">
+        <v>20</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="34">
+        <v>20</v>
+      </c>
+      <c r="D84" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="32" t="s">
+        <v>90</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A84=C84</f>
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="26">
-        <v>25</v>
-      </c>
-      <c r="B85" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="C85" s="28">
-        <v>25</v>
-      </c>
-      <c r="D85" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E85" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F85" s="26" t="s">
-        <v>185</v>
+      <c r="A85" s="32">
+        <v>20</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" s="34">
+        <v>20</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F85" s="32" t="s">
+        <v>86</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A85=C85</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="26">
-        <v>25</v>
-      </c>
-      <c r="B86" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C86" s="28">
-        <v>25</v>
-      </c>
-      <c r="D86" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E86" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F86" s="26" t="s">
-        <v>183</v>
+      <c r="A86" s="32">
+        <v>20</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C86" s="34">
+        <v>20</v>
+      </c>
+      <c r="D86" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="32" t="s">
+        <v>83</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="26">
-        <v>25</v>
-      </c>
-      <c r="B87" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C87" s="28">
-        <v>25</v>
-      </c>
-      <c r="D87" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E87" s="27" t="s">
+      <c r="A87" s="32">
+        <v>20</v>
+      </c>
+      <c r="B87" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" s="34">
+        <v>20</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E87" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F87" s="26" t="s">
-        <v>181</v>
+      <c r="F87" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A87=C87</f>
         <v>1</v>
       </c>
     </row>
@@ -3844,26 +3864,26 @@
         <v>25</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C88" s="28">
         <v>25</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E88" s="27" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A88=C88</f>
         <v>1</v>
       </c>
     </row>
@@ -3872,26 +3892,26 @@
         <v>25</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C89" s="28">
         <v>25</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E89" s="27" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A89=C89</f>
         <v>1</v>
       </c>
     </row>
@@ -3900,26 +3920,26 @@
         <v>25</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C90" s="28">
         <v>25</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A90=C90</f>
         <v>1</v>
       </c>
     </row>
@@ -3928,26 +3948,26 @@
         <v>25</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C91" s="28">
         <v>25</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A91=C91</f>
         <v>1</v>
       </c>
     </row>
@@ -3956,26 +3976,26 @@
         <v>25</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C92" s="28">
         <v>25</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A92=C92</f>
         <v>1</v>
       </c>
     </row>
@@ -3984,7 +4004,7 @@
         <v>25</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C93" s="28">
         <v>25</v>
@@ -3993,17 +4013,17 @@
         <v>241</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A93=C93</f>
         <v>1</v>
       </c>
     </row>
@@ -4012,54 +4032,54 @@
         <v>25</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C94" s="28">
         <v>25</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="E94" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A94=C94</f>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
+      <c r="A95" s="32">
         <v>25</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C95" s="28">
+      <c r="B95" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="34">
         <v>25</v>
       </c>
-      <c r="D95" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>165</v>
+      <c r="D95" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="E95" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="32" t="s">
+        <v>106</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A95=C95</f>
         <v>1</v>
       </c>
     </row>
@@ -4068,26 +4088,26 @@
         <v>25</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>262</v>
+        <v>171</v>
       </c>
       <c r="C96" s="28">
         <v>25</v>
       </c>
-      <c r="D96" s="42" t="s">
-        <v>243</v>
+      <c r="D96" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A96=C96</f>
         <v>1</v>
       </c>
     </row>
@@ -4096,26 +4116,26 @@
         <v>25</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C97" s="28">
         <v>25</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
@@ -4124,26 +4144,26 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>267</v>
+        <v>167</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
-      <c r="D98" s="26">
-        <v>2.5</v>
+      <c r="D98" s="26" t="s">
+        <v>239</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f t="shared" ref="H98:H110" si="3">A98=C98</f>
+        <f>A98=C98</f>
         <v>1</v>
       </c>
     </row>
@@ -4152,410 +4172,562 @@
         <v>25</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C99" s="28">
         <v>25</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E99" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A99=C99</f>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="32">
-        <v>30</v>
-      </c>
-      <c r="B100" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C100" s="34">
-        <v>30</v>
-      </c>
-      <c r="D100" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="E100" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F100" s="32" t="s">
-        <v>207</v>
+      <c r="A100" s="26">
+        <v>25</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C100" s="28">
+        <v>25</v>
+      </c>
+      <c r="D100" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>164</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="32">
-        <v>30</v>
-      </c>
-      <c r="B101" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="C101" s="34">
-        <v>30</v>
-      </c>
-      <c r="D101" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="E101" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F101" s="32" t="s">
-        <v>204</v>
+      <c r="A101" s="26">
+        <v>25</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C101" s="28">
+        <v>25</v>
+      </c>
+      <c r="D101" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>162</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="32">
-        <v>30</v>
-      </c>
-      <c r="B102" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="C102" s="34">
-        <v>30</v>
-      </c>
-      <c r="D102" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E102" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F102" s="32" t="s">
-        <v>204</v>
+      <c r="A102" s="26">
+        <v>25</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C102" s="28">
+        <v>25</v>
+      </c>
+      <c r="D102" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E102" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>160</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A102=C102</f>
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="32">
-        <v>30</v>
-      </c>
-      <c r="B103" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="C103" s="34">
-        <v>30</v>
-      </c>
-      <c r="D103" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="E103" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" s="32" t="s">
-        <v>202</v>
+      <c r="A103" s="26">
+        <v>25</v>
+      </c>
+      <c r="B103" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C103" s="28">
+        <v>25</v>
+      </c>
+      <c r="D103" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E103" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F103" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A103=C103</f>
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="32">
-        <v>30</v>
-      </c>
-      <c r="B104" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="C104" s="34">
-        <v>30</v>
-      </c>
-      <c r="D104" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="E104" s="33" t="s">
+      <c r="A104" s="26">
+        <v>25</v>
+      </c>
+      <c r="B104" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C104" s="28">
+        <v>25</v>
+      </c>
+      <c r="D104" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="E104" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F104" s="32" t="s">
-        <v>201</v>
+      <c r="F104" s="26" t="s">
+        <v>256</v>
       </c>
       <c r="G104" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A104=C104</f>
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="32">
-        <v>30</v>
-      </c>
-      <c r="B105" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="C105" s="34">
-        <v>30</v>
-      </c>
-      <c r="D105" s="32" t="s">
+      <c r="A105" s="26">
+        <v>25</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C105" s="28">
+        <v>25</v>
+      </c>
+      <c r="D105" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="E105" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="F105" s="32" t="s">
-        <v>199</v>
+      <c r="E105" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>156</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A105=C105</f>
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="32">
-        <v>30</v>
-      </c>
-      <c r="B106" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C106" s="34">
-        <v>30</v>
-      </c>
-      <c r="D106" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="E106" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F106" s="32" t="s">
-        <v>197</v>
+      <c r="A106" s="26">
+        <v>25</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C106" s="28">
+        <v>25</v>
+      </c>
+      <c r="D106" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E106" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F106" s="26" t="s">
+        <v>261</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A106=C106</f>
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="32">
-        <v>30</v>
-      </c>
-      <c r="B107" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C107" s="34">
-        <v>30</v>
-      </c>
-      <c r="D107" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="E107" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F107" s="32" t="s">
-        <v>195</v>
+      <c r="A107" s="26">
+        <v>25</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C107" s="28">
+        <v>25</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A107=C107</f>
         <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="26">
-        <v>40</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="C108" s="28">
-        <v>40</v>
-      </c>
-      <c r="D108" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="E108" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>213</v>
+      <c r="A108" s="32">
+        <v>30</v>
+      </c>
+      <c r="B108" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" s="34">
+        <v>30</v>
+      </c>
+      <c r="D108" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="E108" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="F108" s="32" t="s">
+        <v>200</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A108=C108</f>
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="26">
-        <v>40</v>
-      </c>
-      <c r="B109" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="C109" s="28">
-        <v>40</v>
-      </c>
-      <c r="D109" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>210</v>
+      <c r="A109" s="32">
+        <v>30</v>
+      </c>
+      <c r="B109" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C109" s="34">
+        <v>30</v>
+      </c>
+      <c r="D109" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E109" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="F109" s="32" t="s">
+        <v>197</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A109=C109</f>
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="26">
-        <v>40</v>
-      </c>
-      <c r="B110" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="C110" s="28">
-        <v>40</v>
-      </c>
-      <c r="D110" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E110" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>266</v>
+      <c r="A110" s="32">
+        <v>30</v>
+      </c>
+      <c r="B110" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C110" s="34">
+        <v>30</v>
+      </c>
+      <c r="D110" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="E110" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="F110" s="32" t="s">
+        <v>197</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="30"/>
-      <c r="B111" s="31"/>
-      <c r="C111" s="30"/>
-      <c r="D111" s="30"/>
-      <c r="E111" s="31"/>
-      <c r="F111" s="30"/>
-      <c r="G111" s="31"/>
+      <c r="A111" s="32">
+        <v>30</v>
+      </c>
+      <c r="B111" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="C111" s="34">
+        <v>30</v>
+      </c>
+      <c r="D111" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="G111" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H111" s="21" t="b">
+        <f>A111=C111</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="30"/>
-      <c r="B112" s="31"/>
-      <c r="C112" s="30"/>
-      <c r="D112" s="30"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="30"/>
-      <c r="G112" s="31"/>
-    </row>
-    <row r="113" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="30"/>
-      <c r="B113" s="31"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="31"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="31"/>
-    </row>
-    <row r="114" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="30"/>
-      <c r="B114" s="31"/>
-      <c r="C114" s="30"/>
-      <c r="D114" s="30"/>
-      <c r="E114" s="31"/>
-      <c r="F114" s="30"/>
-      <c r="G114" s="31"/>
-    </row>
-    <row r="115" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="30"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="30"/>
-      <c r="D115" s="30"/>
-      <c r="E115" s="31"/>
-      <c r="F115" s="30"/>
-      <c r="G115" s="31"/>
-    </row>
-    <row r="116" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="30"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="30"/>
-      <c r="D116" s="30"/>
-      <c r="E116" s="31"/>
-      <c r="F116" s="30"/>
-      <c r="G116" s="31"/>
-    </row>
-    <row r="117" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="30"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="30"/>
-      <c r="D117" s="30"/>
-      <c r="E117" s="31"/>
-      <c r="F117" s="30"/>
-      <c r="G117" s="31"/>
-    </row>
-    <row r="118" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="30"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="30"/>
-      <c r="D118" s="30"/>
-      <c r="E118" s="31"/>
-      <c r="F118" s="30"/>
-      <c r="G118" s="31"/>
-    </row>
-    <row r="119" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="32">
+        <v>30</v>
+      </c>
+      <c r="B112" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C112" s="34">
+        <v>30</v>
+      </c>
+      <c r="D112" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E112" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="G112" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H112" s="21" t="b">
+        <f>A112=C112</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="32">
+        <v>30</v>
+      </c>
+      <c r="B113" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C113" s="34">
+        <v>30</v>
+      </c>
+      <c r="D113" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E113" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F113" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="G113" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H113" s="21" t="b">
+        <f>A113=C113</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="32">
+        <v>30</v>
+      </c>
+      <c r="B114" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C114" s="34">
+        <v>30</v>
+      </c>
+      <c r="D114" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="E114" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="F114" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="G114" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H114" s="21" t="b">
+        <f>A114=C114</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="32">
+        <v>30</v>
+      </c>
+      <c r="B115" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C115" s="34">
+        <v>30</v>
+      </c>
+      <c r="D115" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="E115" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="F115" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="G115" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H115" s="21" t="b">
+        <f>A115=C115</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A116" s="26">
+        <v>40</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C116" s="28">
+        <v>40</v>
+      </c>
+      <c r="D116" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G116" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H116" s="21" t="b">
+        <f>A116=C116</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="26">
+        <v>40</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C117" s="28">
+        <v>40</v>
+      </c>
+      <c r="D117" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="G117" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H117" s="21" t="b">
+        <f>A117=C117</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="26">
+        <v>40</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C118" s="28">
+        <v>40</v>
+      </c>
+      <c r="D118" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="G118" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H118" s="21" t="b">
+        <f>A118=C118</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A119" s="30"/>
       <c r="B119" s="31"/>
       <c r="C119" s="30"/>
@@ -4564,7 +4736,7 @@
       <c r="F119" s="30"/>
       <c r="G119" s="31"/>
     </row>
-    <row r="120" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A120" s="30"/>
       <c r="B120" s="31"/>
       <c r="C120" s="30"/>
@@ -4573,7 +4745,7 @@
       <c r="F120" s="30"/>
       <c r="G120" s="31"/>
     </row>
-    <row r="121" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="30"/>
       <c r="B121" s="31"/>
       <c r="C121" s="30"/>
@@ -4582,7 +4754,7 @@
       <c r="F121" s="30"/>
       <c r="G121" s="31"/>
     </row>
-    <row r="122" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A122" s="30"/>
       <c r="B122" s="31"/>
       <c r="C122" s="30"/>
@@ -4591,7 +4763,7 @@
       <c r="F122" s="30"/>
       <c r="G122" s="31"/>
     </row>
-    <row r="123" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A123" s="30"/>
       <c r="B123" s="31"/>
       <c r="C123" s="30"/>
@@ -4600,127 +4772,151 @@
       <c r="F123" s="30"/>
       <c r="G123" s="31"/>
     </row>
-    <row r="124" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="F124" s="1"/>
-    </row>
-    <row r="125" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="F125" s="1"/>
-    </row>
-    <row r="126" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="F126" s="1"/>
-    </row>
-    <row r="127" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="F127" s="1"/>
-    </row>
-    <row r="128" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="F128" s="1"/>
-    </row>
-    <row r="129" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="F129" s="1"/>
-    </row>
-    <row r="130" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="F130" s="1"/>
-    </row>
-    <row r="131" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="F131" s="1"/>
-    </row>
-    <row r="132" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="30"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="30"/>
+      <c r="D124" s="30"/>
+      <c r="E124" s="31"/>
+      <c r="F124" s="30"/>
+      <c r="G124" s="31"/>
+    </row>
+    <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="30"/>
+      <c r="D125" s="30"/>
+      <c r="E125" s="31"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="31"/>
+    </row>
+    <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="30"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="30"/>
+      <c r="D126" s="30"/>
+      <c r="E126" s="31"/>
+      <c r="F126" s="30"/>
+      <c r="G126" s="31"/>
+    </row>
+    <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="30"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="30"/>
+      <c r="D127" s="30"/>
+      <c r="E127" s="31"/>
+      <c r="F127" s="30"/>
+      <c r="G127" s="31"/>
+    </row>
+    <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="30"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="30"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="31"/>
+      <c r="F128" s="30"/>
+      <c r="G128" s="31"/>
+    </row>
+    <row r="129" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="30"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="31"/>
+      <c r="F129" s="30"/>
+      <c r="G129" s="31"/>
+    </row>
+    <row r="130" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="30"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="31"/>
+      <c r="F130" s="30"/>
+      <c r="G130" s="31"/>
+    </row>
+    <row r="131" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="30"/>
+      <c r="D131" s="30"/>
+      <c r="E131" s="31"/>
+      <c r="F131" s="30"/>
+      <c r="G131" s="31"/>
+    </row>
+    <row r="132" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="F132" s="1"/>
     </row>
-    <row r="133" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="F133" s="1"/>
     </row>
-    <row r="134" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="F134" s="1"/>
     </row>
-    <row r="135" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="F135" s="1"/>
     </row>
-    <row r="136" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="F136" s="1"/>
     </row>
-    <row r="137" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="F137" s="1"/>
     </row>
-    <row r="138" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="F138" s="1"/>
     </row>
-    <row r="139" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="F139" s="1"/>
     </row>
-    <row r="140" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="F140" s="1"/>
     </row>
-    <row r="141" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="F141" s="1"/>
     </row>
-    <row r="142" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="F142" s="1"/>
     </row>
-    <row r="143" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="F143" s="1"/>
     </row>
-    <row r="144" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -9910,12 +10106,60 @@
       <c r="D1008" s="1"/>
       <c r="F1008" s="1"/>
     </row>
+    <row r="1009" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1009" s="1"/>
+      <c r="C1009" s="1"/>
+      <c r="D1009" s="1"/>
+      <c r="F1009" s="1"/>
+    </row>
+    <row r="1010" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1010" s="1"/>
+      <c r="C1010" s="1"/>
+      <c r="D1010" s="1"/>
+      <c r="F1010" s="1"/>
+    </row>
+    <row r="1011" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1011" s="1"/>
+      <c r="C1011" s="1"/>
+      <c r="D1011" s="1"/>
+      <c r="F1011" s="1"/>
+    </row>
+    <row r="1012" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1012" s="1"/>
+      <c r="C1012" s="1"/>
+      <c r="D1012" s="1"/>
+      <c r="F1012" s="1"/>
+    </row>
+    <row r="1013" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1013" s="1"/>
+      <c r="C1013" s="1"/>
+      <c r="D1013" s="1"/>
+      <c r="F1013" s="1"/>
+    </row>
+    <row r="1014" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1014" s="1"/>
+      <c r="C1014" s="1"/>
+      <c r="D1014" s="1"/>
+      <c r="F1014" s="1"/>
+    </row>
+    <row r="1015" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1015" s="1"/>
+      <c r="C1015" s="1"/>
+      <c r="D1015" s="1"/>
+      <c r="F1015" s="1"/>
+    </row>
+    <row r="1016" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1016" s="1"/>
+      <c r="C1016" s="1"/>
+      <c r="D1016" s="1"/>
+      <c r="F1016" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H110">
-    <sortState ref="A2:H110">
-      <sortCondition ref="A2:A110"/>
-      <sortCondition ref="B2:B110"/>
-      <sortCondition ref="D2:D110"/>
+  <autoFilter ref="A1:H118">
+    <sortState ref="A2:H118">
+      <sortCondition ref="A2:A118"/>
+      <sortCondition ref="B2:B118"/>
+      <sortCondition ref="D2:D118"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H102">
@@ -9945,7 +10189,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -9958,7 +10202,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -129,9 +129,6 @@
     <t>21740-020</t>
   </si>
   <si>
-    <t>VIERA ARAUJO</t>
-  </si>
-  <si>
     <t>21740-030</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
     <t>21740-210</t>
   </si>
   <si>
-    <t>CARROBE DA COSTA</t>
-  </si>
-  <si>
     <t>21740-220</t>
   </si>
   <si>
@@ -889,6 +883,12 @@
   </si>
   <si>
     <t>DONA OLIMPIA</t>
+  </si>
+  <si>
+    <t>VIEIRA ARAUJO</t>
+  </si>
+  <si>
+    <t>CANROBERT DA COSTA</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1448,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1456,7 +1456,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C2" s="34">
         <v>13</v>
@@ -1465,7 +1465,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F2" s="32" t="s">
         <v>26</v>
@@ -1512,7 +1512,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C4" s="34">
         <v>13</v>
@@ -1521,7 +1521,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>26</v>
@@ -1540,7 +1540,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C5" s="34">
         <v>13</v>
@@ -1549,7 +1549,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>26</v>
@@ -1596,7 +1596,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C7" s="34">
         <v>13</v>
@@ -1605,7 +1605,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F7" s="32" t="s">
         <v>26</v>
@@ -1624,7 +1624,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C8" s="34">
         <v>13</v>
@@ -1633,7 +1633,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>26</v>
@@ -1680,7 +1680,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C10" s="34">
         <v>13</v>
@@ -1689,7 +1689,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F10" s="32" t="s">
         <v>26</v>
@@ -1714,7 +1714,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>8</v>
@@ -1736,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C12" s="34">
         <v>13</v>
@@ -1745,7 +1745,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>26</v>
@@ -1792,7 +1792,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C14" s="34">
         <v>13</v>
@@ -1801,7 +1801,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>26</v>
@@ -1904,19 +1904,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="28">
         <v>15</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G18" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F18),0)&gt;0), MAX($G$1:G17)+1, ""))</f>
@@ -1932,19 +1932,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" s="28">
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G19" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F19),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
@@ -1960,19 +1960,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="28">
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G20" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -1988,19 +1988,19 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
@@ -2016,19 +2016,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
@@ -2044,19 +2044,19 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2072,7 +2072,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
@@ -2084,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
@@ -2100,19 +2100,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
@@ -2128,19 +2128,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
@@ -2156,19 +2156,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2184,19 +2184,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
@@ -2212,7 +2212,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
@@ -2224,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2240,19 +2240,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2268,19 +2268,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2296,19 +2296,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2324,19 +2324,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2352,19 +2352,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2380,7 +2380,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
@@ -2389,10 +2389,10 @@
         <v>2.1</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2408,19 +2408,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2436,19 +2436,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2464,19 +2464,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2492,19 +2492,19 @@
         <v>17</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C39" s="37">
         <v>17</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E39" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2520,19 +2520,19 @@
         <v>17</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>70</v>
+        <v>287</v>
       </c>
       <c r="C40" s="37">
         <v>17</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2548,19 +2548,19 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C41" s="37">
         <v>17</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E41" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2576,19 +2576,19 @@
         <v>17</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="37">
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E42" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="35" t="s">
         <v>62</v>
-      </c>
-      <c r="F42" s="35" t="s">
-        <v>63</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2604,19 +2604,19 @@
         <v>17</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C43" s="40">
         <v>17</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E43" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2632,19 +2632,19 @@
         <v>17</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44" s="40">
         <v>17</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E44" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2660,19 +2660,19 @@
         <v>17</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="37">
         <v>17</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E45" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2688,19 +2688,19 @@
         <v>17</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="37">
         <v>17</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E46" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2716,19 +2716,19 @@
         <v>17</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C47" s="40">
         <v>17</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E47" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C48" s="40">
         <v>17</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E48" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
@@ -2772,19 +2772,19 @@
         <v>17</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49" s="37">
         <v>17</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E49" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -2800,19 +2800,19 @@
         <v>17</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C50" s="40">
         <v>17</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E50" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -2834,7 +2834,7 @@
         <v>17</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E51" s="36" t="s">
         <v>8</v>
@@ -2862,7 +2862,7 @@
         <v>17</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E52" s="36" t="s">
         <v>8</v>
@@ -2884,19 +2884,19 @@
         <v>20</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C53" s="34">
         <v>20</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E53" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F53" s="32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -2912,19 +2912,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C54" s="34">
         <v>20</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
@@ -2940,19 +2940,19 @@
         <v>20</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C55" s="34">
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
@@ -2968,19 +2968,19 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -2996,19 +2996,19 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
@@ -3024,19 +3024,19 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
@@ -3052,7 +3052,7 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
@@ -3080,19 +3080,19 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3108,19 +3108,19 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3136,19 +3136,19 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3164,19 +3164,19 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3192,19 +3192,19 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3220,19 +3220,19 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3248,19 +3248,19 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3276,19 +3276,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3304,19 +3304,19 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3332,19 +3332,19 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3360,19 +3360,19 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3388,19 +3388,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3416,19 +3416,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3444,19 +3444,19 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3472,19 +3472,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3500,19 +3500,19 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3528,19 +3528,19 @@
         <v>20</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C76" s="34">
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F76" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3556,19 +3556,19 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E77" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
@@ -3596,7 +3596,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3612,19 +3612,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3640,19 +3640,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E80" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3668,19 +3668,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E81" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3696,19 +3696,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3724,19 +3724,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E83" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3752,19 +3752,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3780,19 +3780,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3808,19 +3808,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C86" s="34">
         <v>20</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="32" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3836,19 +3836,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3864,19 +3864,19 @@
         <v>25</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C88" s="28">
         <v>25</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E88" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -3892,19 +3892,19 @@
         <v>25</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C89" s="28">
         <v>25</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E89" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -3920,19 +3920,19 @@
         <v>25</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C90" s="28">
         <v>25</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -3948,19 +3948,19 @@
         <v>25</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C91" s="28">
         <v>25</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -3976,19 +3976,19 @@
         <v>25</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C92" s="28">
         <v>25</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4004,19 +4004,19 @@
         <v>25</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C93" s="28">
         <v>25</v>
       </c>
       <c r="D93" s="26" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4032,19 +4032,19 @@
         <v>25</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C94" s="28">
         <v>25</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E94" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4060,19 +4060,19 @@
         <v>25</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C95" s="34">
         <v>25</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E95" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F95" s="32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4088,19 +4088,19 @@
         <v>25</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C96" s="28">
         <v>25</v>
       </c>
       <c r="D96" s="26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4116,19 +4116,19 @@
         <v>25</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C97" s="28">
         <v>25</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4144,19 +4144,19 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4172,19 +4172,19 @@
         <v>25</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C99" s="28">
         <v>25</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E99" s="27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4200,19 +4200,19 @@
         <v>25</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C100" s="28">
         <v>25</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E100" s="27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4228,19 +4228,19 @@
         <v>25</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C101" s="28">
         <v>25</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E101" s="27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4256,19 +4256,19 @@
         <v>25</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C102" s="28">
         <v>25</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E102" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4284,19 +4284,19 @@
         <v>25</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C103" s="28">
         <v>25</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4312,19 +4312,19 @@
         <v>25</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C104" s="28">
         <v>25</v>
       </c>
       <c r="D104" s="41" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E104" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4340,19 +4340,19 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E105" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4368,7 +4368,7 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
@@ -4377,10 +4377,10 @@
         <v>2.5</v>
       </c>
       <c r="E106" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4396,19 +4396,19 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4424,19 +4424,19 @@
         <v>30</v>
       </c>
       <c r="B108" s="33" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C108" s="34">
         <v>30</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F108" s="32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4452,19 +4452,19 @@
         <v>30</v>
       </c>
       <c r="B109" s="33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C109" s="34">
         <v>30</v>
       </c>
       <c r="D109" s="32" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E109" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F109" s="32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4480,19 +4480,19 @@
         <v>30</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C110" s="34">
         <v>30</v>
       </c>
       <c r="D110" s="32" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F110" s="32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4508,19 +4508,19 @@
         <v>30</v>
       </c>
       <c r="B111" s="33" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C111" s="34">
         <v>30</v>
       </c>
       <c r="D111" s="32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E111" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F111" s="32" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4536,19 +4536,19 @@
         <v>30</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C112" s="34">
         <v>30</v>
       </c>
       <c r="D112" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E112" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="32" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4564,19 +4564,19 @@
         <v>30</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C113" s="34">
         <v>30</v>
       </c>
       <c r="D113" s="32" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E113" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F113" s="32" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4592,19 +4592,19 @@
         <v>30</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C114" s="34">
         <v>30</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F114" s="32" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4620,19 +4620,19 @@
         <v>30</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C115" s="34">
         <v>30</v>
       </c>
       <c r="D115" s="32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F115" s="32" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4648,19 +4648,19 @@
         <v>40</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C116" s="28">
         <v>40</v>
       </c>
       <c r="D116" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E116" s="27" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4676,19 +4676,19 @@
         <v>40</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C117" s="28">
         <v>40</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4704,7 +4704,7 @@
         <v>40</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C118" s="28">
         <v>40</v>
@@ -4713,10 +4713,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E118" s="27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -10189,7 +10189,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -10202,7 +10202,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$118</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$123</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="295">
   <si>
     <t>Grupo</t>
   </si>
@@ -889,6 +889,27 @@
   </si>
   <si>
     <t>CANROBERT DA COSTA</t>
+  </si>
+  <si>
+    <t>JUNDIAPEBA</t>
+  </si>
+  <si>
+    <t>Nogueira</t>
+  </si>
+  <si>
+    <t>JOANES</t>
+  </si>
+  <si>
+    <t>VILA DAS MANGUEIRAS</t>
+  </si>
+  <si>
+    <t>TV. ARAUJO BARBOSA</t>
+  </si>
+  <si>
+    <t>TV. CONTE COMIGO</t>
+  </si>
+  <si>
+    <t>TRAJANO</t>
   </si>
 </sst>
 </file>
@@ -1417,14 +1438,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1016"/>
+  <dimension ref="A1:H1022"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
     <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.90625" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4000,26 +4021,26 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="26">
+      <c r="A93" s="32">
         <v>25</v>
       </c>
-      <c r="B93" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C93" s="28">
+      <c r="B93" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C93" s="34">
         <v>25</v>
       </c>
-      <c r="D93" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>174</v>
+      <c r="D93" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E93" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F93" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G93" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
@@ -4028,26 +4049,26 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="26">
+      <c r="A94" s="32">
         <v>25</v>
       </c>
-      <c r="B94" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="C94" s="28">
+      <c r="B94" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C94" s="34">
         <v>25</v>
       </c>
-      <c r="D94" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E94" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="26" t="s">
-        <v>172</v>
+      <c r="D94" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E94" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F94" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G94" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
@@ -4056,23 +4077,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="32">
+      <c r="A95" s="26">
         <v>25</v>
       </c>
-      <c r="B95" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C95" s="34">
+      <c r="B95" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C95" s="28">
         <v>25</v>
       </c>
-      <c r="D95" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="32" t="s">
-        <v>104</v>
+      <c r="D95" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4088,19 +4109,19 @@
         <v>25</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C96" s="28">
         <v>25</v>
       </c>
       <c r="D96" s="26" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4112,26 +4133,26 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="26">
+      <c r="A97" s="32">
         <v>25</v>
       </c>
-      <c r="B97" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="C97" s="28">
+      <c r="B97" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="34">
         <v>25</v>
       </c>
-      <c r="D97" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E97" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F97" s="26" t="s">
-        <v>168</v>
+      <c r="D97" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G97" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
@@ -4144,19 +4165,19 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4172,19 +4193,19 @@
         <v>25</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C99" s="28">
         <v>25</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E99" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4200,19 +4221,19 @@
         <v>25</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C100" s="28">
         <v>25</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E100" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4228,19 +4249,19 @@
         <v>25</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C101" s="28">
         <v>25</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E101" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4256,19 +4277,19 @@
         <v>25</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C102" s="28">
         <v>25</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E102" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4284,19 +4305,19 @@
         <v>25</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C103" s="28">
         <v>25</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4312,22 +4333,22 @@
         <v>25</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="C104" s="28">
         <v>25</v>
       </c>
-      <c r="D104" s="41" t="s">
-        <v>234</v>
+      <c r="D104" s="26" t="s">
+        <v>229</v>
       </c>
       <c r="E104" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="G104" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
@@ -4340,19 +4361,19 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E105" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4368,22 +4389,22 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
-      <c r="D106" s="26">
-        <v>2.5</v>
+      <c r="D106" s="41" t="s">
+        <v>234</v>
       </c>
       <c r="E106" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G106" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
@@ -4396,19 +4417,19 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4421,25 +4442,25 @@
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A108" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B108" s="33" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="C108" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="F108" s="32" t="s">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="G108" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
@@ -4449,25 +4470,25 @@
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A109" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B109" s="33" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="C109" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D109" s="32" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="E109" s="33" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="F109" s="32" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="G109" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
@@ -4477,25 +4498,25 @@
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A110" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="C110" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D110" s="32" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="F110" s="32" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="G110" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
@@ -4504,23 +4525,23 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="32">
-        <v>30</v>
-      </c>
-      <c r="B111" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="C111" s="34">
-        <v>30</v>
-      </c>
-      <c r="D111" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E111" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F111" s="32" t="s">
-        <v>193</v>
+      <c r="A111" s="26">
+        <v>25</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C111" s="28">
+        <v>25</v>
+      </c>
+      <c r="D111" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E111" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>259</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4533,25 +4554,25 @@
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A112" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>191</v>
+        <v>291</v>
       </c>
       <c r="C112" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D112" s="32" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="E112" s="33" t="s">
-        <v>8</v>
+        <v>289</v>
       </c>
       <c r="F112" s="32" t="s">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="G112" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H112" s="21" t="b">
@@ -4560,23 +4581,23 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="32">
-        <v>30</v>
-      </c>
-      <c r="B113" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C113" s="34">
-        <v>30</v>
-      </c>
-      <c r="D113" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="E113" s="33" t="s">
+      <c r="A113" s="26">
+        <v>25</v>
+      </c>
+      <c r="B113" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C113" s="28">
+        <v>25</v>
+      </c>
+      <c r="D113" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E113" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="F113" s="32" t="s">
-        <v>190</v>
+      <c r="F113" s="26" t="s">
+        <v>152</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4592,19 +4613,19 @@
         <v>30</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C114" s="34">
         <v>30</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E114" s="33" t="s">
         <v>134</v>
       </c>
       <c r="F114" s="32" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4620,19 +4641,19 @@
         <v>30</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C115" s="34">
         <v>30</v>
       </c>
       <c r="D115" s="32" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E115" s="33" t="s">
         <v>134</v>
       </c>
       <c r="F115" s="32" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4644,23 +4665,23 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="26">
-        <v>40</v>
-      </c>
-      <c r="B116" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="C116" s="28">
-        <v>40</v>
-      </c>
-      <c r="D116" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>204</v>
+      <c r="A116" s="32">
+        <v>30</v>
+      </c>
+      <c r="B116" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C116" s="34">
+        <v>30</v>
+      </c>
+      <c r="D116" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="E116" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F116" s="32" t="s">
+        <v>195</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4672,23 +4693,23 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="26">
-        <v>40</v>
-      </c>
-      <c r="B117" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C117" s="28">
-        <v>40</v>
-      </c>
-      <c r="D117" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E117" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>201</v>
+      <c r="A117" s="32">
+        <v>30</v>
+      </c>
+      <c r="B117" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="C117" s="34">
+        <v>30</v>
+      </c>
+      <c r="D117" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E117" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" s="32" t="s">
+        <v>193</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4700,23 +4721,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="26">
-        <v>40</v>
-      </c>
-      <c r="B118" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C118" s="28">
-        <v>40</v>
-      </c>
-      <c r="D118" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E118" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>257</v>
+      <c r="A118" s="32">
+        <v>30</v>
+      </c>
+      <c r="B118" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C118" s="34">
+        <v>30</v>
+      </c>
+      <c r="D118" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="E118" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" s="32" t="s">
+        <v>192</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4728,58 +4749,172 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="30"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="30"/>
-      <c r="D119" s="30"/>
-      <c r="E119" s="31"/>
-      <c r="F119" s="30"/>
-      <c r="G119" s="31"/>
+      <c r="A119" s="32">
+        <v>30</v>
+      </c>
+      <c r="B119" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C119" s="34">
+        <v>30</v>
+      </c>
+      <c r="D119" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E119" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="G119" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H119" s="21" t="b">
+        <f>A119=C119</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="30"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="30"/>
-      <c r="D120" s="30"/>
-      <c r="E120" s="31"/>
-      <c r="F120" s="30"/>
-      <c r="G120" s="31"/>
+      <c r="A120" s="32">
+        <v>30</v>
+      </c>
+      <c r="B120" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" s="34">
+        <v>30</v>
+      </c>
+      <c r="D120" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="E120" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F120" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="G120" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H120" s="21" t="b">
+        <f>A120=C120</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="30"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="30"/>
-      <c r="D121" s="30"/>
-      <c r="E121" s="31"/>
-      <c r="F121" s="30"/>
-      <c r="G121" s="31"/>
+      <c r="A121" s="32">
+        <v>30</v>
+      </c>
+      <c r="B121" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C121" s="34">
+        <v>30</v>
+      </c>
+      <c r="D121" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E121" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F121" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="G121" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H121" s="21" t="b">
+        <f>A121=C121</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="30"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="30"/>
-      <c r="D122" s="30"/>
-      <c r="E122" s="31"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="31"/>
+      <c r="A122" s="26">
+        <v>40</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C122" s="28">
+        <v>40</v>
+      </c>
+      <c r="D122" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="G122" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H122" s="21" t="b">
+        <f>A122=C122</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="30"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="30"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="31"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="31"/>
+      <c r="A123" s="26">
+        <v>40</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C123" s="28">
+        <v>40</v>
+      </c>
+      <c r="D123" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="G123" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H123" s="21" t="b">
+        <f>A123=C123</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="30"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="30"/>
-      <c r="D124" s="30"/>
-      <c r="E124" s="31"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="31"/>
+      <c r="A124" s="26">
+        <v>40</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C124" s="28">
+        <v>40</v>
+      </c>
+      <c r="D124" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G124" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H124" s="21" t="b">
+        <f>A124=C124</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="30"/>
@@ -4845,40 +4980,58 @@
       <c r="G131" s="31"/>
     </row>
     <row r="132" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="F132" s="1"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="30"/>
+      <c r="D132" s="30"/>
+      <c r="E132" s="31"/>
+      <c r="F132" s="30"/>
+      <c r="G132" s="31"/>
     </row>
     <row r="133" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="F133" s="1"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="30"/>
+      <c r="E133" s="31"/>
+      <c r="F133" s="30"/>
+      <c r="G133" s="31"/>
     </row>
     <row r="134" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-      <c r="F134" s="1"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="30"/>
+      <c r="D134" s="30"/>
+      <c r="E134" s="31"/>
+      <c r="F134" s="30"/>
+      <c r="G134" s="31"/>
     </row>
     <row r="135" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-      <c r="F135" s="1"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="30"/>
+      <c r="D135" s="30"/>
+      <c r="E135" s="31"/>
+      <c r="F135" s="30"/>
+      <c r="G135" s="31"/>
     </row>
     <row r="136" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-      <c r="F136" s="1"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="31"/>
+      <c r="F136" s="30"/>
+      <c r="G136" s="31"/>
     </row>
     <row r="137" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="F137" s="1"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="30"/>
+      <c r="E137" s="31"/>
+      <c r="F137" s="30"/>
+      <c r="G137" s="31"/>
     </row>
     <row r="138" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
@@ -10154,12 +10307,48 @@
       <c r="D1016" s="1"/>
       <c r="F1016" s="1"/>
     </row>
+    <row r="1017" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1017" s="1"/>
+      <c r="C1017" s="1"/>
+      <c r="D1017" s="1"/>
+      <c r="F1017" s="1"/>
+    </row>
+    <row r="1018" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1018" s="1"/>
+      <c r="C1018" s="1"/>
+      <c r="D1018" s="1"/>
+      <c r="F1018" s="1"/>
+    </row>
+    <row r="1019" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1019" s="1"/>
+      <c r="C1019" s="1"/>
+      <c r="D1019" s="1"/>
+      <c r="F1019" s="1"/>
+    </row>
+    <row r="1020" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1020" s="1"/>
+      <c r="C1020" s="1"/>
+      <c r="D1020" s="1"/>
+      <c r="F1020" s="1"/>
+    </row>
+    <row r="1021" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1021" s="1"/>
+      <c r="C1021" s="1"/>
+      <c r="D1021" s="1"/>
+      <c r="F1021" s="1"/>
+    </row>
+    <row r="1022" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1022" s="1"/>
+      <c r="C1022" s="1"/>
+      <c r="D1022" s="1"/>
+      <c r="F1022" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H118">
-    <sortState ref="A2:H118">
-      <sortCondition ref="A2:A118"/>
-      <sortCondition ref="B2:B118"/>
-      <sortCondition ref="D2:D118"/>
+  <autoFilter ref="A1:H124">
+    <sortState ref="A2:H124">
+      <sortCondition ref="A2:A124"/>
+      <sortCondition ref="B2:B124"/>
+      <sortCondition ref="D2:D124"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H102">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$124</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$125</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="298">
   <si>
     <t>Grupo</t>
   </si>
@@ -910,6 +910,15 @@
   </si>
   <si>
     <t>TRAJANO</t>
+  </si>
+  <si>
+    <t>FRANCISCO MUZZI</t>
+  </si>
+  <si>
+    <t>SÃO PEDRO ALCANTARA</t>
+  </si>
+  <si>
+    <t>Curral</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1447,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1022"/>
+  <dimension ref="A1:H1024"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1632,7 +1641,7 @@
         <v>26</v>
       </c>
       <c r="G7" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F7),0)&gt;0), MAX($G$1:G5)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F7),0)&gt;0), MAX($G$1:G6)+1, ""))</f>
         <v/>
       </c>
       <c r="H7" s="21" t="b">
@@ -1660,7 +1669,7 @@
         <v>26</v>
       </c>
       <c r="G8" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F8),0)&gt;0), MAX($G$1:G6)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F8),0)&gt;0), MAX($G$1:G7)+1, ""))</f>
         <v/>
       </c>
       <c r="H8" s="21" t="b">
@@ -2625,19 +2634,19 @@
         <v>17</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>109</v>
+        <v>295</v>
       </c>
       <c r="C43" s="40">
         <v>17</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E43" s="39" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2653,19 +2662,19 @@
         <v>17</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C44" s="40">
         <v>17</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="E44" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2677,23 +2686,23 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="35">
+      <c r="A45" s="38">
         <v>17</v>
       </c>
-      <c r="B45" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="37">
+      <c r="B45" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="40">
         <v>17</v>
       </c>
-      <c r="D45" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="E45" s="36" t="s">
+      <c r="D45" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="E45" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="35" t="s">
-        <v>54</v>
+      <c r="F45" s="38" t="s">
+        <v>108</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2709,19 +2718,19 @@
         <v>17</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C46" s="37">
         <v>17</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E46" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2733,23 +2742,23 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="38">
+      <c r="A47" s="35">
         <v>17</v>
       </c>
-      <c r="B47" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="40">
+      <c r="B47" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="37">
         <v>17</v>
       </c>
-      <c r="D47" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E47" s="39" t="s">
+      <c r="D47" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="38" t="s">
-        <v>100</v>
+      <c r="F47" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -2765,19 +2774,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C48" s="40">
         <v>17</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E48" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
@@ -2789,23 +2798,23 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="35">
+      <c r="A49" s="38">
         <v>17</v>
       </c>
-      <c r="B49" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="37">
+      <c r="B49" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="40">
         <v>17</v>
       </c>
-      <c r="D49" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E49" s="36" t="s">
+      <c r="D49" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="35" t="s">
-        <v>38</v>
+      <c r="F49" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -2817,23 +2826,23 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="38">
+      <c r="A50" s="35">
         <v>17</v>
       </c>
-      <c r="B50" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="40">
+      <c r="B50" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="37">
         <v>17</v>
       </c>
-      <c r="D50" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E50" s="39" t="s">
+      <c r="D50" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="38" t="s">
-        <v>86</v>
+      <c r="F50" s="35" t="s">
+        <v>38</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -2845,23 +2854,23 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="35">
+      <c r="A51" s="38">
         <v>17</v>
       </c>
-      <c r="B51" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="37">
+      <c r="B51" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="40">
         <v>17</v>
       </c>
-      <c r="D51" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="E51" s="36" t="s">
+      <c r="D51" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="35" t="s">
-        <v>33</v>
+      <c r="F51" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -2877,19 +2886,19 @@
         <v>17</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C52" s="37">
         <v>17</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E52" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -2901,23 +2910,23 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="32">
-        <v>20</v>
-      </c>
-      <c r="B53" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="C53" s="34">
-        <v>20</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E53" s="33" t="s">
+      <c r="A53" s="35">
+        <v>17</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="37">
+        <v>17</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="E53" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="32" t="s">
-        <v>150</v>
+      <c r="F53" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -2933,19 +2942,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C54" s="34">
         <v>20</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
@@ -2961,19 +2970,19 @@
         <v>20</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C55" s="34">
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
@@ -2989,19 +2998,19 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -3017,19 +3026,19 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
@@ -3045,19 +3054,19 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>261</v>
+        <v>141</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>262</v>
+        <v>142</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
@@ -3073,19 +3082,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
-      <c r="D59" s="32">
-        <v>4.2</v>
+      <c r="D59" s="32" t="s">
+        <v>230</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="32">
-        <v>21765430</v>
+      <c r="F59" s="32" t="s">
+        <v>262</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
@@ -3101,19 +3110,19 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
-      <c r="D60" s="32" t="s">
-        <v>215</v>
+      <c r="D60" s="32">
+        <v>4.2</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="32" t="s">
-        <v>140</v>
+      <c r="F60" s="32">
+        <v>21765430</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3129,19 +3138,19 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>271</v>
+        <v>139</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3157,19 +3166,19 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3185,19 +3194,19 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3213,19 +3222,19 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3241,19 +3250,19 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3269,19 +3278,19 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3297,19 +3306,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3325,19 +3334,19 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3353,19 +3362,19 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>264</v>
+        <v>124</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3381,19 +3390,19 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>121</v>
+        <v>263</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>122</v>
+        <v>264</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3409,19 +3418,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3437,19 +3446,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3465,19 +3474,19 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3493,19 +3502,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3521,19 +3530,19 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3549,19 +3558,19 @@
         <v>20</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C76" s="34">
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F76" s="32" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3577,19 +3586,19 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3605,19 +3614,19 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
-      <c r="D78" s="32">
-        <v>6.2</v>
+      <c r="D78" s="32" t="s">
+        <v>212</v>
       </c>
       <c r="E78" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3633,19 +3642,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>101</v>
+        <v>269</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
-      <c r="D79" s="32" t="s">
-        <v>220</v>
+      <c r="D79" s="32">
+        <v>6.2</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>102</v>
+        <v>270</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3661,19 +3670,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3689,19 +3698,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E81" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3717,19 +3726,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3745,19 +3754,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E83" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3773,19 +3782,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>87</v>
+        <v>296</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
-      <c r="D84" s="32" t="s">
-        <v>225</v>
+      <c r="D84" s="32">
+        <v>1.8</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>8</v>
+        <v>297</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3801,19 +3810,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3829,19 +3838,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C86" s="34">
         <v>20</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="32" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3857,19 +3866,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3881,23 +3890,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="26">
-        <v>25</v>
-      </c>
-      <c r="B88" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C88" s="28">
-        <v>25</v>
-      </c>
-      <c r="D88" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E88" s="27" t="s">
+      <c r="A88" s="32">
+        <v>20</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C88" s="34">
+        <v>20</v>
+      </c>
+      <c r="D88" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E88" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F88" s="26" t="s">
-        <v>184</v>
+      <c r="F88" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -3909,23 +3918,23 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="26">
-        <v>25</v>
-      </c>
-      <c r="B89" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C89" s="28">
-        <v>25</v>
-      </c>
-      <c r="D89" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F89" s="26" t="s">
-        <v>182</v>
+      <c r="A89" s="32">
+        <v>20</v>
+      </c>
+      <c r="B89" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C89" s="34">
+        <v>20</v>
+      </c>
+      <c r="D89" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E89" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -3941,19 +3950,19 @@
         <v>25</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C90" s="28">
         <v>25</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -3969,19 +3978,19 @@
         <v>25</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C91" s="28">
         <v>25</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E91" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -3997,19 +4006,19 @@
         <v>25</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C92" s="28">
         <v>25</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E92" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4021,26 +4030,26 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="32">
+      <c r="A93" s="26">
         <v>25</v>
       </c>
-      <c r="B93" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C93" s="34">
+      <c r="B93" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="28">
         <v>25</v>
       </c>
-      <c r="D93" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E93" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F93" s="32" t="s">
-        <v>104</v>
+      <c r="D93" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F93" s="26" t="s">
+        <v>178</v>
       </c>
       <c r="G93" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
@@ -4049,26 +4058,26 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="32">
+      <c r="A94" s="26">
         <v>25</v>
       </c>
-      <c r="B94" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C94" s="34">
+      <c r="B94" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C94" s="28">
         <v>25</v>
       </c>
-      <c r="D94" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E94" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F94" s="32" t="s">
-        <v>104</v>
+      <c r="D94" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F94" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="G94" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
@@ -4077,23 +4086,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
+      <c r="A95" s="32">
         <v>25</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C95" s="28">
+      <c r="B95" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C95" s="34">
         <v>25</v>
       </c>
-      <c r="D95" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>174</v>
+      <c r="D95" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E95" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F95" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4105,23 +4114,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="26">
+      <c r="A96" s="32">
         <v>25</v>
       </c>
-      <c r="B96" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="C96" s="28">
+      <c r="B96" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C96" s="34">
         <v>25</v>
       </c>
-      <c r="D96" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E96" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="26" t="s">
-        <v>172</v>
+      <c r="D96" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F96" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4133,26 +4142,26 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="32">
+      <c r="A97" s="26">
         <v>25</v>
       </c>
-      <c r="B97" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="34">
+      <c r="B97" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C97" s="28">
         <v>25</v>
       </c>
-      <c r="D97" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E97" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" s="32" t="s">
-        <v>104</v>
+      <c r="D97" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="G97" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
@@ -4165,19 +4174,19 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4189,23 +4198,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="26">
+      <c r="A99" s="32">
         <v>25</v>
       </c>
-      <c r="B99" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="C99" s="28">
+      <c r="B99" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="C99" s="34">
         <v>25</v>
       </c>
-      <c r="D99" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>168</v>
+      <c r="D99" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E99" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4221,19 +4230,19 @@
         <v>25</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C100" s="28">
         <v>25</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E100" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4249,19 +4258,19 @@
         <v>25</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C101" s="28">
         <v>25</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E101" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4277,19 +4286,19 @@
         <v>25</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C102" s="28">
         <v>25</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E102" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4305,19 +4314,19 @@
         <v>25</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C103" s="28">
         <v>25</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E103" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4333,19 +4342,19 @@
         <v>25</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C104" s="28">
         <v>25</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E104" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4361,19 +4370,19 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E105" s="27" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4389,22 +4398,22 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
-      <c r="D106" s="41" t="s">
-        <v>234</v>
+      <c r="D106" s="26" t="s">
+        <v>229</v>
       </c>
       <c r="E106" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="G106" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
@@ -4417,19 +4426,19 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E107" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4441,26 +4450,26 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="32">
+      <c r="A108" s="26">
         <v>25</v>
       </c>
-      <c r="B108" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="C108" s="34">
+      <c r="B108" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" s="28">
         <v>25</v>
       </c>
-      <c r="D108" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E108" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F108" s="32" t="s">
-        <v>104</v>
+      <c r="D108" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>254</v>
       </c>
       <c r="G108" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
@@ -4469,26 +4478,26 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="32">
+      <c r="A109" s="26">
         <v>25</v>
       </c>
-      <c r="B109" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C109" s="34">
+      <c r="B109" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C109" s="28">
         <v>25</v>
       </c>
-      <c r="D109" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E109" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F109" s="32" t="s">
-        <v>104</v>
+      <c r="D109" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="G109" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
@@ -4501,7 +4510,7 @@
         <v>25</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C110" s="34">
         <v>25</v>
@@ -4516,7 +4525,7 @@
         <v>104</v>
       </c>
       <c r="G110" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
@@ -4525,23 +4534,23 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="26">
+      <c r="A111" s="32">
         <v>25</v>
       </c>
-      <c r="B111" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C111" s="28">
+      <c r="B111" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C111" s="34">
         <v>25</v>
       </c>
-      <c r="D111" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E111" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>259</v>
+      <c r="D111" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E111" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F111" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4557,7 +4566,7 @@
         <v>25</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C112" s="34">
         <v>25</v>
@@ -4572,7 +4581,7 @@
         <v>104</v>
       </c>
       <c r="G112" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
         <v/>
       </c>
       <c r="H112" s="21" t="b">
@@ -4585,19 +4594,19 @@
         <v>25</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="C113" s="28">
         <v>25</v>
       </c>
-      <c r="D113" s="26" t="s">
-        <v>231</v>
+      <c r="D113" s="26">
+        <v>2.5</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4610,22 +4619,22 @@
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A114" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="C114" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="F114" s="32" t="s">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4637,23 +4646,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="32">
-        <v>30</v>
-      </c>
-      <c r="B115" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C115" s="34">
-        <v>30</v>
-      </c>
-      <c r="D115" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="E115" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="F115" s="32" t="s">
-        <v>195</v>
+      <c r="A115" s="26">
+        <v>25</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="28">
+        <v>25</v>
+      </c>
+      <c r="D115" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>152</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4669,19 +4678,19 @@
         <v>30</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C116" s="34">
         <v>30</v>
       </c>
       <c r="D116" s="32" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E116" s="33" t="s">
         <v>134</v>
       </c>
       <c r="F116" s="32" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4697,19 +4706,19 @@
         <v>30</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="C117" s="34">
         <v>30</v>
       </c>
       <c r="D117" s="32" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E117" s="33" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F117" s="32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4725,19 +4734,19 @@
         <v>30</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C118" s="34">
         <v>30</v>
       </c>
       <c r="D118" s="32" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E118" s="33" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F118" s="32" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4753,19 +4762,19 @@
         <v>30</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="C119" s="34">
         <v>30</v>
       </c>
       <c r="D119" s="32" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F119" s="32" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4781,19 +4790,19 @@
         <v>30</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C120" s="34">
         <v>30</v>
       </c>
       <c r="D120" s="32" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F120" s="32" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4809,19 +4818,19 @@
         <v>30</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C121" s="34">
         <v>30</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E121" s="33" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F121" s="32" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4833,23 +4842,23 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="26">
-        <v>40</v>
-      </c>
-      <c r="B122" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="C122" s="28">
-        <v>40</v>
-      </c>
-      <c r="D122" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E122" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>204</v>
+      <c r="A122" s="32">
+        <v>30</v>
+      </c>
+      <c r="B122" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C122" s="34">
+        <v>30</v>
+      </c>
+      <c r="D122" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="E122" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F122" s="32" t="s">
+        <v>188</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -4861,23 +4870,23 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="26">
-        <v>40</v>
-      </c>
-      <c r="B123" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C123" s="28">
-        <v>40</v>
-      </c>
-      <c r="D123" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E123" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>201</v>
+      <c r="A123" s="32">
+        <v>30</v>
+      </c>
+      <c r="B123" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C123" s="34">
+        <v>30</v>
+      </c>
+      <c r="D123" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E123" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F123" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -4893,19 +4902,19 @@
         <v>40</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="C124" s="28">
         <v>40</v>
       </c>
-      <c r="D124" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D124" s="26" t="s">
+        <v>249</v>
       </c>
       <c r="E124" s="27" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -4917,22 +4926,60 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="30"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="30"/>
-      <c r="D125" s="30"/>
-      <c r="E125" s="31"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="31"/>
+      <c r="A125" s="26">
+        <v>40</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C125" s="28">
+        <v>40</v>
+      </c>
+      <c r="D125" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F125" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="G125" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H125" s="21" t="b">
+        <f>A125=C125</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="30"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="30"/>
-      <c r="D126" s="30"/>
-      <c r="E126" s="31"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="31"/>
+      <c r="A126" s="26">
+        <v>40</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C126" s="28">
+        <v>40</v>
+      </c>
+      <c r="D126" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G126" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H126" s="21" t="b">
+        <f>A126=C126</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A127" s="30"/>
@@ -5034,16 +5081,22 @@
       <c r="G137" s="31"/>
     </row>
     <row r="138" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
-      <c r="F138" s="1"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="30"/>
+      <c r="D138" s="30"/>
+      <c r="E138" s="31"/>
+      <c r="F138" s="30"/>
+      <c r="G138" s="31"/>
     </row>
     <row r="139" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-      <c r="F139" s="1"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="30"/>
+      <c r="D139" s="30"/>
+      <c r="E139" s="31"/>
+      <c r="F139" s="30"/>
+      <c r="G139" s="31"/>
     </row>
     <row r="140" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
@@ -10343,12 +10396,24 @@
       <c r="D1022" s="1"/>
       <c r="F1022" s="1"/>
     </row>
+    <row r="1023" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1023" s="1"/>
+      <c r="C1023" s="1"/>
+      <c r="D1023" s="1"/>
+      <c r="F1023" s="1"/>
+    </row>
+    <row r="1024" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1024" s="1"/>
+      <c r="C1024" s="1"/>
+      <c r="D1024" s="1"/>
+      <c r="F1024" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H124">
-    <sortState ref="A2:H124">
-      <sortCondition ref="A2:A124"/>
-      <sortCondition ref="B2:B124"/>
-      <sortCondition ref="D2:D124"/>
+  <autoFilter ref="A1:H126">
+    <sortState ref="A2:H126">
+      <sortCondition ref="A2:A126"/>
+      <sortCondition ref="B2:B126"/>
+      <sortCondition ref="D2:D126"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H102">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -1505,7 +1505,7 @@
         <v/>
       </c>
       <c r="H2" s="21" t="b">
-        <f>A2=C2</f>
+        <f t="shared" ref="H2:H33" si="0">A2=C2</f>
         <v>1</v>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f>A3=C3</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f>A4=C4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f>A5=C5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f>A6=C6</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f>A7=C7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f>A8=C8</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f>A9=C9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f>A10=C10</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f>A11=C11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f>A12=C12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f>A13=C13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f>A14=C14</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f>A15=C15</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f>A16=C16</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f>A17=C17</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f>A18=C18</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f>A19=C19</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f>A20=C20</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f>A21=C21</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f>A22=C22</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f>A23=C23</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f>A24=C24</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f>A25=C25</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f>A26=C26</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f>A27=C27</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f>A28=C28</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
         <v/>
       </c>
       <c r="H29" s="21" t="b">
-        <f>A29=C29</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
         <v/>
       </c>
       <c r="H30" s="21" t="b">
-        <f>A30=C30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
         <v/>
       </c>
       <c r="H31" s="21" t="b">
-        <f>A31=C31</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="H32" s="21" t="b">
-        <f>A32=C32</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
         <v/>
       </c>
       <c r="H33" s="21" t="b">
-        <f>A33=C33</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v/>
       </c>
       <c r="H34" s="21" t="b">
-        <f>A34=C34</f>
+        <f t="shared" ref="H34:H65" si="1">A34=C34</f>
         <v>1</v>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v/>
       </c>
       <c r="H35" s="21" t="b">
-        <f>A35=C35</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
         <v/>
       </c>
       <c r="H36" s="21" t="b">
-        <f>A36=C36</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
         <v/>
       </c>
       <c r="H37" s="21" t="b">
-        <f>A37=C37</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         <v/>
       </c>
       <c r="H38" s="21" t="b">
-        <f>A38=C38</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="H39" s="21" t="b">
-        <f>A39=C39</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
         <v/>
       </c>
       <c r="H40" s="21" t="b">
-        <f>A40=C40</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
         <v/>
       </c>
       <c r="H41" s="21" t="b">
-        <f>A41=C41</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v/>
       </c>
       <c r="H42" s="21" t="b">
-        <f>A42=C42</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2646,14 +2646,14 @@
         <v>61</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f>A43=C43</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f>A44=C44</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f>A45=C45</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f>A46=C46</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f>A47=C47</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f>A48=C48</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f>A49=C49</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f>A50=C50</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f>A51=C51</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f>A52=C52</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f>A53=C53</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f>A54=C54</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f>A55=C55</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f>A56=C56</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
         <v/>
       </c>
       <c r="H57" s="21" t="b">
-        <f>A57=C57</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="H58" s="21" t="b">
-        <f>A58=C58</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f>A59=C59</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f>A60=C60</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f>A61=C61</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f>A62=C62</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f>A63=C63</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f>A64=C64</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f>A65=C65</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f>A66=C66</f>
+        <f t="shared" ref="H66:H97" si="2">A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f>A67=C67</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f>A68=C68</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f>A69=C69</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f>A70=C70</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
         <v/>
       </c>
       <c r="H71" s="21" t="b">
-        <f>A71=C71</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f>A72=C72</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f>A73=C73</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f>A74=C74</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f>A75=C75</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f>A76=C76</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f>A77=C77</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f>A78=C78</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f>A80=C80</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f>A81=C81</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f>A82=C82</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f>A83=C83</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f>A84=C84</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f>A85=C85</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f>A86=C86</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f>A87=C87</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f>A88=C88</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f>A89=C89</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f>A90=C90</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f>A91=C91</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f>A92=C92</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f>A93=C93</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f>A94=C94</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f>A95=C95</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f>A96=C96</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f>A97=C97</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f>A98=C98</f>
+        <f t="shared" ref="H98:H126" si="3">A98=C98</f>
         <v>1</v>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f>A99=C99</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f>A100=C100</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f>A101=C101</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f>A102=C102</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f>A103=C103</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f>A104=C104</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f>A105=C105</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
         <v/>
       </c>
       <c r="H106" s="21" t="b">
-        <f>A106=C106</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f>A107=C107</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f>A108=C108</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f>A109=C109</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f>A110=C110</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
         <v/>
       </c>
       <c r="H111" s="21" t="b">
-        <f>A111=C111</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
         <v/>
       </c>
       <c r="H112" s="21" t="b">
-        <f>A112=C112</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
         <v/>
       </c>
       <c r="H113" s="21" t="b">
-        <f>A113=C113</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="H114" s="21" t="b">
-        <f>A114=C114</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
         <v/>
       </c>
       <c r="H115" s="21" t="b">
-        <f>A115=C115</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="H116" s="21" t="b">
-        <f>A116=C116</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="H117" s="21" t="b">
-        <f>A117=C117</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
         <v/>
       </c>
       <c r="H118" s="21" t="b">
-        <f>A118=C118</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
         <v/>
       </c>
       <c r="H119" s="21" t="b">
-        <f>A119=C119</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
         <v/>
       </c>
       <c r="H120" s="21" t="b">
-        <f>A120=C120</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v/>
       </c>
       <c r="H121" s="21" t="b">
-        <f>A121=C121</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
         <v/>
       </c>
       <c r="H122" s="21" t="b">
-        <f>A122=C122</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="H123" s="21" t="b">
-        <f>A123=C123</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         <v/>
       </c>
       <c r="H124" s="21" t="b">
-        <f>A124=C124</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
         <v/>
       </c>
       <c r="H125" s="21" t="b">
-        <f>A125=C125</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="H126" s="21" t="b">
-        <f>A126=C126</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$126</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$126</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="300">
   <si>
     <t>Grupo</t>
   </si>
@@ -919,6 +919,12 @@
   </si>
   <si>
     <t>Curral</t>
+  </si>
+  <si>
+    <t>JEQUITINHONHA</t>
+  </si>
+  <si>
+    <t>21755-360</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1453,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1024"/>
+  <dimension ref="A1:H1025"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1505,7 +1511,7 @@
         <v/>
       </c>
       <c r="H2" s="21" t="b">
-        <f t="shared" ref="H2:H33" si="0">A2=C2</f>
+        <f>A2=C2</f>
         <v>1</v>
       </c>
     </row>
@@ -1533,7 +1539,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A3=C3</f>
         <v>1</v>
       </c>
     </row>
@@ -1561,7 +1567,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A4=C4</f>
         <v>1</v>
       </c>
     </row>
@@ -1589,7 +1595,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A5=C5</f>
         <v>1</v>
       </c>
     </row>
@@ -1617,7 +1623,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A6=C6</f>
         <v>1</v>
       </c>
     </row>
@@ -1645,7 +1651,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A7=C7</f>
         <v>1</v>
       </c>
     </row>
@@ -1673,7 +1679,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A8=C8</f>
         <v>1</v>
       </c>
     </row>
@@ -1701,7 +1707,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A9=C9</f>
         <v>1</v>
       </c>
     </row>
@@ -1729,7 +1735,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A10=C10</f>
         <v>1</v>
       </c>
     </row>
@@ -1757,7 +1763,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A11=C11</f>
         <v>1</v>
       </c>
     </row>
@@ -1785,7 +1791,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A12=C12</f>
         <v>1</v>
       </c>
     </row>
@@ -1813,7 +1819,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A13=C13</f>
         <v>1</v>
       </c>
     </row>
@@ -1841,7 +1847,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A14=C14</f>
         <v>1</v>
       </c>
     </row>
@@ -1869,7 +1875,7 @@
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A15=C15</f>
         <v>1</v>
       </c>
     </row>
@@ -1897,7 +1903,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A16=C16</f>
         <v>1</v>
       </c>
     </row>
@@ -1925,7 +1931,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A17=C17</f>
         <v>1</v>
       </c>
     </row>
@@ -1953,7 +1959,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A18=C18</f>
         <v>1</v>
       </c>
     </row>
@@ -1981,7 +1987,7 @@
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A19=C19</f>
         <v>1</v>
       </c>
     </row>
@@ -2009,7 +2015,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A20=C20</f>
         <v>1</v>
       </c>
     </row>
@@ -2037,7 +2043,7 @@
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A21=C21</f>
         <v>1</v>
       </c>
     </row>
@@ -2065,7 +2071,7 @@
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A22=C22</f>
         <v>1</v>
       </c>
     </row>
@@ -2093,7 +2099,7 @@
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A23=C23</f>
         <v>1</v>
       </c>
     </row>
@@ -2121,7 +2127,7 @@
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A24=C24</f>
         <v>1</v>
       </c>
     </row>
@@ -2149,7 +2155,7 @@
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A25=C25</f>
         <v>1</v>
       </c>
     </row>
@@ -2177,7 +2183,7 @@
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A26=C26</f>
         <v>1</v>
       </c>
     </row>
@@ -2205,7 +2211,7 @@
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A27=C27</f>
         <v>1</v>
       </c>
     </row>
@@ -2233,7 +2239,7 @@
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A28=C28</f>
         <v>1</v>
       </c>
     </row>
@@ -2261,7 +2267,7 @@
         <v/>
       </c>
       <c r="H29" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A29=C29</f>
         <v>1</v>
       </c>
     </row>
@@ -2270,26 +2276,26 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>51</v>
+        <v>298</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
-      <c r="D30" s="26" t="s">
-        <v>218</v>
+      <c r="D30" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>52</v>
+        <v>299</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
         <v/>
       </c>
       <c r="H30" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A30=C30</f>
         <v>1</v>
       </c>
     </row>
@@ -2298,26 +2304,26 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
         <v/>
       </c>
       <c r="H31" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A31=C31</f>
         <v>1</v>
       </c>
     </row>
@@ -2326,26 +2332,26 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
         <v/>
       </c>
       <c r="H32" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A32=C32</f>
         <v>1</v>
       </c>
     </row>
@@ -2354,26 +2360,26 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
         <v/>
       </c>
       <c r="H33" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A33=C33</f>
         <v>1</v>
       </c>
     </row>
@@ -2382,26 +2388,26 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
         <v/>
       </c>
       <c r="H34" s="21" t="b">
-        <f t="shared" ref="H34:H65" si="1">A34=C34</f>
+        <f>A34=C34</f>
         <v>1</v>
       </c>
     </row>
@@ -2410,26 +2416,26 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>250</v>
+        <v>41</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
-      <c r="D35" s="26">
-        <v>2.1</v>
+      <c r="D35" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>251</v>
+        <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>207</v>
+        <v>42</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
         <v/>
       </c>
       <c r="H35" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A35=C35</f>
         <v>1</v>
       </c>
     </row>
@@ -2438,26 +2444,26 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
-      <c r="D36" s="26" t="s">
-        <v>216</v>
+      <c r="D36" s="26">
+        <v>2.1</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>8</v>
+        <v>251</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
         <v/>
       </c>
       <c r="H36" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A36=C36</f>
         <v>1</v>
       </c>
     </row>
@@ -2466,26 +2472,26 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
         <v/>
       </c>
       <c r="H37" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A37=C37</f>
         <v>1</v>
       </c>
     </row>
@@ -2494,54 +2500,54 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>286</v>
+        <v>35</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>273</v>
+        <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
         <v/>
       </c>
       <c r="H38" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A38=C38</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="35">
-        <v>17</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="37">
-        <v>17</v>
-      </c>
-      <c r="D39" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E39" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="35" t="s">
-        <v>73</v>
+      <c r="A39" s="26">
+        <v>15</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C39" s="28">
+        <v>15</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
         <v/>
       </c>
       <c r="H39" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A39=C39</f>
         <v>1</v>
       </c>
     </row>
@@ -2550,26 +2556,26 @@
         <v>17</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>287</v>
+        <v>72</v>
       </c>
       <c r="C40" s="37">
         <v>17</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
         <v/>
       </c>
       <c r="H40" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A40=C40</f>
         <v>1</v>
       </c>
     </row>
@@ -2578,26 +2584,26 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>63</v>
+        <v>287</v>
       </c>
       <c r="C41" s="37">
         <v>17</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
         <v/>
       </c>
       <c r="H41" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A41=C41</f>
         <v>1</v>
       </c>
     </row>
@@ -2606,54 +2612,54 @@
         <v>17</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C42" s="37">
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
         <v/>
       </c>
       <c r="H42" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A42=C42</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="38">
+      <c r="A43" s="35">
         <v>17</v>
       </c>
-      <c r="B43" s="39" t="s">
-        <v>295</v>
-      </c>
-      <c r="C43" s="40">
+      <c r="B43" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="37">
         <v>17</v>
       </c>
-      <c r="D43" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E43" s="39" t="s">
+      <c r="D43" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="E43" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="38" t="s">
-        <v>114</v>
+      <c r="F43" s="35" t="s">
+        <v>62</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A43=C43</f>
         <v>1</v>
       </c>
     </row>
@@ -2662,26 +2668,26 @@
         <v>17</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>109</v>
+        <v>295</v>
       </c>
       <c r="C44" s="40">
         <v>17</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A44=C44</f>
         <v>1</v>
       </c>
     </row>
@@ -2690,54 +2696,54 @@
         <v>17</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" s="40">
         <v>17</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="E45" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A45=C45</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="35">
+      <c r="A46" s="38">
         <v>17</v>
       </c>
-      <c r="B46" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="37">
+      <c r="B46" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="40">
         <v>17</v>
       </c>
-      <c r="D46" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="E46" s="36" t="s">
+      <c r="D46" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="E46" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="35" t="s">
-        <v>54</v>
+      <c r="F46" s="38" t="s">
+        <v>108</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A46=C46</f>
         <v>1</v>
       </c>
     </row>
@@ -2746,54 +2752,54 @@
         <v>17</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C47" s="37">
         <v>17</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E47" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="38">
+      <c r="A48" s="35">
         <v>17</v>
       </c>
-      <c r="B48" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="40">
+      <c r="B48" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="37">
         <v>17</v>
       </c>
-      <c r="D48" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E48" s="39" t="s">
+      <c r="D48" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="E48" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="38" t="s">
-        <v>100</v>
+      <c r="F48" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
@@ -2802,110 +2808,110 @@
         <v>17</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C49" s="40">
         <v>17</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E49" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A49=C49</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="35">
+      <c r="A50" s="38">
         <v>17</v>
       </c>
-      <c r="B50" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="37">
+      <c r="B50" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="40">
         <v>17</v>
       </c>
-      <c r="D50" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E50" s="36" t="s">
+      <c r="D50" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E50" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="35" t="s">
-        <v>38</v>
+      <c r="F50" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A50=C50</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="38">
+      <c r="A51" s="35">
         <v>17</v>
       </c>
-      <c r="B51" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" s="40">
+      <c r="B51" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="37">
         <v>17</v>
       </c>
-      <c r="D51" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E51" s="39" t="s">
+      <c r="D51" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="38" t="s">
-        <v>86</v>
+      <c r="F51" s="35" t="s">
+        <v>38</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="35">
+      <c r="A52" s="38">
         <v>17</v>
       </c>
-      <c r="B52" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="37">
+      <c r="B52" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="40">
         <v>17</v>
       </c>
-      <c r="D52" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="E52" s="36" t="s">
+      <c r="D52" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="35" t="s">
-        <v>33</v>
+      <c r="F52" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A52=C52</f>
         <v>1</v>
       </c>
     </row>
@@ -2914,54 +2920,54 @@
         <v>17</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C53" s="37">
         <v>17</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E53" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A53=C53</f>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="32">
-        <v>20</v>
-      </c>
-      <c r="B54" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="C54" s="34">
-        <v>20</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E54" s="33" t="s">
+      <c r="A54" s="35">
+        <v>17</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="37">
+        <v>17</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="32" t="s">
-        <v>150</v>
+      <c r="F54" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
@@ -2970,26 +2976,26 @@
         <v>20</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C55" s="34">
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
@@ -2998,26 +3004,26 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
@@ -3026,26 +3032,26 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
         <v/>
       </c>
       <c r="H57" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A57=C57</f>
         <v>1</v>
       </c>
     </row>
@@ -3054,26 +3060,26 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
         <v/>
       </c>
       <c r="H58" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A58=C58</f>
         <v>1</v>
       </c>
     </row>
@@ -3082,26 +3088,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>261</v>
+        <v>141</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>262</v>
+        <v>142</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
@@ -3110,26 +3116,26 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
-      <c r="D60" s="32">
-        <v>4.2</v>
+      <c r="D60" s="32" t="s">
+        <v>230</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="32">
-        <v>21765430</v>
+      <c r="F60" s="32" t="s">
+        <v>262</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
@@ -3138,26 +3144,26 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
-      <c r="D61" s="32" t="s">
-        <v>215</v>
+      <c r="D61" s="32">
+        <v>4.2</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="32" t="s">
-        <v>140</v>
+      <c r="F61" s="32">
+        <v>21765430</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
@@ -3166,26 +3172,26 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>271</v>
+        <v>139</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
@@ -3194,26 +3200,26 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
@@ -3222,26 +3228,26 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
@@ -3250,26 +3256,26 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A65=C65</f>
         <v>1</v>
       </c>
     </row>
@@ -3278,26 +3284,26 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f t="shared" ref="H66:H97" si="2">A66=C66</f>
+        <f>A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3306,26 +3312,26 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A67=C67</f>
         <v>1</v>
       </c>
     </row>
@@ -3334,26 +3340,26 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A68=C68</f>
         <v>1</v>
       </c>
     </row>
@@ -3362,26 +3368,26 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
@@ -3390,26 +3396,26 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>264</v>
+        <v>124</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
@@ -3418,26 +3424,26 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>121</v>
+        <v>263</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>122</v>
+        <v>264</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
         <v/>
       </c>
       <c r="H71" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A71=C71</f>
         <v>1</v>
       </c>
     </row>
@@ -3446,26 +3452,26 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
@@ -3474,26 +3480,26 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3502,26 +3508,26 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
@@ -3530,26 +3536,26 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
@@ -3558,26 +3564,26 @@
         <v>20</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C76" s="34">
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E76" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F76" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A76=C76</f>
         <v>1</v>
       </c>
     </row>
@@ -3586,26 +3592,26 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A77=C77</f>
         <v>1</v>
       </c>
     </row>
@@ -3614,26 +3620,26 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
@@ -3642,26 +3648,26 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
-      <c r="D79" s="32">
-        <v>6.2</v>
+      <c r="D79" s="32" t="s">
+        <v>212</v>
       </c>
       <c r="E79" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3670,26 +3676,26 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>101</v>
+        <v>269</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
-      <c r="D80" s="32" t="s">
-        <v>220</v>
+      <c r="D80" s="32">
+        <v>6.2</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>102</v>
+        <v>270</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
@@ -3698,26 +3704,26 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A81=C81</f>
         <v>1</v>
       </c>
     </row>
@@ -3726,26 +3732,26 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A82=C82</f>
         <v>1</v>
       </c>
     </row>
@@ -3754,26 +3760,26 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E83" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A83=C83</f>
         <v>1</v>
       </c>
     </row>
@@ -3782,16 +3788,16 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>296</v>
+        <v>91</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
-      <c r="D84" s="32">
-        <v>1.8</v>
+      <c r="D84" s="32" t="s">
+        <v>228</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
         <v>92</v>
@@ -3801,7 +3807,7 @@
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A84=C84</f>
         <v>1</v>
       </c>
     </row>
@@ -3810,26 +3816,26 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
-      <c r="D85" s="32" t="s">
-        <v>227</v>
+      <c r="D85" s="32">
+        <v>1.8</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>8</v>
+        <v>297</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A85=C85</f>
         <v>1</v>
       </c>
     </row>
@@ -3838,26 +3844,26 @@
         <v>20</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C86" s="34">
         <v>20</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
@@ -3866,26 +3872,26 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A87=C87</f>
         <v>1</v>
       </c>
     </row>
@@ -3894,26 +3900,26 @@
         <v>20</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C88" s="34">
         <v>20</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F88" s="32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A88=C88</f>
         <v>1</v>
       </c>
     </row>
@@ -3922,54 +3928,54 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A89=C89</f>
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="26">
-        <v>25</v>
-      </c>
-      <c r="B90" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C90" s="28">
-        <v>25</v>
-      </c>
-      <c r="D90" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E90" s="27" t="s">
+      <c r="A90" s="32">
+        <v>20</v>
+      </c>
+      <c r="B90" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C90" s="34">
+        <v>20</v>
+      </c>
+      <c r="D90" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E90" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F90" s="26" t="s">
-        <v>184</v>
+      <c r="F90" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A90=C90</f>
         <v>1</v>
       </c>
     </row>
@@ -3978,26 +3984,26 @@
         <v>25</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C91" s="28">
         <v>25</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A91=C91</f>
         <v>1</v>
       </c>
     </row>
@@ -4006,26 +4012,26 @@
         <v>25</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C92" s="28">
         <v>25</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E92" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A92=C92</f>
         <v>1</v>
       </c>
     </row>
@@ -4034,26 +4040,26 @@
         <v>25</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C93" s="28">
         <v>25</v>
       </c>
       <c r="D93" s="26" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E93" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A93=C93</f>
         <v>1</v>
       </c>
     </row>
@@ -4062,54 +4068,54 @@
         <v>25</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C94" s="28">
         <v>25</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E94" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A94=C94</f>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="32">
+      <c r="A95" s="26">
         <v>25</v>
       </c>
-      <c r="B95" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C95" s="34">
+      <c r="B95" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C95" s="28">
         <v>25</v>
       </c>
-      <c r="D95" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F95" s="32" t="s">
-        <v>104</v>
+      <c r="D95" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A95=C95</f>
         <v>1</v>
       </c>
     </row>
@@ -4118,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C96" s="34">
         <v>25</v>
@@ -4137,35 +4143,35 @@
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A96=C96</f>
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="26">
+      <c r="A97" s="32">
         <v>25</v>
       </c>
-      <c r="B97" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C97" s="28">
+      <c r="B97" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C97" s="34">
         <v>25</v>
       </c>
-      <c r="D97" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E97" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F97" s="26" t="s">
-        <v>174</v>
+      <c r="D97" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F97" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
@@ -4174,82 +4180,82 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f t="shared" ref="H98:H126" si="3">A98=C98</f>
+        <f>A98=C98</f>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="32">
+      <c r="A99" s="26">
         <v>25</v>
       </c>
-      <c r="B99" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C99" s="34">
+      <c r="B99" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C99" s="28">
         <v>25</v>
       </c>
-      <c r="D99" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E99" s="33" t="s">
+      <c r="D99" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="E99" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F99" s="32" t="s">
-        <v>104</v>
+      <c r="F99" s="26" t="s">
+        <v>172</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A99=C99</f>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="26">
+      <c r="A100" s="32">
         <v>25</v>
       </c>
-      <c r="B100" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="C100" s="28">
+      <c r="B100" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="C100" s="34">
         <v>25</v>
       </c>
-      <c r="D100" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E100" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F100" s="26" t="s">
-        <v>170</v>
+      <c r="D100" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E100" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
@@ -4258,26 +4264,26 @@
         <v>25</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C101" s="28">
         <v>25</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E101" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
@@ -4286,26 +4292,26 @@
         <v>25</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C102" s="28">
         <v>25</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E102" s="27" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A102=C102</f>
         <v>1</v>
       </c>
     </row>
@@ -4314,26 +4320,26 @@
         <v>25</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C103" s="28">
         <v>25</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E103" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A103=C103</f>
         <v>1</v>
       </c>
     </row>
@@ -4342,26 +4348,26 @@
         <v>25</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C104" s="28">
         <v>25</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E104" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A104=C104</f>
         <v>1</v>
       </c>
     </row>
@@ -4370,26 +4376,26 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E105" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A105=C105</f>
         <v>1</v>
       </c>
     </row>
@@ -4398,26 +4404,26 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E106" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A106=C106</f>
         <v>1</v>
       </c>
     </row>
@@ -4426,26 +4432,26 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A107=C107</f>
         <v>1</v>
       </c>
     </row>
@@ -4454,26 +4460,26 @@
         <v>25</v>
       </c>
       <c r="B108" s="27" t="s">
-        <v>253</v>
+        <v>155</v>
       </c>
       <c r="C108" s="28">
         <v>25</v>
       </c>
-      <c r="D108" s="41" t="s">
-        <v>234</v>
+      <c r="D108" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="E108" s="27" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A108=C108</f>
         <v>1</v>
       </c>
     </row>
@@ -4482,54 +4488,54 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
-      <c r="D109" s="26" t="s">
-        <v>240</v>
+      <c r="D109" s="41" t="s">
+        <v>234</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A109=C109</f>
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="32">
+      <c r="A110" s="26">
         <v>25</v>
       </c>
-      <c r="B110" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="C110" s="34">
+      <c r="B110" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C110" s="28">
         <v>25</v>
       </c>
-      <c r="D110" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E110" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F110" s="32" t="s">
-        <v>104</v>
+      <c r="D110" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E110" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F110" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
@@ -4538,7 +4544,7 @@
         <v>25</v>
       </c>
       <c r="B111" s="33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C111" s="34">
         <v>25</v>
@@ -4557,7 +4563,7 @@
         <v/>
       </c>
       <c r="H111" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A111=C111</f>
         <v>1</v>
       </c>
     </row>
@@ -4566,7 +4572,7 @@
         <v>25</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C112" s="34">
         <v>25</v>
@@ -4585,119 +4591,119 @@
         <v/>
       </c>
       <c r="H112" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A112=C112</f>
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="26">
+      <c r="A113" s="32">
         <v>25</v>
       </c>
-      <c r="B113" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C113" s="28">
+      <c r="B113" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C113" s="34">
         <v>25</v>
       </c>
-      <c r="D113" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E113" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>259</v>
+      <c r="D113" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E113" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F113" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
         <v/>
       </c>
       <c r="H113" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A113=C113</f>
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="32">
+      <c r="A114" s="26">
         <v>25</v>
       </c>
-      <c r="B114" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="C114" s="34">
+      <c r="B114" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C114" s="28">
         <v>25</v>
       </c>
-      <c r="D114" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E114" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F114" s="32" t="s">
-        <v>104</v>
+      <c r="D114" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E114" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>259</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
         <v/>
       </c>
       <c r="H114" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A114=C114</f>
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="26">
+      <c r="A115" s="32">
         <v>25</v>
       </c>
-      <c r="B115" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C115" s="28">
+      <c r="B115" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="C115" s="34">
         <v>25</v>
       </c>
-      <c r="D115" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>152</v>
+      <c r="D115" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E115" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F115" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
         <v/>
       </c>
       <c r="H115" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A115=C115</f>
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="32">
-        <v>30</v>
-      </c>
-      <c r="B116" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="C116" s="34">
-        <v>30</v>
-      </c>
-      <c r="D116" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="E116" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="F116" s="32" t="s">
-        <v>198</v>
+      <c r="A116" s="26">
+        <v>25</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C116" s="28">
+        <v>25</v>
+      </c>
+      <c r="D116" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>152</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
         <v/>
       </c>
       <c r="H116" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A116=C116</f>
         <v>1</v>
       </c>
     </row>
@@ -4706,26 +4712,26 @@
         <v>30</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C117" s="34">
         <v>30</v>
       </c>
       <c r="D117" s="32" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E117" s="33" t="s">
         <v>134</v>
       </c>
       <c r="F117" s="32" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
         <v/>
       </c>
       <c r="H117" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A117=C117</f>
         <v>1</v>
       </c>
     </row>
@@ -4734,13 +4740,13 @@
         <v>30</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C118" s="34">
         <v>30</v>
       </c>
       <c r="D118" s="32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E118" s="33" t="s">
         <v>134</v>
@@ -4753,7 +4759,7 @@
         <v/>
       </c>
       <c r="H118" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A118=C118</f>
         <v>1</v>
       </c>
     </row>
@@ -4762,26 +4768,26 @@
         <v>30</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="C119" s="34">
         <v>30</v>
       </c>
       <c r="D119" s="32" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="F119" s="32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
         <v/>
       </c>
       <c r="H119" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A119=C119</f>
         <v>1</v>
       </c>
     </row>
@@ -4790,26 +4796,26 @@
         <v>30</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="C120" s="34">
         <v>30</v>
       </c>
       <c r="D120" s="32" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E120" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F120" s="32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
         <v/>
       </c>
       <c r="H120" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A120=C120</f>
         <v>1</v>
       </c>
     </row>
@@ -4818,26 +4824,26 @@
         <v>30</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C121" s="34">
         <v>30</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E121" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F121" s="32" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H121" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A121=C121</f>
         <v>1</v>
       </c>
     </row>
@@ -4846,26 +4852,26 @@
         <v>30</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C122" s="34">
         <v>30</v>
       </c>
       <c r="D122" s="32" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E122" s="33" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F122" s="32" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A122=C122</f>
         <v>1</v>
       </c>
     </row>
@@ -4874,54 +4880,54 @@
         <v>30</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C123" s="34">
         <v>30</v>
       </c>
       <c r="D123" s="32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E123" s="33" t="s">
         <v>134</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
         <v/>
       </c>
       <c r="H123" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A123=C123</f>
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="26">
-        <v>40</v>
-      </c>
-      <c r="B124" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="C124" s="28">
-        <v>40</v>
-      </c>
-      <c r="D124" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E124" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F124" s="26" t="s">
-        <v>204</v>
+      <c r="A124" s="32">
+        <v>30</v>
+      </c>
+      <c r="B124" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C124" s="34">
+        <v>30</v>
+      </c>
+      <c r="D124" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E124" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F124" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
         <v/>
       </c>
       <c r="H124" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A124=C124</f>
         <v>1</v>
       </c>
     </row>
@@ -4930,26 +4936,26 @@
         <v>40</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C125" s="28">
         <v>40</v>
       </c>
       <c r="D125" s="26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
         <v/>
       </c>
       <c r="H125" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A125=C125</f>
         <v>1</v>
       </c>
     </row>
@@ -4958,37 +4964,56 @@
         <v>40</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="C126" s="28">
         <v>40</v>
       </c>
-      <c r="D126" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D126" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
         <v/>
       </c>
       <c r="H126" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A126=C126</f>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="30"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="30"/>
-      <c r="D127" s="30"/>
-      <c r="E127" s="31"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="31"/>
+      <c r="A127" s="26">
+        <v>40</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" s="28">
+        <v>40</v>
+      </c>
+      <c r="D127" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="F127" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G127" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H127" s="21" t="b">
+        <f>A127=C127</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A128" s="30"/>
@@ -5099,10 +5124,13 @@
       <c r="G139" s="31"/>
     </row>
     <row r="140" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="F140" s="1"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="31"/>
+      <c r="F140" s="30"/>
+      <c r="G140" s="31"/>
     </row>
     <row r="141" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
@@ -10408,12 +10436,18 @@
       <c r="D1024" s="1"/>
       <c r="F1024" s="1"/>
     </row>
+    <row r="1025" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1025" s="1"/>
+      <c r="C1025" s="1"/>
+      <c r="D1025" s="1"/>
+      <c r="F1025" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H126">
-    <sortState ref="A2:H126">
-      <sortCondition ref="A2:A126"/>
-      <sortCondition ref="B2:B126"/>
-      <sortCondition ref="D2:D126"/>
+  <autoFilter ref="A1:H127">
+    <sortState ref="A2:H127">
+      <sortCondition ref="A2:A127"/>
+      <sortCondition ref="B2:B127"/>
+      <sortCondition ref="D2:D127"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H102">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="303">
   <si>
     <t>Grupo</t>
   </si>
@@ -925,6 +925,15 @@
   </si>
   <si>
     <t>21755-360</t>
+  </si>
+  <si>
+    <t>MARECHAL HERMES</t>
+  </si>
+  <si>
+    <t>Marechal Hermes</t>
+  </si>
+  <si>
+    <t>21331-020</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1468,7 @@
     <col min="1" max="1" width="5.453125" customWidth="1"/>
     <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
@@ -5016,13 +5025,32 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="30"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="30"/>
-      <c r="D128" s="30"/>
-      <c r="E128" s="31"/>
-      <c r="F128" s="30"/>
-      <c r="G128" s="31"/>
+      <c r="A128" s="26">
+        <v>45</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C128" s="28">
+        <v>45</v>
+      </c>
+      <c r="D128" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="G128" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H128" s="21" t="b">
+        <f>A128=C128</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="129" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A129" s="30"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="310">
   <si>
     <t>Grupo</t>
   </si>
@@ -348,9 +348,6 @@
     <t>21735-010</t>
   </si>
   <si>
-    <t>LIMITE</t>
-  </si>
-  <si>
     <t>21750-120</t>
   </si>
   <si>
@@ -934,6 +931,30 @@
   </si>
   <si>
     <t>21331-020</t>
+  </si>
+  <si>
+    <t>JUSTINO ARAUJO</t>
+  </si>
+  <si>
+    <t>21775-800</t>
+  </si>
+  <si>
+    <t>Limites - Padre Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO MELLO </t>
+  </si>
+  <si>
+    <t>21775-410</t>
+  </si>
+  <si>
+    <t>LUISA BARATA</t>
+  </si>
+  <si>
+    <t>LIMITES</t>
+  </si>
+  <si>
+    <t>Limites  - Realengo</t>
   </si>
 </sst>
 </file>
@@ -1493,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1501,7 +1522,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C2" s="34">
         <v>13</v>
@@ -1510,7 +1531,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F2" s="32" t="s">
         <v>26</v>
@@ -1548,7 +1569,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f>A3=C3</f>
+        <f t="shared" ref="H3:H66" si="0">A3=C3</f>
         <v>1</v>
       </c>
     </row>
@@ -1557,7 +1578,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C4" s="34">
         <v>13</v>
@@ -1566,7 +1587,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>26</v>
@@ -1576,7 +1597,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f>A4=C4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1585,7 +1606,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C5" s="34">
         <v>13</v>
@@ -1594,7 +1615,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>26</v>
@@ -1604,7 +1625,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f>A5=C5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1632,7 +1653,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f>A6=C6</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1641,7 +1662,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="34">
         <v>13</v>
@@ -1650,7 +1671,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F7" s="32" t="s">
         <v>26</v>
@@ -1660,7 +1681,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f>A7=C7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1669,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C8" s="34">
         <v>13</v>
@@ -1678,7 +1699,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>26</v>
@@ -1688,7 +1709,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f>A8=C8</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1716,7 +1737,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f>A9=C9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1725,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10" s="34">
         <v>13</v>
@@ -1734,7 +1755,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F10" s="32" t="s">
         <v>26</v>
@@ -1744,7 +1765,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f>A10=C10</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1759,7 +1780,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>8</v>
@@ -1772,7 +1793,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f>A11=C11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1781,7 +1802,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C12" s="34">
         <v>13</v>
@@ -1790,7 +1811,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>26</v>
@@ -1800,7 +1821,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f>A12=C12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1828,7 +1849,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f>A13=C13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1837,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C14" s="34">
         <v>13</v>
@@ -1846,7 +1867,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>26</v>
@@ -1856,7 +1877,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f>A14=C14</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1884,7 +1905,7 @@
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f>A15=C15</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1912,7 +1933,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f>A16=C16</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1940,7 +1961,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f>A17=C17</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1955,7 +1976,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>8</v>
@@ -1968,7 +1989,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f>A18=C18</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1983,7 +2004,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>8</v>
@@ -1996,7 +2017,7 @@
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f>A19=C19</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2011,7 +2032,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
@@ -2024,7 +2045,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f>A20=C20</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2039,7 +2060,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
@@ -2052,7 +2073,7 @@
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f>A21=C21</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2067,7 +2088,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
@@ -2080,7 +2101,7 @@
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f>A22=C22</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2089,16 +2110,16 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>66</v>
@@ -2108,7 +2129,7 @@
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f>A23=C23</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2117,7 +2138,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
@@ -2129,14 +2150,14 @@
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f>A24=C24</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2151,7 +2172,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
@@ -2164,7 +2185,7 @@
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f>A25=C25</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2173,13 +2194,13 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
@@ -2192,7 +2213,7 @@
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f>A26=C26</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2207,7 +2228,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>8</v>
@@ -2220,7 +2241,7 @@
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f>A27=C27</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2229,13 +2250,13 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
@@ -2248,7 +2269,7 @@
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f>A28=C28</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2257,7 +2278,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
@@ -2269,14 +2290,14 @@
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
         <v/>
       </c>
       <c r="H29" s="21" t="b">
-        <f>A29=C29</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2285,7 +2306,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
@@ -2297,14 +2318,14 @@
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
         <v/>
       </c>
       <c r="H30" s="21" t="b">
-        <f>A30=C30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2319,7 +2340,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
@@ -2332,7 +2353,7 @@
         <v/>
       </c>
       <c r="H31" s="21" t="b">
-        <f>A31=C31</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2347,7 +2368,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
@@ -2360,7 +2381,7 @@
         <v/>
       </c>
       <c r="H32" s="21" t="b">
-        <f>A32=C32</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2375,7 +2396,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
@@ -2388,7 +2409,7 @@
         <v/>
       </c>
       <c r="H33" s="21" t="b">
-        <f>A33=C33</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2403,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
@@ -2416,7 +2437,7 @@
         <v/>
       </c>
       <c r="H34" s="21" t="b">
-        <f>A34=C34</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2431,7 +2452,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
@@ -2444,7 +2465,7 @@
         <v/>
       </c>
       <c r="H35" s="21" t="b">
-        <f>A35=C35</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2453,7 +2474,7 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
@@ -2462,17 +2483,17 @@
         <v>2.1</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
         <v/>
       </c>
       <c r="H36" s="21" t="b">
-        <f>A36=C36</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2487,7 +2508,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
@@ -2500,7 +2521,7 @@
         <v/>
       </c>
       <c r="H37" s="21" t="b">
-        <f>A37=C37</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2515,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
@@ -2528,7 +2549,7 @@
         <v/>
       </c>
       <c r="H38" s="21" t="b">
-        <f>A38=C38</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2537,16 +2558,16 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F39" s="26" t="s">
         <v>34</v>
@@ -2556,7 +2577,7 @@
         <v/>
       </c>
       <c r="H39" s="21" t="b">
-        <f>A39=C39</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2571,7 +2592,7 @@
         <v>17</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E40" s="36" t="s">
         <v>8</v>
@@ -2584,7 +2605,7 @@
         <v/>
       </c>
       <c r="H40" s="21" t="b">
-        <f>A40=C40</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2593,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C41" s="37">
         <v>17</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E41" s="36" t="s">
         <v>61</v>
@@ -2612,7 +2633,7 @@
         <v/>
       </c>
       <c r="H41" s="21" t="b">
-        <f>A41=C41</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2627,7 +2648,7 @@
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>8</v>
@@ -2640,7 +2661,7 @@
         <v/>
       </c>
       <c r="H42" s="21" t="b">
-        <f>A42=C42</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2655,7 +2676,7 @@
         <v>17</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E43" s="36" t="s">
         <v>61</v>
@@ -2668,7 +2689,7 @@
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f>A43=C43</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2677,26 +2698,26 @@
         <v>17</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C44" s="40">
         <v>17</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E44" s="39" t="s">
         <v>61</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f>A44=C44</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2705,26 +2726,26 @@
         <v>17</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C45" s="40">
         <v>17</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E45" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f>A45=C45</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2733,26 +2754,26 @@
         <v>17</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>107</v>
+        <v>308</v>
       </c>
       <c r="C46" s="40">
         <v>17</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f>A46=C46</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2767,7 +2788,7 @@
         <v>17</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E47" s="36" t="s">
         <v>8</v>
@@ -2780,7 +2801,7 @@
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f>A47=C47</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2795,7 +2816,7 @@
         <v>17</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E48" s="36" t="s">
         <v>8</v>
@@ -2808,7 +2829,7 @@
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f>A48=C48</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2823,7 +2844,7 @@
         <v>17</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E49" s="39" t="s">
         <v>8</v>
@@ -2836,7 +2857,7 @@
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f>A49=C49</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2851,7 +2872,7 @@
         <v>17</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E50" s="39" t="s">
         <v>8</v>
@@ -2864,7 +2885,7 @@
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f>A50=C50</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2879,7 +2900,7 @@
         <v>17</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E51" s="36" t="s">
         <v>8</v>
@@ -2892,7 +2913,7 @@
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f>A51=C51</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2907,7 +2928,7 @@
         <v>17</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E52" s="39" t="s">
         <v>8</v>
@@ -2920,7 +2941,7 @@
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f>A52=C52</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2935,7 +2956,7 @@
         <v>17</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E53" s="36" t="s">
         <v>8</v>
@@ -2948,7 +2969,7 @@
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f>A53=C53</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2963,7 +2984,7 @@
         <v>17</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E54" s="36" t="s">
         <v>8</v>
@@ -2976,7 +2997,7 @@
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f>A54=C54</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2985,26 +3006,26 @@
         <v>20</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C55" s="34">
         <v>20</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f>A55=C55</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3013,26 +3034,26 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f>A56=C56</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3041,26 +3062,26 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
         <v/>
       </c>
       <c r="H57" s="21" t="b">
-        <f>A57=C57</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3069,26 +3090,26 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
         <v/>
       </c>
       <c r="H58" s="21" t="b">
-        <f>A58=C58</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3097,26 +3118,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f>A59=C59</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3125,26 +3146,26 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f>A60=C60</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3153,7 +3174,7 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
@@ -3172,7 +3193,7 @@
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f>A61=C61</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3181,26 +3202,26 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f>A62=C62</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3209,26 +3230,26 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f>A63=C63</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3237,26 +3258,26 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f>A64=C64</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3265,26 +3286,26 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E65" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="F65" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f>A65=C65</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3293,26 +3314,26 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f>A66=C66</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3321,26 +3342,26 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f>A67=C67</f>
+        <f t="shared" ref="H67:H130" si="1">A67=C67</f>
         <v>1</v>
       </c>
     </row>
@@ -3349,26 +3370,26 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f>A68=C68</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3377,26 +3398,26 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f>A69=C69</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3405,26 +3426,26 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f>A70=C70</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3433,26 +3454,26 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
         <v/>
       </c>
       <c r="H71" s="21" t="b">
-        <f>A71=C71</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3461,26 +3482,26 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f>A72=C72</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3489,26 +3510,26 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f>A73=C73</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3517,54 +3538,54 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f>A74=C74</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="32">
+      <c r="A75" s="26">
         <v>20</v>
       </c>
-      <c r="B75" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="C75" s="34">
+      <c r="B75" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C75" s="28">
         <v>20</v>
       </c>
-      <c r="D75" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E75" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="32" t="s">
-        <v>116</v>
+      <c r="D75" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F75" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f>A75=C75</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3573,26 +3594,26 @@
         <v>20</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C76" s="34">
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E76" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F76" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f>A76=C76</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3601,26 +3622,26 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f>A77=C77</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3629,54 +3650,54 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f>A78=C78</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="32">
+      <c r="A79" s="26">
         <v>20</v>
       </c>
-      <c r="B79" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C79" s="34">
+      <c r="B79" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="C79" s="28">
         <v>20</v>
       </c>
-      <c r="D79" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E79" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="32" t="s">
-        <v>104</v>
+      <c r="D79" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F79" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3685,26 +3706,26 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>269</v>
+        <v>105</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
-      <c r="D80" s="32">
-        <v>6.2</v>
+      <c r="D80" s="32" t="s">
+        <v>218</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>270</v>
+        <v>106</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f>A80=C80</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3713,26 +3734,26 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f>A81=C81</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3741,26 +3762,26 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
-      <c r="D82" s="32" t="s">
-        <v>221</v>
+      <c r="D82" s="32">
+        <v>6.2</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f>A82=C82</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3769,54 +3790,54 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f>A83=C83</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="32">
+      <c r="A84" s="26">
         <v>20</v>
       </c>
-      <c r="B84" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C84" s="34">
+      <c r="B84" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C84" s="28">
         <v>20</v>
       </c>
-      <c r="D84" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="E84" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="32" t="s">
-        <v>92</v>
+      <c r="D84" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E84" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F84" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f>A84=C84</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3825,26 +3846,26 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>296</v>
+        <v>97</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
-      <c r="D85" s="32">
-        <v>1.8</v>
+      <c r="D85" s="32" t="s">
+        <v>220</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f>A85=C85</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3853,26 +3874,26 @@
         <v>20</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C86" s="34">
         <v>20</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="32" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f>A86=C86</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3881,26 +3902,26 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f>A87=C87</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3909,26 +3930,26 @@
         <v>20</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="C88" s="34">
         <v>20</v>
       </c>
-      <c r="D88" s="32" t="s">
-        <v>223</v>
+      <c r="D88" s="32">
+        <v>1.8</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="F88" s="32" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f>A88=C88</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3937,26 +3958,26 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f>A89=C89</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3965,110 +3986,110 @@
         <v>20</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C90" s="34">
         <v>20</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E90" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="32" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f>A90=C90</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="26">
-        <v>25</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C91" s="28">
-        <v>25</v>
-      </c>
-      <c r="D91" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E91" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="26" t="s">
-        <v>184</v>
+      <c r="A91" s="32">
+        <v>20</v>
+      </c>
+      <c r="B91" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91" s="34">
+        <v>20</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E91" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F91" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f>A91=C91</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="26">
-        <v>25</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C92" s="28">
-        <v>25</v>
-      </c>
-      <c r="D92" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E92" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F92" s="26" t="s">
-        <v>182</v>
+      <c r="A92" s="32">
+        <v>20</v>
+      </c>
+      <c r="B92" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C92" s="34">
+        <v>20</v>
+      </c>
+      <c r="D92" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E92" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f>A92=C92</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="26">
-        <v>25</v>
-      </c>
-      <c r="B93" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C93" s="28">
-        <v>25</v>
-      </c>
-      <c r="D93" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>180</v>
+      <c r="A93" s="32">
+        <v>20</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C93" s="34">
+        <v>20</v>
+      </c>
+      <c r="D93" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E93" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f>A93=C93</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4077,7 +4098,7 @@
         <v>25</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C94" s="28">
         <v>25</v>
@@ -4086,17 +4107,17 @@
         <v>229</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f>A94=C94</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4105,7 +4126,7 @@
         <v>25</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C95" s="28">
         <v>25</v>
@@ -4114,73 +4135,73 @@
         <v>242</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f>A95=C95</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="32">
+      <c r="A96" s="26">
         <v>25</v>
       </c>
-      <c r="B96" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C96" s="34">
+      <c r="B96" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C96" s="28">
         <v>25</v>
       </c>
-      <c r="D96" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E96" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F96" s="32" t="s">
-        <v>104</v>
+      <c r="D96" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>179</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f>A96=C96</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="32">
+      <c r="A97" s="26">
         <v>25</v>
       </c>
-      <c r="B97" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C97" s="34">
+      <c r="B97" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C97" s="28">
         <v>25</v>
       </c>
-      <c r="D97" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E97" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F97" s="32" t="s">
-        <v>104</v>
+      <c r="D97" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f>A97=C97</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4189,54 +4210,54 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f>A98=C98</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="26">
+      <c r="A99" s="32">
         <v>25</v>
       </c>
-      <c r="B99" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="C99" s="28">
+      <c r="B99" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="C99" s="34">
         <v>25</v>
       </c>
-      <c r="D99" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>172</v>
+      <c r="D99" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f>A99=C99</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4245,16 +4266,16 @@
         <v>25</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C100" s="34">
         <v>25</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E100" s="33" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
       <c r="F100" s="32" t="s">
         <v>104</v>
@@ -4264,7 +4285,7 @@
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f>A100=C100</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4273,26 +4294,26 @@
         <v>25</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C101" s="28">
         <v>25</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E101" s="27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f>A101=C101</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4301,54 +4322,54 @@
         <v>25</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C102" s="28">
         <v>25</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E102" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f>A102=C102</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="26">
+      <c r="A103" s="32">
         <v>25</v>
       </c>
-      <c r="B103" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="C103" s="28">
+      <c r="B103" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="C103" s="34">
         <v>25</v>
       </c>
-      <c r="D103" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E103" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F103" s="26" t="s">
-        <v>166</v>
+      <c r="D103" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f>A103=C103</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4357,26 +4378,26 @@
         <v>25</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C104" s="28">
         <v>25</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E104" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f>A104=C104</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4385,7 +4406,7 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
@@ -4394,17 +4415,17 @@
         <v>233</v>
       </c>
       <c r="E105" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f>A105=C105</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4413,26 +4434,26 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E106" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
-        <f>A106=C106</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4441,26 +4462,26 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f>A107=C107</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4469,26 +4490,26 @@
         <v>25</v>
       </c>
       <c r="B108" s="27" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C108" s="28">
         <v>25</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E108" s="27" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f>A108=C108</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4497,26 +4518,26 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>253</v>
+        <v>158</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
-      <c r="D109" s="41" t="s">
-        <v>234</v>
+      <c r="D109" s="26" t="s">
+        <v>231</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f>A109=C109</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4525,138 +4546,138 @@
         <v>25</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C110" s="28">
         <v>25</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E110" s="27" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f>A110=C110</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="32">
+      <c r="A111" s="26">
         <v>25</v>
       </c>
-      <c r="B111" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="C111" s="34">
+      <c r="B111" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="28">
         <v>25</v>
       </c>
-      <c r="D111" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E111" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F111" s="32" t="s">
-        <v>104</v>
+      <c r="D111" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E111" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
         <v/>
       </c>
       <c r="H111" s="21" t="b">
-        <f>A111=C111</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="32">
+      <c r="A112" s="26">
         <v>25</v>
       </c>
-      <c r="B112" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C112" s="34">
+      <c r="B112" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C112" s="28">
         <v>25</v>
       </c>
-      <c r="D112" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E112" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F112" s="32" t="s">
-        <v>104</v>
+      <c r="D112" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E112" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
         <v/>
       </c>
       <c r="H112" s="21" t="b">
-        <f>A112=C112</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="32">
+      <c r="A113" s="26">
         <v>25</v>
       </c>
-      <c r="B113" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="C113" s="34">
+      <c r="B113" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113" s="28">
         <v>25</v>
       </c>
-      <c r="D113" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E113" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F113" s="32" t="s">
-        <v>104</v>
+      <c r="D113" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E113" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
         <v/>
       </c>
       <c r="H113" s="21" t="b">
-        <f>A113=C113</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="26">
+      <c r="A114" s="32">
         <v>25</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C114" s="28">
+      <c r="B114" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C114" s="34">
         <v>25</v>
       </c>
-      <c r="D114" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>259</v>
+      <c r="D114" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E114" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F114" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
         <v/>
       </c>
       <c r="H114" s="21" t="b">
-        <f>A114=C114</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4671,10 +4692,10 @@
         <v>25</v>
       </c>
       <c r="D115" s="32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F115" s="32" t="s">
         <v>104</v>
@@ -4684,119 +4705,119 @@
         <v/>
       </c>
       <c r="H115" s="21" t="b">
-        <f>A115=C115</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="26">
+      <c r="A116" s="32">
         <v>25</v>
       </c>
-      <c r="B116" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C116" s="28">
+      <c r="B116" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C116" s="34">
         <v>25</v>
       </c>
-      <c r="D116" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>152</v>
+      <c r="D116" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E116" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F116" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
         <v/>
       </c>
       <c r="H116" s="21" t="b">
-        <f>A116=C116</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="32">
-        <v>30</v>
-      </c>
-      <c r="B117" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="C117" s="34">
-        <v>30</v>
-      </c>
-      <c r="D117" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="E117" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="F117" s="32" t="s">
-        <v>198</v>
+      <c r="A117" s="26">
+        <v>25</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C117" s="28">
+        <v>25</v>
+      </c>
+      <c r="D117" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>258</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
         <v/>
       </c>
       <c r="H117" s="21" t="b">
-        <f>A117=C117</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A118" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="C118" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D118" s="32" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="E118" s="33" t="s">
-        <v>134</v>
+        <v>288</v>
       </c>
       <c r="F118" s="32" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
         <v/>
       </c>
       <c r="H118" s="21" t="b">
-        <f>A118=C118</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="32">
-        <v>30</v>
-      </c>
-      <c r="B119" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C119" s="34">
-        <v>30</v>
-      </c>
-      <c r="D119" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="E119" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="F119" s="32" t="s">
-        <v>195</v>
+      <c r="A119" s="26">
+        <v>25</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C119" s="28">
+        <v>25</v>
+      </c>
+      <c r="D119" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E119" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
         <v/>
       </c>
       <c r="H119" s="21" t="b">
-        <f>A119=C119</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4805,26 +4826,26 @@
         <v>30</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="C120" s="34">
         <v>30</v>
       </c>
       <c r="D120" s="32" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F120" s="32" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
         <v/>
       </c>
       <c r="H120" s="21" t="b">
-        <f>A120=C120</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4833,26 +4854,26 @@
         <v>30</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C121" s="34">
         <v>30</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E121" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F121" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H121" s="21" t="b">
-        <f>A121=C121</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4861,26 +4882,26 @@
         <v>30</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C122" s="34">
         <v>30</v>
       </c>
       <c r="D122" s="32" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E122" s="33" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F122" s="32" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
-        <f>A122=C122</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4889,26 +4910,26 @@
         <v>30</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="C123" s="34">
         <v>30</v>
       </c>
       <c r="D123" s="32" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="E123" s="33" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
         <v/>
       </c>
       <c r="H123" s="21" t="b">
-        <f>A123=C123</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4917,169 +4938,226 @@
         <v>30</v>
       </c>
       <c r="B124" s="33" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C124" s="34">
         <v>30</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E124" s="33" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
         <v/>
       </c>
       <c r="H124" s="21" t="b">
-        <f>A124=C124</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="26">
-        <v>40</v>
-      </c>
-      <c r="B125" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="C125" s="28">
-        <v>40</v>
-      </c>
-      <c r="D125" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E125" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F125" s="26" t="s">
-        <v>204</v>
+      <c r="A125" s="32">
+        <v>30</v>
+      </c>
+      <c r="B125" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C125" s="34">
+        <v>30</v>
+      </c>
+      <c r="D125" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E125" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F125" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
         <v/>
       </c>
       <c r="H125" s="21" t="b">
-        <f>A125=C125</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="26">
-        <v>40</v>
-      </c>
-      <c r="B126" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C126" s="28">
-        <v>40</v>
-      </c>
-      <c r="D126" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>201</v>
+      <c r="A126" s="32">
+        <v>30</v>
+      </c>
+      <c r="B126" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C126" s="34">
+        <v>30</v>
+      </c>
+      <c r="D126" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E126" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F126" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
         <v/>
       </c>
       <c r="H126" s="21" t="b">
-        <f>A126=C126</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="26">
-        <v>40</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C127" s="28">
-        <v>40</v>
-      </c>
-      <c r="D127" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>257</v>
+      <c r="A127" s="32">
+        <v>30</v>
+      </c>
+      <c r="B127" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C127" s="34">
+        <v>30</v>
+      </c>
+      <c r="D127" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F127" s="32" t="s">
+        <v>185</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
         <v/>
       </c>
       <c r="H127" s="21" t="b">
-        <f>A127=C127</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A128" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="C128" s="28">
-        <v>45</v>
-      </c>
-      <c r="D128" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D128" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="E128" s="27" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>302</v>
+        <v>203</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
-        <f>A128=C128</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="30"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="30"/>
-      <c r="D129" s="30"/>
-      <c r="E129" s="31"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="31"/>
-    </row>
-    <row r="130" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="30"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="30"/>
-      <c r="D130" s="30"/>
-      <c r="E130" s="31"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="31"/>
-    </row>
-    <row r="131" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="30"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="30"/>
-      <c r="D131" s="30"/>
-      <c r="E131" s="31"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="31"/>
-    </row>
-    <row r="132" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="26">
+        <v>40</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C129" s="28">
+        <v>40</v>
+      </c>
+      <c r="D129" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E129" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F129" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="G129" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H129" s="21" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="26">
+        <v>40</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C130" s="28">
+        <v>40</v>
+      </c>
+      <c r="D130" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E130" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="F130" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="G130" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H130" s="21" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="26">
+        <v>45</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C131" s="28">
+        <v>45</v>
+      </c>
+      <c r="D131" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E131" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F131" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="G131" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H131" s="21" t="b">
+        <f t="shared" ref="H131" si="2">A131=C131</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="30"/>
       <c r="B132" s="31"/>
       <c r="C132" s="30"/>
@@ -5088,7 +5166,7 @@
       <c r="F132" s="30"/>
       <c r="G132" s="31"/>
     </row>
-    <row r="133" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="30"/>
       <c r="B133" s="31"/>
       <c r="C133" s="30"/>
@@ -5097,7 +5175,7 @@
       <c r="F133" s="30"/>
       <c r="G133" s="31"/>
     </row>
-    <row r="134" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="30"/>
       <c r="B134" s="31"/>
       <c r="C134" s="30"/>
@@ -5106,7 +5184,7 @@
       <c r="F134" s="30"/>
       <c r="G134" s="31"/>
     </row>
-    <row r="135" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A135" s="30"/>
       <c r="B135" s="31"/>
       <c r="C135" s="30"/>
@@ -5115,7 +5193,7 @@
       <c r="F135" s="30"/>
       <c r="G135" s="31"/>
     </row>
-    <row r="136" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A136" s="30"/>
       <c r="B136" s="31"/>
       <c r="C136" s="30"/>
@@ -5124,7 +5202,7 @@
       <c r="F136" s="30"/>
       <c r="G136" s="31"/>
     </row>
-    <row r="137" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A137" s="30"/>
       <c r="B137" s="31"/>
       <c r="C137" s="30"/>
@@ -5133,7 +5211,7 @@
       <c r="F137" s="30"/>
       <c r="G137" s="31"/>
     </row>
-    <row r="138" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A138" s="30"/>
       <c r="B138" s="31"/>
       <c r="C138" s="30"/>
@@ -5142,7 +5220,7 @@
       <c r="F138" s="30"/>
       <c r="G138" s="31"/>
     </row>
-    <row r="139" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A139" s="30"/>
       <c r="B139" s="31"/>
       <c r="C139" s="30"/>
@@ -5151,7 +5229,7 @@
       <c r="F139" s="30"/>
       <c r="G139" s="31"/>
     </row>
-    <row r="140" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="30"/>
       <c r="B140" s="31"/>
       <c r="C140" s="30"/>
@@ -5160,25 +5238,25 @@
       <c r="F140" s="30"/>
       <c r="G140" s="31"/>
     </row>
-    <row r="141" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="F141" s="1"/>
     </row>
-    <row r="142" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="F142" s="1"/>
     </row>
-    <row r="143" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="F143" s="1"/>
     </row>
-    <row r="144" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -10478,10 +10556,10 @@
       <sortCondition ref="D2:D127"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H102">
-    <sortCondition ref="A2:A102"/>
-    <sortCondition ref="B2:B102"/>
-    <sortCondition ref="D2:D102"/>
+  <sortState ref="A2:H131">
+    <sortCondition ref="A2:A131"/>
+    <sortCondition ref="B2:B131"/>
+    <sortCondition ref="D2:D131"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10505,7 +10583,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -10518,7 +10596,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$131</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$126</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="311">
   <si>
     <t>Grupo</t>
   </si>
@@ -955,6 +955,9 @@
   </si>
   <si>
     <t>Limites  - Realengo</t>
+  </si>
+  <si>
+    <t>Limites - Realengo</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +1982,7 @@
         <v>214</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>77</v>
@@ -3099,7 +3102,7 @@
         <v>220</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F58" s="32" t="s">
         <v>143</v>
@@ -3183,7 +3186,7 @@
         <v>4.2</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F61" s="32">
         <v>21765430</v>
@@ -3267,7 +3270,7 @@
         <v>223</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F64" s="32" t="s">
         <v>136</v>
@@ -3351,7 +3354,7 @@
         <v>238</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F67" s="32" t="s">
         <v>129</v>
@@ -3435,7 +3438,7 @@
         <v>227</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F70" s="32" t="s">
         <v>123</v>
@@ -10549,7 +10552,7 @@
       <c r="F1025" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H127">
+  <autoFilter ref="A1:H131">
     <sortState ref="A2:H127">
       <sortCondition ref="A2:A127"/>
       <sortCondition ref="B2:B127"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="313">
   <si>
     <t>Grupo</t>
   </si>
@@ -958,6 +958,12 @@
   </si>
   <si>
     <t>Limites - Realengo</t>
+  </si>
+  <si>
+    <t>GENERAL ZESEFREDO</t>
+  </si>
+  <si>
+    <t>21715-062</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1578,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f t="shared" ref="H3:H66" si="0">A3=C3</f>
+        <f>A3=C3</f>
         <v>1</v>
       </c>
     </row>
@@ -1600,7 +1606,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A4=C4</f>
         <v>1</v>
       </c>
     </row>
@@ -1628,7 +1634,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A5=C5</f>
         <v>1</v>
       </c>
     </row>
@@ -1656,7 +1662,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A6=C6</f>
         <v>1</v>
       </c>
     </row>
@@ -1684,7 +1690,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A7=C7</f>
         <v>1</v>
       </c>
     </row>
@@ -1712,7 +1718,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A8=C8</f>
         <v>1</v>
       </c>
     </row>
@@ -1740,7 +1746,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A9=C9</f>
         <v>1</v>
       </c>
     </row>
@@ -1768,7 +1774,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A10=C10</f>
         <v>1</v>
       </c>
     </row>
@@ -1796,7 +1802,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A11=C11</f>
         <v>1</v>
       </c>
     </row>
@@ -1824,7 +1830,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A12=C12</f>
         <v>1</v>
       </c>
     </row>
@@ -1852,7 +1858,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A13=C13</f>
         <v>1</v>
       </c>
     </row>
@@ -1880,7 +1886,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A14=C14</f>
         <v>1</v>
       </c>
     </row>
@@ -1908,7 +1914,7 @@
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A15=C15</f>
         <v>1</v>
       </c>
     </row>
@@ -1936,7 +1942,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A16=C16</f>
         <v>1</v>
       </c>
     </row>
@@ -1964,7 +1970,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A17=C17</f>
         <v>1</v>
       </c>
     </row>
@@ -1992,7 +1998,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A18=C18</f>
         <v>1</v>
       </c>
     </row>
@@ -2020,7 +2026,7 @@
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A19=C19</f>
         <v>1</v>
       </c>
     </row>
@@ -2048,7 +2054,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A20=C20</f>
         <v>1</v>
       </c>
     </row>
@@ -2076,7 +2082,7 @@
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A21=C21</f>
         <v>1</v>
       </c>
     </row>
@@ -2104,7 +2110,7 @@
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A22=C22</f>
         <v>1</v>
       </c>
     </row>
@@ -2132,7 +2138,7 @@
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A23=C23</f>
         <v>1</v>
       </c>
     </row>
@@ -2160,7 +2166,7 @@
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A24=C24</f>
         <v>1</v>
       </c>
     </row>
@@ -2188,7 +2194,7 @@
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A25=C25</f>
         <v>1</v>
       </c>
     </row>
@@ -2216,7 +2222,7 @@
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A26=C26</f>
         <v>1</v>
       </c>
     </row>
@@ -2225,26 +2231,26 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>55</v>
+        <v>311</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>208</v>
+      <c r="D27" s="26">
+        <v>2.1</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>56</v>
+        <v>312</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A27=C27</f>
         <v>1</v>
       </c>
     </row>
@@ -2253,26 +2259,26 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>282</v>
+        <v>55</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A28=C28</f>
         <v>1</v>
       </c>
     </row>
@@ -2281,26 +2287,26 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
         <v/>
       </c>
       <c r="H29" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A29=C29</f>
         <v>1</v>
       </c>
     </row>
@@ -2309,26 +2315,26 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>297</v>
+        <v>265</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
-      <c r="D30" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D30" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
         <v/>
       </c>
       <c r="H30" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A30=C30</f>
         <v>1</v>
       </c>
     </row>
@@ -2337,26 +2343,26 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>51</v>
+        <v>297</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
-      <c r="D31" s="26" t="s">
-        <v>217</v>
+      <c r="D31" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>52</v>
+        <v>298</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
         <v/>
       </c>
       <c r="H31" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A31=C31</f>
         <v>1</v>
       </c>
     </row>
@@ -2365,26 +2371,26 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
         <v/>
       </c>
       <c r="H32" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A32=C32</f>
         <v>1</v>
       </c>
     </row>
@@ -2393,26 +2399,26 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
         <v/>
       </c>
       <c r="H33" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A33=C33</f>
         <v>1</v>
       </c>
     </row>
@@ -2421,26 +2427,26 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
         <v/>
       </c>
       <c r="H34" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A34=C34</f>
         <v>1</v>
       </c>
     </row>
@@ -2449,26 +2455,26 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
         <v/>
       </c>
       <c r="H35" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A35=C35</f>
         <v>1</v>
       </c>
     </row>
@@ -2477,26 +2483,26 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>249</v>
+        <v>41</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
-      <c r="D36" s="26">
-        <v>2.1</v>
+      <c r="D36" s="26" t="s">
+        <v>216</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>206</v>
+        <v>42</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
         <v/>
       </c>
       <c r="H36" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A36=C36</f>
         <v>1</v>
       </c>
     </row>
@@ -2505,26 +2511,26 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>39</v>
+        <v>249</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
-      <c r="D37" s="26" t="s">
-        <v>215</v>
+      <c r="D37" s="26">
+        <v>2.1</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
         <v/>
       </c>
       <c r="H37" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A37=C37</f>
         <v>1</v>
       </c>
     </row>
@@ -2533,26 +2539,26 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
         <v/>
       </c>
       <c r="H38" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A38=C38</f>
         <v>1</v>
       </c>
     </row>
@@ -2561,54 +2567,54 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>285</v>
+        <v>35</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
         <v/>
       </c>
       <c r="H39" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A39=C39</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="35">
-        <v>17</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="37">
-        <v>17</v>
-      </c>
-      <c r="D40" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="35" t="s">
-        <v>73</v>
+      <c r="A40" s="26">
+        <v>15</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="28">
+        <v>15</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="F40" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
         <v/>
       </c>
       <c r="H40" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A40=C40</f>
         <v>1</v>
       </c>
     </row>
@@ -2617,26 +2623,26 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>286</v>
+        <v>72</v>
       </c>
       <c r="C41" s="37">
         <v>17</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
         <v/>
       </c>
       <c r="H41" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A41=C41</f>
         <v>1</v>
       </c>
     </row>
@@ -2645,26 +2651,26 @@
         <v>17</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>63</v>
+        <v>286</v>
       </c>
       <c r="C42" s="37">
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
         <v/>
       </c>
       <c r="H42" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A42=C42</f>
         <v>1</v>
       </c>
     </row>
@@ -2673,54 +2679,54 @@
         <v>17</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C43" s="37">
         <v>17</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E43" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A43=C43</f>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="38">
+      <c r="A44" s="35">
         <v>17</v>
       </c>
-      <c r="B44" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C44" s="40">
+      <c r="B44" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="37">
         <v>17</v>
       </c>
-      <c r="D44" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E44" s="39" t="s">
+      <c r="D44" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="38" t="s">
-        <v>113</v>
+      <c r="F44" s="35" t="s">
+        <v>62</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A44=C44</f>
         <v>1</v>
       </c>
     </row>
@@ -2729,26 +2735,26 @@
         <v>17</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="C45" s="40">
         <v>17</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A45=C45</f>
         <v>1</v>
       </c>
     </row>
@@ -2757,54 +2763,54 @@
         <v>17</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>308</v>
+        <v>108</v>
       </c>
       <c r="C46" s="40">
         <v>17</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A46=C46</f>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="35">
+      <c r="A47" s="38">
         <v>17</v>
       </c>
-      <c r="B47" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="37">
+      <c r="B47" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="C47" s="40">
         <v>17</v>
       </c>
-      <c r="D47" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="35" t="s">
-        <v>54</v>
+      <c r="D47" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
@@ -2813,54 +2819,54 @@
         <v>17</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C48" s="37">
         <v>17</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E48" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="38">
+      <c r="A49" s="35">
         <v>17</v>
       </c>
-      <c r="B49" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="40">
+      <c r="B49" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" s="37">
         <v>17</v>
       </c>
-      <c r="D49" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E49" s="39" t="s">
+      <c r="D49" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="38" t="s">
-        <v>100</v>
+      <c r="F49" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A49=C49</f>
         <v>1</v>
       </c>
     </row>
@@ -2869,110 +2875,110 @@
         <v>17</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C50" s="40">
         <v>17</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E50" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A50=C50</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="35">
+      <c r="A51" s="38">
         <v>17</v>
       </c>
-      <c r="B51" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="37">
+      <c r="B51" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C51" s="40">
         <v>17</v>
       </c>
-      <c r="D51" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E51" s="36" t="s">
+      <c r="D51" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E51" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="35" t="s">
-        <v>38</v>
+      <c r="F51" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="38">
+      <c r="A52" s="35">
         <v>17</v>
       </c>
-      <c r="B52" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C52" s="40">
+      <c r="B52" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="37">
         <v>17</v>
       </c>
-      <c r="D52" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E52" s="39" t="s">
+      <c r="D52" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="38" t="s">
-        <v>86</v>
+      <c r="F52" s="35" t="s">
+        <v>38</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A52=C52</f>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="35">
+      <c r="A53" s="38">
         <v>17</v>
       </c>
-      <c r="B53" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="37">
+      <c r="B53" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" s="40">
         <v>17</v>
       </c>
-      <c r="D53" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="E53" s="36" t="s">
+      <c r="D53" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E53" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="35" t="s">
-        <v>33</v>
+      <c r="F53" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
         <v/>
       </c>
       <c r="H53" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A53=C53</f>
         <v>1</v>
       </c>
     </row>
@@ -2981,54 +2987,54 @@
         <v>17</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C54" s="37">
         <v>17</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E54" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="32">
-        <v>20</v>
-      </c>
-      <c r="B55" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C55" s="34">
-        <v>20</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E55" s="33" t="s">
+      <c r="A55" s="35">
+        <v>17</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="37">
+        <v>17</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="32" t="s">
-        <v>149</v>
+      <c r="F55" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H55" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
@@ -3037,26 +3043,26 @@
         <v>20</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C56" s="34">
         <v>20</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
@@ -3065,26 +3071,26 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
         <v/>
       </c>
       <c r="H57" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A57=C57</f>
         <v>1</v>
       </c>
     </row>
@@ -3093,26 +3099,26 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
         <v/>
       </c>
       <c r="H58" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A58=C58</f>
         <v>1</v>
       </c>
     </row>
@@ -3121,26 +3127,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
@@ -3149,26 +3155,26 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>261</v>
+        <v>141</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
@@ -3177,26 +3183,26 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
-      <c r="D61" s="32">
-        <v>4.2</v>
+      <c r="D61" s="32" t="s">
+        <v>229</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="F61" s="32">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
@@ -3205,26 +3211,26 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
-      <c r="D62" s="32" t="s">
-        <v>214</v>
+      <c r="D62" s="32">
+        <v>4.2</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>139</v>
+        <v>310</v>
+      </c>
+      <c r="F62" s="32">
+        <v>21765430</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
@@ -3233,26 +3239,26 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
@@ -3261,26 +3267,26 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
@@ -3289,26 +3295,26 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A65=C65</f>
         <v>1</v>
       </c>
     </row>
@@ -3317,26 +3323,26 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
         <v/>
       </c>
       <c r="H66" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3345,26 +3351,26 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
         <v/>
       </c>
       <c r="H67" s="21" t="b">
-        <f t="shared" ref="H67:H130" si="1">A67=C67</f>
+        <f>A67=C67</f>
         <v>1</v>
       </c>
     </row>
@@ -3373,26 +3379,26 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
         <v/>
       </c>
       <c r="H68" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A68=C68</f>
         <v>1</v>
       </c>
     </row>
@@ -3401,26 +3407,26 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
@@ -3429,26 +3435,26 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
@@ -3457,26 +3463,26 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
         <v/>
       </c>
       <c r="H71" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A71=C71</f>
         <v>1</v>
       </c>
     </row>
@@ -3485,26 +3491,26 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>120</v>
+        <v>262</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>121</v>
+        <v>263</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
         <v/>
       </c>
       <c r="H72" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
@@ -3513,26 +3519,26 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3541,82 +3547,82 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="26">
+      <c r="A75" s="32">
         <v>20</v>
       </c>
-      <c r="B75" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C75" s="28">
+      <c r="B75" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" s="34">
         <v>20</v>
       </c>
-      <c r="D75" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F75" s="26" t="s">
-        <v>303</v>
+      <c r="D75" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E75" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="32" t="s">
+        <v>117</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="32">
+      <c r="A76" s="26">
         <v>20</v>
       </c>
-      <c r="B76" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" s="34">
+      <c r="B76" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C76" s="28">
         <v>20</v>
       </c>
-      <c r="D76" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="E76" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="32" t="s">
-        <v>115</v>
+      <c r="D76" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E76" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A76=C76</f>
         <v>1</v>
       </c>
     </row>
@@ -3625,26 +3631,26 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A77=C77</f>
         <v>1</v>
       </c>
     </row>
@@ -3653,82 +3659,82 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="26">
+      <c r="A79" s="32">
         <v>20</v>
       </c>
-      <c r="B79" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="C79" s="28">
+      <c r="B79" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C79" s="34">
         <v>20</v>
       </c>
-      <c r="D79" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E79" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F79" s="26" t="s">
-        <v>306</v>
+      <c r="D79" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="32">
+      <c r="A80" s="26">
         <v>20</v>
       </c>
-      <c r="B80" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="C80" s="34">
+      <c r="B80" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="C80" s="28">
         <v>20</v>
       </c>
-      <c r="D80" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="E80" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F80" s="32" t="s">
-        <v>106</v>
+      <c r="D80" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E80" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F80" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
@@ -3737,26 +3743,26 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A81=C81</f>
         <v>1</v>
       </c>
     </row>
@@ -3765,26 +3771,26 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
-      <c r="D82" s="32">
-        <v>6.2</v>
+      <c r="D82" s="32" t="s">
+        <v>211</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>269</v>
+        <v>104</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A82=C82</f>
         <v>1</v>
       </c>
     </row>
@@ -3793,82 +3799,82 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>101</v>
+        <v>268</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
-      <c r="D83" s="32" t="s">
-        <v>219</v>
+      <c r="D83" s="32">
+        <v>6.2</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A83=C83</f>
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="26">
+      <c r="A84" s="32">
         <v>20</v>
       </c>
-      <c r="B84" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C84" s="28">
+      <c r="B84" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C84" s="34">
         <v>20</v>
       </c>
-      <c r="D84" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E84" s="27" t="s">
+      <c r="D84" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E84" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="F84" s="26" t="s">
-        <v>306</v>
+      <c r="F84" s="32" t="s">
+        <v>102</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A84=C84</f>
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="32">
+      <c r="A85" s="26">
         <v>20</v>
       </c>
-      <c r="B85" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C85" s="34">
+      <c r="B85" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C85" s="28">
         <v>20</v>
       </c>
-      <c r="D85" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E85" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="32" t="s">
-        <v>98</v>
+      <c r="D85" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A85=C85</f>
         <v>1</v>
       </c>
     </row>
@@ -3877,26 +3883,26 @@
         <v>20</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C86" s="34">
         <v>20</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
@@ -3905,26 +3911,26 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A87=C87</f>
         <v>1</v>
       </c>
     </row>
@@ -3933,16 +3939,16 @@
         <v>20</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="C88" s="34">
         <v>20</v>
       </c>
-      <c r="D88" s="32">
-        <v>1.8</v>
+      <c r="D88" s="32" t="s">
+        <v>227</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>296</v>
+        <v>8</v>
       </c>
       <c r="F88" s="32" t="s">
         <v>92</v>
@@ -3952,7 +3958,7 @@
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A88=C88</f>
         <v>1</v>
       </c>
     </row>
@@ -3961,26 +3967,26 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
-      <c r="D89" s="32" t="s">
-        <v>226</v>
+      <c r="D89" s="32">
+        <v>1.8</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A89=C89</f>
         <v>1</v>
       </c>
     </row>
@@ -3989,26 +3995,26 @@
         <v>20</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C90" s="34">
         <v>20</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E90" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A90=C90</f>
         <v>1</v>
       </c>
     </row>
@@ -4017,26 +4023,26 @@
         <v>20</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C91" s="34">
         <v>20</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F91" s="32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A91=C91</f>
         <v>1</v>
       </c>
     </row>
@@ -4045,26 +4051,26 @@
         <v>20</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C92" s="34">
         <v>20</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E92" s="33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F92" s="32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A92=C92</f>
         <v>1</v>
       </c>
     </row>
@@ -4073,54 +4079,54 @@
         <v>20</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C93" s="34">
         <v>20</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E93" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F93" s="32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A93=C93</f>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="26">
-        <v>25</v>
-      </c>
-      <c r="B94" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C94" s="28">
-        <v>25</v>
-      </c>
-      <c r="D94" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E94" s="27" t="s">
+      <c r="A94" s="32">
+        <v>20</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C94" s="34">
+        <v>20</v>
+      </c>
+      <c r="D94" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E94" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="26" t="s">
-        <v>183</v>
+      <c r="F94" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A94=C94</f>
         <v>1</v>
       </c>
     </row>
@@ -4129,26 +4135,26 @@
         <v>25</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C95" s="28">
         <v>25</v>
       </c>
       <c r="D95" s="26" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A95=C95</f>
         <v>1</v>
       </c>
     </row>
@@ -4157,26 +4163,26 @@
         <v>25</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C96" s="28">
         <v>25</v>
       </c>
       <c r="D96" s="26" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E96" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A96=C96</f>
         <v>1</v>
       </c>
     </row>
@@ -4185,26 +4191,26 @@
         <v>25</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C97" s="28">
         <v>25</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E97" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
@@ -4213,54 +4219,54 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E98" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A98=C98</f>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="32">
+      <c r="A99" s="26">
         <v>25</v>
       </c>
-      <c r="B99" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C99" s="34">
+      <c r="B99" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C99" s="28">
         <v>25</v>
       </c>
-      <c r="D99" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E99" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>104</v>
+      <c r="D99" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E99" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A99=C99</f>
         <v>1</v>
       </c>
     </row>
@@ -4269,7 +4275,7 @@
         <v>25</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C100" s="34">
         <v>25</v>
@@ -4288,35 +4294,35 @@
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="26">
+      <c r="A101" s="32">
         <v>25</v>
       </c>
-      <c r="B101" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C101" s="28">
+      <c r="B101" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="C101" s="34">
         <v>25</v>
       </c>
-      <c r="D101" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>173</v>
+      <c r="D101" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F101" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
         <v/>
       </c>
       <c r="H101" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
@@ -4325,82 +4331,82 @@
         <v>25</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C102" s="28">
         <v>25</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E102" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A102=C102</f>
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="32">
+      <c r="A103" s="26">
         <v>25</v>
       </c>
-      <c r="B103" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="34">
+      <c r="B103" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103" s="28">
         <v>25</v>
       </c>
-      <c r="D103" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E103" s="33" t="s">
+      <c r="D103" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E103" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F103" s="32" t="s">
-        <v>104</v>
+      <c r="F103" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A103=C103</f>
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="26">
+      <c r="A104" s="32">
         <v>25</v>
       </c>
-      <c r="B104" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C104" s="28">
+      <c r="B104" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="C104" s="34">
         <v>25</v>
       </c>
-      <c r="D104" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F104" s="26" t="s">
-        <v>169</v>
+      <c r="D104" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A104=C104</f>
         <v>1</v>
       </c>
     </row>
@@ -4409,26 +4415,26 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E105" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A105=C105</f>
         <v>1</v>
       </c>
     </row>
@@ -4437,26 +4443,26 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E106" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
         <v/>
       </c>
       <c r="H106" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A106=C106</f>
         <v>1</v>
       </c>
     </row>
@@ -4465,26 +4471,26 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E107" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A107=C107</f>
         <v>1</v>
       </c>
     </row>
@@ -4493,26 +4499,26 @@
         <v>25</v>
       </c>
       <c r="B108" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C108" s="28">
         <v>25</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E108" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A108=C108</f>
         <v>1</v>
       </c>
     </row>
@@ -4521,26 +4527,26 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E109" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A109=C109</f>
         <v>1</v>
       </c>
     </row>
@@ -4549,26 +4555,26 @@
         <v>25</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C110" s="28">
         <v>25</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E110" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
@@ -4577,26 +4583,26 @@
         <v>25</v>
       </c>
       <c r="B111" s="27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C111" s="28">
         <v>25</v>
       </c>
       <c r="D111" s="26" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E111" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
         <v/>
       </c>
       <c r="H111" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A111=C111</f>
         <v>1</v>
       </c>
     </row>
@@ -4605,26 +4611,26 @@
         <v>25</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>252</v>
+        <v>154</v>
       </c>
       <c r="C112" s="28">
         <v>25</v>
       </c>
-      <c r="D112" s="41" t="s">
-        <v>233</v>
+      <c r="D112" s="26" t="s">
+        <v>234</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>253</v>
+        <v>155</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
         <v/>
       </c>
       <c r="H112" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A112=C112</f>
         <v>1</v>
       </c>
     </row>
@@ -4633,54 +4639,54 @@
         <v>25</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="C113" s="28">
         <v>25</v>
       </c>
-      <c r="D113" s="26" t="s">
-        <v>239</v>
+      <c r="D113" s="41" t="s">
+        <v>233</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
         <v/>
       </c>
       <c r="H113" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A113=C113</f>
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="32">
+      <c r="A114" s="26">
         <v>25</v>
       </c>
-      <c r="B114" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="C114" s="34">
+      <c r="B114" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C114" s="28">
         <v>25</v>
       </c>
-      <c r="D114" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E114" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F114" s="32" t="s">
-        <v>104</v>
+      <c r="D114" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E114" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
         <v/>
       </c>
       <c r="H114" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A114=C114</f>
         <v>1</v>
       </c>
     </row>
@@ -4689,7 +4695,7 @@
         <v>25</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C115" s="34">
         <v>25</v>
@@ -4708,7 +4714,7 @@
         <v/>
       </c>
       <c r="H115" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A115=C115</f>
         <v>1</v>
       </c>
     </row>
@@ -4717,7 +4723,7 @@
         <v>25</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C116" s="34">
         <v>25</v>
@@ -4736,119 +4742,119 @@
         <v/>
       </c>
       <c r="H116" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A116=C116</f>
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="26">
+      <c r="A117" s="32">
         <v>25</v>
       </c>
-      <c r="B117" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C117" s="28">
+      <c r="B117" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C117" s="34">
         <v>25</v>
       </c>
-      <c r="D117" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E117" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>258</v>
+      <c r="D117" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F117" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
         <v/>
       </c>
       <c r="H117" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A117=C117</f>
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="32">
+      <c r="A118" s="26">
         <v>25</v>
       </c>
-      <c r="B118" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C118" s="34">
+      <c r="B118" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C118" s="28">
         <v>25</v>
       </c>
-      <c r="D118" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E118" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F118" s="32" t="s">
-        <v>104</v>
+      <c r="D118" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>258</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
         <v/>
       </c>
       <c r="H118" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A118=C118</f>
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="26">
+      <c r="A119" s="32">
         <v>25</v>
       </c>
-      <c r="B119" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C119" s="28">
+      <c r="B119" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C119" s="34">
         <v>25</v>
       </c>
-      <c r="D119" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E119" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F119" s="26" t="s">
-        <v>151</v>
+      <c r="D119" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F119" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
         <v/>
       </c>
       <c r="H119" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A119=C119</f>
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="32">
-        <v>30</v>
-      </c>
-      <c r="B120" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C120" s="34">
-        <v>30</v>
-      </c>
-      <c r="D120" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E120" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F120" s="32" t="s">
-        <v>197</v>
+      <c r="A120" s="26">
+        <v>25</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C120" s="28">
+        <v>25</v>
+      </c>
+      <c r="D120" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
         <v/>
       </c>
       <c r="H120" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A120=C120</f>
         <v>1</v>
       </c>
     </row>
@@ -4857,26 +4863,26 @@
         <v>30</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C121" s="34">
         <v>30</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E121" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F121" s="32" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H121" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A121=C121</f>
         <v>1</v>
       </c>
     </row>
@@ -4885,13 +4891,13 @@
         <v>30</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C122" s="34">
         <v>30</v>
       </c>
       <c r="D122" s="32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E122" s="33" t="s">
         <v>133</v>
@@ -4904,7 +4910,7 @@
         <v/>
       </c>
       <c r="H122" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A122=C122</f>
         <v>1</v>
       </c>
     </row>
@@ -4913,26 +4919,26 @@
         <v>30</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="C123" s="34">
         <v>30</v>
       </c>
       <c r="D123" s="32" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E123" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
         <v/>
       </c>
       <c r="H123" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A123=C123</f>
         <v>1</v>
       </c>
     </row>
@@ -4941,26 +4947,26 @@
         <v>30</v>
       </c>
       <c r="B124" s="33" t="s">
-        <v>190</v>
+        <v>251</v>
       </c>
       <c r="C124" s="34">
         <v>30</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E124" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
         <v/>
       </c>
       <c r="H124" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A124=C124</f>
         <v>1</v>
       </c>
     </row>
@@ -4969,26 +4975,26 @@
         <v>30</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C125" s="34">
         <v>30</v>
       </c>
       <c r="D125" s="32" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E125" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F125" s="32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
         <v/>
       </c>
       <c r="H125" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A125=C125</f>
         <v>1</v>
       </c>
     </row>
@@ -4997,26 +5003,26 @@
         <v>30</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C126" s="34">
         <v>30</v>
       </c>
       <c r="D126" s="32" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E126" s="33" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F126" s="32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
         <v/>
       </c>
       <c r="H126" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A126=C126</f>
         <v>1</v>
       </c>
     </row>
@@ -5025,54 +5031,54 @@
         <v>30</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C127" s="34">
         <v>30</v>
       </c>
       <c r="D127" s="32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E127" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F127" s="32" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
         <v/>
       </c>
       <c r="H127" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A127=C127</f>
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="26">
-        <v>40</v>
-      </c>
-      <c r="B128" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C128" s="28">
-        <v>40</v>
-      </c>
-      <c r="D128" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>203</v>
+      <c r="A128" s="32">
+        <v>30</v>
+      </c>
+      <c r="B128" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C128" s="34">
+        <v>30</v>
+      </c>
+      <c r="D128" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E128" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F128" s="32" t="s">
+        <v>185</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A128=C128</f>
         <v>1</v>
       </c>
     </row>
@@ -5081,26 +5087,26 @@
         <v>40</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C129" s="28">
         <v>40</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
         <v/>
       </c>
       <c r="H129" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A129=C129</f>
         <v>1</v>
       </c>
     </row>
@@ -5109,65 +5115,84 @@
         <v>40</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="C130" s="28">
         <v>40</v>
       </c>
-      <c r="D130" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D130" s="26" t="s">
+        <v>247</v>
       </c>
       <c r="E130" s="27" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
         <v/>
       </c>
       <c r="H130" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A130=C130</f>
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A131" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="C131" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D131" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
-        <f t="shared" ref="H131" si="2">A131=C131</f>
+        <f>A131=C131</f>
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="30"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="30"/>
-      <c r="D132" s="30"/>
-      <c r="E132" s="31"/>
-      <c r="F132" s="30"/>
-      <c r="G132" s="31"/>
+      <c r="A132" s="26">
+        <v>45</v>
+      </c>
+      <c r="B132" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C132" s="28">
+        <v>45</v>
+      </c>
+      <c r="D132" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E132" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F132" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="G132" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H132" s="21" t="b">
+        <f>A132=C132</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="30"/>
@@ -10559,10 +10584,10 @@
       <sortCondition ref="D2:D127"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H131">
-    <sortCondition ref="A2:A131"/>
-    <sortCondition ref="B2:B131"/>
-    <sortCondition ref="D2:D131"/>
+  <sortState ref="A2:H132">
+    <sortCondition ref="A2:A132"/>
+    <sortCondition ref="B2:B132"/>
+    <sortCondition ref="D2:D132"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$131</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$128</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="317">
   <si>
     <t>Grupo</t>
   </si>
@@ -964,6 +964,18 @@
   </si>
   <si>
     <t>21715-062</t>
+  </si>
+  <si>
+    <t>RUA DO CACAU</t>
+  </si>
+  <si>
+    <t>Ouro Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESIDENCIAL FLORIDA </t>
+  </si>
+  <si>
+    <t>21770-200</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1504,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1025"/>
+  <dimension ref="A1:H1027"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -2050,7 +2062,7 @@
         <v>71</v>
       </c>
       <c r="G20" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
         <v/>
       </c>
       <c r="H20" s="21" t="b">
@@ -2511,19 +2523,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2539,19 +2551,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>39</v>
+        <v>249</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
-      <c r="D38" s="26" t="s">
-        <v>215</v>
+      <c r="D38" s="26">
+        <v>2.1</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2567,19 +2579,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2595,19 +2607,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>285</v>
+        <v>35</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2619,23 +2631,23 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="35">
-        <v>17</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="37">
-        <v>17</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="35" t="s">
-        <v>73</v>
+      <c r="A41" s="26">
+        <v>15</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C41" s="28">
+        <v>15</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2651,19 +2663,19 @@
         <v>17</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>286</v>
+        <v>72</v>
       </c>
       <c r="C42" s="37">
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2679,19 +2691,19 @@
         <v>17</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>63</v>
+        <v>286</v>
       </c>
       <c r="C43" s="37">
         <v>17</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E43" s="36" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2707,19 +2719,19 @@
         <v>17</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C44" s="37">
         <v>17</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2731,23 +2743,23 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="38">
+      <c r="A45" s="35">
         <v>17</v>
       </c>
-      <c r="B45" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C45" s="40">
+      <c r="B45" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="37">
         <v>17</v>
       </c>
-      <c r="D45" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E45" s="39" t="s">
+      <c r="D45" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="38" t="s">
-        <v>113</v>
+      <c r="F45" s="35" t="s">
+        <v>62</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2763,19 +2775,19 @@
         <v>17</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="C46" s="40">
         <v>17</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2791,19 +2803,19 @@
         <v>17</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>308</v>
+        <v>108</v>
       </c>
       <c r="C47" s="40">
         <v>17</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -2815,23 +2827,23 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="35">
+      <c r="A48" s="38">
         <v>17</v>
       </c>
-      <c r="B48" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="37">
+      <c r="B48" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="C48" s="40">
         <v>17</v>
       </c>
-      <c r="D48" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="35" t="s">
-        <v>54</v>
+      <c r="D48" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
@@ -2847,19 +2859,19 @@
         <v>17</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C49" s="37">
         <v>17</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E49" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -2871,23 +2883,23 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="38">
+      <c r="A50" s="35">
         <v>17</v>
       </c>
-      <c r="B50" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="40">
+      <c r="B50" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="37">
         <v>17</v>
       </c>
-      <c r="D50" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E50" s="39" t="s">
+      <c r="D50" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E50" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="38" t="s">
-        <v>100</v>
+      <c r="F50" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -2903,19 +2915,19 @@
         <v>17</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C51" s="40">
         <v>17</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E51" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -2927,23 +2939,23 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="35">
+      <c r="A52" s="38">
         <v>17</v>
       </c>
-      <c r="B52" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="37">
+      <c r="B52" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="40">
         <v>17</v>
       </c>
-      <c r="D52" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E52" s="36" t="s">
+      <c r="D52" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E52" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="35" t="s">
-        <v>38</v>
+      <c r="F52" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -2955,23 +2967,23 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="38">
+      <c r="A53" s="35">
         <v>17</v>
       </c>
-      <c r="B53" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C53" s="40">
+      <c r="B53" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="37">
         <v>17</v>
       </c>
-      <c r="D53" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E53" s="39" t="s">
+      <c r="D53" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E53" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="38" t="s">
-        <v>86</v>
+      <c r="F53" s="35" t="s">
+        <v>38</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -2983,23 +2995,23 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="35">
+      <c r="A54" s="38">
         <v>17</v>
       </c>
-      <c r="B54" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="37">
+      <c r="B54" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="40">
         <v>17</v>
       </c>
-      <c r="D54" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="E54" s="36" t="s">
+      <c r="D54" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E54" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="35" t="s">
-        <v>33</v>
+      <c r="F54" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
@@ -3015,19 +3027,19 @@
         <v>17</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C55" s="37">
         <v>17</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E55" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
@@ -3039,23 +3051,23 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="32">
-        <v>20</v>
-      </c>
-      <c r="B56" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" s="34">
-        <v>20</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E56" s="33" t="s">
+      <c r="A56" s="35">
+        <v>17</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="37">
+        <v>17</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="32" t="s">
-        <v>149</v>
+      <c r="F56" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -3071,19 +3083,19 @@
         <v>20</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C57" s="34">
         <v>20</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
@@ -3099,19 +3111,19 @@
         <v>20</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C58" s="34">
         <v>20</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
@@ -3127,19 +3139,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C59" s="34">
         <v>20</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
@@ -3155,19 +3167,19 @@
         <v>20</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C60" s="34">
         <v>20</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3183,19 +3195,19 @@
         <v>20</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="C61" s="34">
         <v>20</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>261</v>
+        <v>141</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3211,19 +3223,19 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
-      <c r="D62" s="32">
-        <v>4.2</v>
+      <c r="D62" s="32" t="s">
+        <v>229</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="F62" s="32">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3239,19 +3251,19 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
-      <c r="D63" s="32" t="s">
-        <v>214</v>
+      <c r="D63" s="32">
+        <v>4.2</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="32" t="s">
-        <v>139</v>
+        <v>310</v>
+      </c>
+      <c r="F63" s="32">
+        <v>21765430</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3267,19 +3279,19 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3295,19 +3307,19 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3323,19 +3335,19 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3351,19 +3363,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3379,19 +3391,19 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3407,19 +3419,19 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3435,19 +3447,19 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3463,19 +3475,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3491,19 +3503,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3519,19 +3531,19 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>120</v>
+        <v>262</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>121</v>
+        <v>263</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3547,19 +3559,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3575,19 +3587,19 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3599,23 +3611,23 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="26">
+      <c r="A76" s="32">
         <v>20</v>
       </c>
-      <c r="B76" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C76" s="28">
+      <c r="B76" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" s="34">
         <v>20</v>
       </c>
-      <c r="D76" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E76" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F76" s="26" t="s">
-        <v>303</v>
+      <c r="D76" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E76" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>117</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3627,23 +3639,23 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="32">
+      <c r="A77" s="26">
         <v>20</v>
       </c>
-      <c r="B77" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C77" s="34">
+      <c r="B77" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C77" s="28">
         <v>20</v>
       </c>
-      <c r="D77" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="E77" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="32" t="s">
-        <v>115</v>
+      <c r="D77" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E77" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F77" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3659,19 +3671,19 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3687,19 +3699,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3711,23 +3723,23 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="26">
+      <c r="A80" s="32">
         <v>20</v>
       </c>
-      <c r="B80" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="C80" s="28">
+      <c r="B80" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C80" s="34">
         <v>20</v>
       </c>
-      <c r="D80" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E80" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F80" s="26" t="s">
-        <v>306</v>
+      <c r="D80" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3739,23 +3751,23 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="32">
+      <c r="A81" s="26">
         <v>20</v>
       </c>
-      <c r="B81" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="C81" s="34">
+      <c r="B81" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="C81" s="28">
         <v>20</v>
       </c>
-      <c r="D81" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="E81" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F81" s="32" t="s">
-        <v>106</v>
+      <c r="D81" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F81" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3771,19 +3783,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3799,19 +3811,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
-      <c r="D83" s="32">
-        <v>6.2</v>
+      <c r="D83" s="32" t="s">
+        <v>211</v>
       </c>
       <c r="E83" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>269</v>
+        <v>104</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3827,19 +3839,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>101</v>
+        <v>268</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
-      <c r="D84" s="32" t="s">
-        <v>219</v>
+      <c r="D84" s="32">
+        <v>6.2</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3851,23 +3863,23 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="26">
+      <c r="A85" s="32">
         <v>20</v>
       </c>
-      <c r="B85" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C85" s="28">
+      <c r="B85" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C85" s="34">
         <v>20</v>
       </c>
-      <c r="D85" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E85" s="27" t="s">
+      <c r="D85" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E85" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="F85" s="26" t="s">
-        <v>306</v>
+      <c r="F85" s="32" t="s">
+        <v>102</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3879,23 +3891,23 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="32">
+      <c r="A86" s="26">
         <v>20</v>
       </c>
-      <c r="B86" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="34">
+      <c r="B86" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C86" s="28">
         <v>20</v>
       </c>
-      <c r="D86" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E86" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="32" t="s">
-        <v>98</v>
+      <c r="D86" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E86" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F86" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3911,19 +3923,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3939,19 +3951,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C88" s="34">
         <v>20</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E88" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F88" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -3967,16 +3979,16 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
-      <c r="D89" s="32">
-        <v>1.8</v>
+      <c r="D89" s="32" t="s">
+        <v>227</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>296</v>
+        <v>8</v>
       </c>
       <c r="F89" s="32" t="s">
         <v>92</v>
@@ -3995,19 +4007,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="C90" s="34">
         <v>20</v>
       </c>
-      <c r="D90" s="32" t="s">
-        <v>226</v>
+      <c r="D90" s="32">
+        <v>1.8</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="F90" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4023,19 +4035,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C91" s="34">
         <v>20</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E91" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F91" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4051,19 +4063,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C92" s="34">
         <v>20</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E92" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F92" s="32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4079,19 +4091,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C93" s="34">
         <v>20</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F93" s="32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4107,19 +4119,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C94" s="34">
         <v>20</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E94" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4131,23 +4143,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
-        <v>25</v>
-      </c>
-      <c r="B95" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C95" s="28">
-        <v>25</v>
-      </c>
-      <c r="D95" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E95" s="27" t="s">
+      <c r="A95" s="32">
+        <v>20</v>
+      </c>
+      <c r="B95" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C95" s="34">
+        <v>20</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E95" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F95" s="26" t="s">
-        <v>183</v>
+      <c r="F95" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4163,19 +4175,19 @@
         <v>25</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C96" s="28">
         <v>25</v>
       </c>
       <c r="D96" s="26" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4191,19 +4203,19 @@
         <v>25</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C97" s="28">
         <v>25</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E97" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4219,19 +4231,19 @@
         <v>25</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C98" s="28">
         <v>25</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E98" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4247,19 +4259,19 @@
         <v>25</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C99" s="28">
         <v>25</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E99" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4271,23 +4283,23 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="32">
+      <c r="A100" s="26">
         <v>25</v>
       </c>
-      <c r="B100" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C100" s="34">
+      <c r="B100" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C100" s="28">
         <v>25</v>
       </c>
-      <c r="D100" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E100" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F100" s="32" t="s">
-        <v>104</v>
+      <c r="D100" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4303,7 +4315,7 @@
         <v>25</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C101" s="34">
         <v>25</v>
@@ -4327,23 +4339,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
+      <c r="A102" s="32">
         <v>25</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C102" s="28">
+      <c r="B102" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="C102" s="34">
         <v>25</v>
       </c>
-      <c r="D102" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>173</v>
+      <c r="D102" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F102" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4359,19 +4371,19 @@
         <v>25</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C103" s="28">
         <v>25</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4383,23 +4395,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="32">
+      <c r="A104" s="26">
         <v>25</v>
       </c>
-      <c r="B104" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="C104" s="34">
+      <c r="B104" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104" s="28">
         <v>25</v>
       </c>
-      <c r="D104" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E104" s="33" t="s">
+      <c r="D104" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E104" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F104" s="32" t="s">
-        <v>104</v>
+      <c r="F104" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4411,23 +4423,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="26">
+      <c r="A105" s="32">
         <v>25</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C105" s="28">
+      <c r="B105" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="C105" s="34">
         <v>25</v>
       </c>
-      <c r="D105" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>169</v>
+      <c r="D105" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E105" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4443,19 +4455,19 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E106" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4471,19 +4483,19 @@
         <v>25</v>
       </c>
       <c r="B107" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C107" s="28">
         <v>25</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4499,19 +4511,19 @@
         <v>25</v>
       </c>
       <c r="B108" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C108" s="28">
         <v>25</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E108" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4527,19 +4539,19 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E109" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4555,19 +4567,19 @@
         <v>25</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C110" s="28">
         <v>25</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E110" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4583,22 +4595,22 @@
         <v>25</v>
       </c>
       <c r="B111" s="27" t="s">
-        <v>156</v>
+        <v>315</v>
       </c>
       <c r="C111" s="28">
         <v>25</v>
       </c>
-      <c r="D111" s="26" t="s">
-        <v>228</v>
+      <c r="D111" s="26">
+        <v>3.9</v>
       </c>
       <c r="E111" s="27" t="s">
-        <v>8</v>
+        <v>314</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>157</v>
+        <v>316</v>
       </c>
       <c r="G111" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H111" s="21" t="b">
@@ -4611,19 +4623,19 @@
         <v>25</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C112" s="28">
         <v>25</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4639,19 +4651,19 @@
         <v>25</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>252</v>
+        <v>156</v>
       </c>
       <c r="C113" s="28">
         <v>25</v>
       </c>
-      <c r="D113" s="41" t="s">
-        <v>233</v>
+      <c r="D113" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E113" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4667,19 +4679,19 @@
         <v>25</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C114" s="28">
         <v>25</v>
       </c>
       <c r="D114" s="26" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E114" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4691,23 +4703,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="32">
+      <c r="A115" s="26">
         <v>25</v>
       </c>
-      <c r="B115" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="C115" s="34">
+      <c r="B115" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C115" s="28">
         <v>25</v>
       </c>
-      <c r="D115" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E115" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F115" s="32" t="s">
-        <v>104</v>
+      <c r="D115" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4719,23 +4731,23 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="32">
+      <c r="A116" s="26">
         <v>25</v>
       </c>
-      <c r="B116" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="C116" s="34">
+      <c r="B116" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C116" s="28">
         <v>25</v>
       </c>
-      <c r="D116" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E116" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F116" s="32" t="s">
-        <v>104</v>
+      <c r="D116" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4751,7 +4763,7 @@
         <v>25</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C117" s="34">
         <v>25</v>
@@ -4775,23 +4787,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="26">
+      <c r="A118" s="32">
         <v>25</v>
       </c>
-      <c r="B118" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C118" s="28">
+      <c r="B118" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="C118" s="34">
         <v>25</v>
       </c>
-      <c r="D118" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E118" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>258</v>
+      <c r="D118" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E118" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F118" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4807,7 +4819,7 @@
         <v>25</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C119" s="34">
         <v>25</v>
@@ -4835,19 +4847,19 @@
         <v>25</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="C120" s="28">
         <v>25</v>
       </c>
-      <c r="D120" s="26" t="s">
-        <v>230</v>
+      <c r="D120" s="26">
+        <v>2.5</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4860,22 +4872,22 @@
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="C121" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E121" s="33" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="F121" s="32" t="s">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4887,26 +4899,26 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="32">
-        <v>30</v>
-      </c>
-      <c r="B122" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="C122" s="34">
-        <v>30</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="E122" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F122" s="32" t="s">
-        <v>194</v>
+      <c r="A122" s="26">
+        <v>25</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C122" s="28">
+        <v>25</v>
+      </c>
+      <c r="D122" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G122" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
@@ -4919,19 +4931,19 @@
         <v>30</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C123" s="34">
         <v>30</v>
       </c>
       <c r="D123" s="32" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E123" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -4947,19 +4959,19 @@
         <v>30</v>
       </c>
       <c r="B124" s="33" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="C124" s="34">
         <v>30</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="E124" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -4975,19 +4987,19 @@
         <v>30</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C125" s="34">
         <v>30</v>
       </c>
       <c r="D125" s="32" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E125" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F125" s="32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5003,19 +5015,19 @@
         <v>30</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="C126" s="34">
         <v>30</v>
       </c>
       <c r="D126" s="32" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E126" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F126" s="32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5031,19 +5043,19 @@
         <v>30</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C127" s="34">
         <v>30</v>
       </c>
       <c r="D127" s="32" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E127" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F127" s="32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5059,19 +5071,19 @@
         <v>30</v>
       </c>
       <c r="B128" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C128" s="34">
         <v>30</v>
       </c>
       <c r="D128" s="32" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E128" s="33" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F128" s="32" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5083,23 +5095,23 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="26">
-        <v>40</v>
-      </c>
-      <c r="B129" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C129" s="28">
-        <v>40</v>
-      </c>
-      <c r="D129" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E129" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="F129" s="26" t="s">
-        <v>203</v>
+      <c r="A129" s="32">
+        <v>30</v>
+      </c>
+      <c r="B129" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C129" s="34">
+        <v>30</v>
+      </c>
+      <c r="D129" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E129" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F129" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5111,23 +5123,23 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="26">
-        <v>40</v>
-      </c>
-      <c r="B130" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="C130" s="28">
-        <v>40</v>
-      </c>
-      <c r="D130" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="E130" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F130" s="26" t="s">
-        <v>200</v>
+      <c r="A130" s="32">
+        <v>30</v>
+      </c>
+      <c r="B130" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C130" s="34">
+        <v>30</v>
+      </c>
+      <c r="D130" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E130" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F130" s="32" t="s">
+        <v>185</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5143,19 +5155,19 @@
         <v>40</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="C131" s="28">
         <v>40</v>
       </c>
-      <c r="D131" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D131" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5168,22 +5180,22 @@
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>299</v>
+        <v>198</v>
       </c>
       <c r="C132" s="28">
-        <v>45</v>
-      </c>
-      <c r="D132" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D132" s="26" t="s">
+        <v>247</v>
       </c>
       <c r="E132" s="27" t="s">
-        <v>300</v>
+        <v>199</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5195,22 +5207,60 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="30"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="30"/>
-      <c r="D133" s="30"/>
-      <c r="E133" s="31"/>
-      <c r="F133" s="30"/>
-      <c r="G133" s="31"/>
+      <c r="A133" s="26">
+        <v>40</v>
+      </c>
+      <c r="B133" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C133" s="28">
+        <v>40</v>
+      </c>
+      <c r="D133" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E133" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="F133" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="G133" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H133" s="21" t="b">
+        <f>A133=C133</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="30"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="30"/>
-      <c r="D134" s="30"/>
-      <c r="E134" s="31"/>
-      <c r="F134" s="30"/>
-      <c r="G134" s="31"/>
+      <c r="A134" s="26">
+        <v>45</v>
+      </c>
+      <c r="B134" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C134" s="28">
+        <v>45</v>
+      </c>
+      <c r="D134" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E134" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F134" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="G134" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H134" s="21" t="b">
+        <f>A134=C134</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A135" s="30"/>
@@ -5267,16 +5317,22 @@
       <c r="G140" s="31"/>
     </row>
     <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="F141" s="1"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="30"/>
+      <c r="E141" s="31"/>
+      <c r="F141" s="30"/>
+      <c r="G141" s="31"/>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-      <c r="F142" s="1"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="30"/>
+      <c r="E142" s="31"/>
+      <c r="F142" s="30"/>
+      <c r="G142" s="31"/>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
@@ -10576,18 +10632,30 @@
       <c r="D1025" s="1"/>
       <c r="F1025" s="1"/>
     </row>
+    <row r="1026" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1026" s="1"/>
+      <c r="C1026" s="1"/>
+      <c r="D1026" s="1"/>
+      <c r="F1026" s="1"/>
+    </row>
+    <row r="1027" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1027" s="1"/>
+      <c r="C1027" s="1"/>
+      <c r="D1027" s="1"/>
+      <c r="F1027" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H131">
+  <autoFilter ref="A1:H133">
     <sortState ref="A2:H127">
       <sortCondition ref="A2:A127"/>
       <sortCondition ref="B2:B127"/>
       <sortCondition ref="D2:D127"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H132">
-    <sortCondition ref="A2:A132"/>
-    <sortCondition ref="B2:B132"/>
-    <sortCondition ref="D2:D132"/>
+  <sortState ref="A2:H134">
+    <sortCondition ref="A2:A134"/>
+    <sortCondition ref="B2:B134"/>
+    <sortCondition ref="D2:D134"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="329">
   <si>
     <t>Grupo</t>
   </si>
@@ -976,6 +976,42 @@
   </si>
   <si>
     <t>21770-200</t>
+  </si>
+  <si>
+    <t>CONCORDIA</t>
+  </si>
+  <si>
+    <t>CARNEIRO DA CUNHA</t>
+  </si>
+  <si>
+    <t>IRINEU BRITO</t>
+  </si>
+  <si>
+    <t>CRISPIM DE MACEDO</t>
+  </si>
+  <si>
+    <t>FLORENTINO DE VASCONCELHOS</t>
+  </si>
+  <si>
+    <t>LIBERIA</t>
+  </si>
+  <si>
+    <t>21750-330</t>
+  </si>
+  <si>
+    <t>21710-470</t>
+  </si>
+  <si>
+    <t>21710-480</t>
+  </si>
+  <si>
+    <t>21750-340</t>
+  </si>
+  <si>
+    <t>21710-500</t>
+  </si>
+  <si>
+    <t>21750-290</t>
   </si>
 </sst>
 </file>
@@ -2715,28 +2751,25 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="35">
+      <c r="A44" s="26">
         <v>17</v>
       </c>
-      <c r="B44" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="37">
+      <c r="B44" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C44" s="28">
         <v>17</v>
       </c>
-      <c r="D44" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="G44" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D44" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="G44" s="29"/>
       <c r="H44" s="21" t="b">
         <f>A44=C44</f>
         <v>1</v>
@@ -2747,19 +2780,19 @@
         <v>17</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C45" s="37">
         <v>17</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E45" s="36" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2771,23 +2804,23 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="38">
+      <c r="A46" s="35">
         <v>17</v>
       </c>
-      <c r="B46" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C46" s="40">
+      <c r="B46" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="37">
         <v>17</v>
       </c>
-      <c r="D46" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E46" s="39" t="s">
+      <c r="D46" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E46" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="38" t="s">
-        <v>113</v>
+      <c r="F46" s="35" t="s">
+        <v>62</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2799,79 +2832,73 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="38">
+      <c r="A47" s="26">
         <v>17</v>
       </c>
-      <c r="B47" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="40">
+      <c r="B47" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="C47" s="28">
         <v>17</v>
       </c>
-      <c r="D47" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E47" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="G47" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D47" s="26">
+        <v>3</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="G47" s="29"/>
       <c r="H47" s="21" t="b">
         <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="38">
+      <c r="A48" s="26">
         <v>17</v>
       </c>
-      <c r="B48" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="C48" s="40">
+      <c r="B48" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="C48" s="28">
         <v>17</v>
       </c>
-      <c r="D48" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="F48" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="G48" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D48" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="G48" s="29"/>
       <c r="H48" s="21" t="b">
         <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="35">
+      <c r="A49" s="38">
         <v>17</v>
       </c>
-      <c r="B49" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="37">
+      <c r="B49" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" s="40">
         <v>17</v>
       </c>
-      <c r="D49" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="35" t="s">
-        <v>54</v>
+      <c r="D49" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>113</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -2883,56 +2910,50 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="35">
+      <c r="A50" s="26">
         <v>17</v>
       </c>
-      <c r="B50" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="37">
+      <c r="B50" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C50" s="28">
         <v>17</v>
       </c>
-      <c r="D50" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G50" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D50" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="G50" s="29"/>
       <c r="H50" s="21" t="b">
         <f>A50=C50</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="38">
+      <c r="A51" s="26">
         <v>17</v>
       </c>
-      <c r="B51" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="40">
+      <c r="B51" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="C51" s="28">
         <v>17</v>
       </c>
-      <c r="D51" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E51" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="G51" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D51" s="26">
+        <v>2</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="G51" s="29"/>
       <c r="H51" s="21" t="b">
         <f>A51=C51</f>
         <v>1</v>
@@ -2943,19 +2964,19 @@
         <v>17</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C52" s="40">
         <v>17</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E52" s="39" t="s">
         <v>8</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -2967,23 +2988,23 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="35">
+      <c r="A53" s="38">
         <v>17</v>
       </c>
-      <c r="B53" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="37">
+      <c r="B53" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="C53" s="40">
         <v>17</v>
       </c>
-      <c r="D53" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="35" t="s">
-        <v>38</v>
+      <c r="D53" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -2995,23 +3016,23 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="38">
+      <c r="A54" s="35">
         <v>17</v>
       </c>
-      <c r="B54" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="40">
+      <c r="B54" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="37">
         <v>17</v>
       </c>
-      <c r="D54" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E54" s="39" t="s">
+      <c r="D54" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E54" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="38" t="s">
-        <v>86</v>
+      <c r="F54" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
@@ -3027,19 +3048,19 @@
         <v>17</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C55" s="37">
         <v>17</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E55" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
@@ -3051,23 +3072,23 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="35">
+      <c r="A56" s="38">
         <v>17</v>
       </c>
-      <c r="B56" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="37">
+      <c r="B56" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="40">
         <v>17</v>
       </c>
-      <c r="D56" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E56" s="36" t="s">
+      <c r="D56" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E56" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="35" t="s">
-        <v>31</v>
+      <c r="F56" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -3079,23 +3100,23 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="32">
-        <v>20</v>
-      </c>
-      <c r="B57" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C57" s="34">
-        <v>20</v>
-      </c>
-      <c r="D57" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E57" s="33" t="s">
+      <c r="A57" s="38">
+        <v>17</v>
+      </c>
+      <c r="B57" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="40">
+        <v>17</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E57" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="32" t="s">
-        <v>149</v>
+      <c r="F57" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
@@ -3107,23 +3128,23 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="32">
-        <v>20</v>
-      </c>
-      <c r="B58" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C58" s="34">
-        <v>20</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="E58" s="33" t="s">
+      <c r="A58" s="35">
+        <v>17</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" s="37">
+        <v>17</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E58" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="32" t="s">
-        <v>147</v>
+      <c r="F58" s="35" t="s">
+        <v>38</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
@@ -3135,23 +3156,23 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="32">
-        <v>20</v>
-      </c>
-      <c r="B59" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="C59" s="34">
-        <v>20</v>
-      </c>
-      <c r="D59" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="E59" s="33" t="s">
+      <c r="A59" s="38">
+        <v>17</v>
+      </c>
+      <c r="B59" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="40">
+        <v>17</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="32" t="s">
-        <v>145</v>
+      <c r="F59" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
@@ -3163,23 +3184,23 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="32">
-        <v>20</v>
-      </c>
-      <c r="B60" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" s="34">
-        <v>20</v>
-      </c>
-      <c r="D60" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E60" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="F60" s="32" t="s">
-        <v>143</v>
+      <c r="A60" s="35">
+        <v>17</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="37">
+        <v>17</v>
+      </c>
+      <c r="D60" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="35" t="s">
+        <v>33</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3191,23 +3212,23 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="32">
-        <v>20</v>
-      </c>
-      <c r="B61" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C61" s="34">
-        <v>20</v>
-      </c>
-      <c r="D61" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="E61" s="33" t="s">
+      <c r="A61" s="35">
+        <v>17</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="37">
+        <v>17</v>
+      </c>
+      <c r="D61" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E61" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="32" t="s">
-        <v>141</v>
+      <c r="F61" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3223,19 +3244,19 @@
         <v>20</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>260</v>
+        <v>148</v>
       </c>
       <c r="C62" s="34">
         <v>20</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>261</v>
+        <v>149</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3251,19 +3272,19 @@
         <v>20</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="C63" s="34">
         <v>20</v>
       </c>
-      <c r="D63" s="32">
-        <v>4.2</v>
+      <c r="D63" s="32" t="s">
+        <v>213</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="F63" s="32">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>147</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3279,19 +3300,19 @@
         <v>20</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C64" s="34">
         <v>20</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3307,19 +3328,19 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>270</v>
+        <v>142</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3335,19 +3356,19 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3363,19 +3384,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3391,19 +3412,19 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>130</v>
+        <v>259</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
-      <c r="D68" s="32" t="s">
-        <v>224</v>
+      <c r="D68" s="32">
+        <v>4.2</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="32" t="s">
-        <v>131</v>
+        <v>310</v>
+      </c>
+      <c r="F68" s="32">
+        <v>21765430</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3419,19 +3440,19 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3447,19 +3468,19 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3475,19 +3496,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3503,19 +3524,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3527,23 +3548,23 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="32">
+      <c r="A73" s="26">
         <v>20</v>
       </c>
-      <c r="B73" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="C73" s="34">
+      <c r="B73" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C73" s="28">
         <v>20</v>
       </c>
-      <c r="D73" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="E73" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="32" t="s">
-        <v>263</v>
+      <c r="D73" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>323</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3559,19 +3580,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3587,19 +3608,19 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3615,19 +3636,19 @@
         <v>20</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C76" s="34">
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E76" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F76" s="32" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3639,23 +3660,23 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="26">
+      <c r="A77" s="32">
         <v>20</v>
       </c>
-      <c r="B77" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C77" s="28">
+      <c r="B77" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C77" s="34">
         <v>20</v>
       </c>
-      <c r="D77" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E77" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F77" s="26" t="s">
-        <v>303</v>
+      <c r="D77" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="32" t="s">
+        <v>125</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3671,19 +3692,19 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3699,19 +3720,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3727,19 +3748,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E80" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3751,23 +3772,23 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="26">
+      <c r="A81" s="32">
         <v>20</v>
       </c>
-      <c r="B81" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="C81" s="28">
+      <c r="B81" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C81" s="34">
         <v>20</v>
       </c>
-      <c r="D81" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E81" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F81" s="26" t="s">
-        <v>306</v>
+      <c r="D81" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="32" t="s">
+        <v>119</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3783,19 +3804,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3807,23 +3828,23 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="32">
+      <c r="A83" s="26">
         <v>20</v>
       </c>
-      <c r="B83" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C83" s="34">
+      <c r="B83" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C83" s="28">
         <v>20</v>
       </c>
-      <c r="D83" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E83" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="32" t="s">
-        <v>104</v>
+      <c r="D83" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F83" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3839,19 +3860,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>268</v>
+        <v>114</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
-      <c r="D84" s="32">
-        <v>6.2</v>
+      <c r="D84" s="32" t="s">
+        <v>223</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>269</v>
+        <v>115</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3867,19 +3888,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E85" s="33" t="s">
         <v>304</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3891,23 +3912,23 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="26">
+      <c r="A86" s="32">
         <v>20</v>
       </c>
-      <c r="B86" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C86" s="28">
+      <c r="B86" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="34">
         <v>20</v>
       </c>
-      <c r="D86" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E86" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F86" s="26" t="s">
-        <v>306</v>
+      <c r="D86" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3919,23 +3940,23 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="32">
+      <c r="A87" s="26">
         <v>20</v>
       </c>
-      <c r="B87" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C87" s="34">
+      <c r="B87" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="C87" s="28">
         <v>20</v>
       </c>
-      <c r="D87" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E87" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" s="32" t="s">
-        <v>98</v>
+      <c r="D87" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E87" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F87" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3951,19 +3972,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C88" s="34">
         <v>20</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F88" s="32" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -3979,19 +4000,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4007,19 +4028,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="C90" s="34">
         <v>20</v>
       </c>
       <c r="D90" s="32">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>296</v>
+        <v>8</v>
       </c>
       <c r="F90" s="32" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4035,19 +4056,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C91" s="34">
         <v>20</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F91" s="32" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4059,23 +4080,23 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="32">
+      <c r="A92" s="26">
         <v>20</v>
       </c>
-      <c r="B92" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C92" s="34">
+      <c r="B92" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C92" s="28">
         <v>20</v>
       </c>
-      <c r="D92" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E92" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="32" t="s">
-        <v>88</v>
+      <c r="D92" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E92" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F92" s="26" t="s">
+        <v>306</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4091,19 +4112,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C93" s="34">
         <v>20</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F93" s="32" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4119,19 +4140,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C94" s="34">
         <v>20</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E94" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="32" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4147,19 +4168,19 @@
         <v>20</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C95" s="34">
         <v>20</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E95" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F95" s="32" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4171,23 +4192,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="26">
-        <v>25</v>
-      </c>
-      <c r="B96" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="28">
-        <v>25</v>
-      </c>
-      <c r="D96" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E96" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="26" t="s">
-        <v>183</v>
+      <c r="A96" s="32">
+        <v>20</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="C96" s="34">
+        <v>20</v>
+      </c>
+      <c r="D96" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="E96" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="F96" s="32" t="s">
+        <v>92</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4199,23 +4220,23 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="26">
-        <v>25</v>
-      </c>
-      <c r="B97" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C97" s="28">
-        <v>25</v>
-      </c>
-      <c r="D97" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E97" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F97" s="26" t="s">
-        <v>181</v>
+      <c r="A97" s="32">
+        <v>20</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C97" s="34">
+        <v>20</v>
+      </c>
+      <c r="D97" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="E97" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" s="32" t="s">
+        <v>90</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4227,23 +4248,23 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="26">
-        <v>25</v>
-      </c>
-      <c r="B98" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C98" s="28">
-        <v>25</v>
-      </c>
-      <c r="D98" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="E98" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F98" s="26" t="s">
-        <v>179</v>
+      <c r="A98" s="32">
+        <v>20</v>
+      </c>
+      <c r="B98" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C98" s="34">
+        <v>20</v>
+      </c>
+      <c r="D98" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="32" t="s">
+        <v>88</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4255,23 +4276,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="26">
-        <v>25</v>
-      </c>
-      <c r="B99" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C99" s="28">
-        <v>25</v>
-      </c>
-      <c r="D99" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>177</v>
+      <c r="A99" s="32">
+        <v>20</v>
+      </c>
+      <c r="B99" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C99" s="34">
+        <v>20</v>
+      </c>
+      <c r="D99" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E99" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4283,23 +4304,23 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="26">
-        <v>25</v>
-      </c>
-      <c r="B100" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C100" s="28">
-        <v>25</v>
-      </c>
-      <c r="D100" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="E100" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F100" s="26" t="s">
-        <v>175</v>
+      <c r="A100" s="32">
+        <v>20</v>
+      </c>
+      <c r="B100" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C100" s="34">
+        <v>20</v>
+      </c>
+      <c r="D100" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E100" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4312,22 +4333,22 @@
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="32">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="C101" s="34">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>288</v>
+        <v>8</v>
       </c>
       <c r="F101" s="32" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4339,23 +4360,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="32">
+      <c r="A102" s="26">
         <v>25</v>
       </c>
-      <c r="B102" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="C102" s="34">
+      <c r="B102" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C102" s="28">
         <v>25</v>
       </c>
-      <c r="D102" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E102" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F102" s="32" t="s">
-        <v>104</v>
+      <c r="D102" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E102" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4371,19 +4392,19 @@
         <v>25</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C103" s="28">
         <v>25</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E103" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4399,19 +4420,19 @@
         <v>25</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C104" s="28">
         <v>25</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E104" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4423,23 +4444,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="32">
+      <c r="A105" s="26">
         <v>25</v>
       </c>
-      <c r="B105" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="C105" s="34">
+      <c r="B105" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C105" s="28">
         <v>25</v>
       </c>
-      <c r="D105" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E105" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" s="32" t="s">
-        <v>104</v>
+      <c r="D105" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4455,19 +4476,19 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="E106" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4479,23 +4500,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="26">
+      <c r="A107" s="32">
         <v>25</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C107" s="28">
+      <c r="B107" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="C107" s="34">
         <v>25</v>
       </c>
-      <c r="D107" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="E107" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>167</v>
+      <c r="D107" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F107" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4507,23 +4528,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="26">
+      <c r="A108" s="32">
         <v>25</v>
       </c>
-      <c r="B108" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C108" s="28">
+      <c r="B108" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="C108" s="34">
         <v>25</v>
       </c>
-      <c r="D108" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E108" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>165</v>
+      <c r="D108" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F108" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4539,19 +4560,19 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4567,19 +4588,19 @@
         <v>25</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C110" s="28">
         <v>25</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E110" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4591,26 +4612,26 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="26">
+      <c r="A111" s="32">
         <v>25</v>
       </c>
-      <c r="B111" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C111" s="28">
+      <c r="B111" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="C111" s="34">
         <v>25</v>
       </c>
-      <c r="D111" s="26">
-        <v>3.9</v>
-      </c>
-      <c r="E111" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>316</v>
+      <c r="D111" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G111" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
         <v/>
       </c>
       <c r="H111" s="21" t="b">
@@ -4623,19 +4644,19 @@
         <v>25</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C112" s="28">
         <v>25</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4651,19 +4672,19 @@
         <v>25</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C113" s="28">
         <v>25</v>
       </c>
       <c r="D113" s="26" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4679,19 +4700,19 @@
         <v>25</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C114" s="28">
         <v>25</v>
       </c>
       <c r="D114" s="26" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E114" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4707,19 +4728,19 @@
         <v>25</v>
       </c>
       <c r="B115" s="27" t="s">
-        <v>252</v>
+        <v>162</v>
       </c>
       <c r="C115" s="28">
         <v>25</v>
       </c>
-      <c r="D115" s="41" t="s">
-        <v>233</v>
+      <c r="D115" s="26" t="s">
+        <v>240</v>
       </c>
       <c r="E115" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>253</v>
+        <v>163</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4735,19 +4756,19 @@
         <v>25</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C116" s="28">
         <v>25</v>
       </c>
       <c r="D116" s="26" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E116" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4759,26 +4780,26 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="32">
+      <c r="A117" s="26">
         <v>25</v>
       </c>
-      <c r="B117" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="C117" s="34">
+      <c r="B117" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C117" s="28">
         <v>25</v>
       </c>
-      <c r="D117" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E117" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F117" s="32" t="s">
-        <v>104</v>
+      <c r="D117" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>316</v>
       </c>
       <c r="G117" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
         <v/>
       </c>
       <c r="H117" s="21" t="b">
@@ -4787,23 +4808,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="32">
+      <c r="A118" s="26">
         <v>25</v>
       </c>
-      <c r="B118" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="C118" s="34">
+      <c r="B118" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C118" s="28">
         <v>25</v>
       </c>
-      <c r="D118" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E118" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F118" s="32" t="s">
-        <v>104</v>
+      <c r="D118" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>159</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4815,23 +4836,23 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="32">
+      <c r="A119" s="26">
         <v>25</v>
       </c>
-      <c r="B119" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C119" s="34">
+      <c r="B119" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C119" s="28">
         <v>25</v>
       </c>
-      <c r="D119" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E119" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F119" s="32" t="s">
-        <v>104</v>
+      <c r="D119" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E119" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4847,19 +4868,19 @@
         <v>25</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="C120" s="28">
         <v>25</v>
       </c>
-      <c r="D120" s="26">
-        <v>2.5</v>
+      <c r="D120" s="26" t="s">
+        <v>234</v>
       </c>
       <c r="E120" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4871,23 +4892,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="32">
+      <c r="A121" s="26">
         <v>25</v>
       </c>
-      <c r="B121" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C121" s="34">
+      <c r="B121" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C121" s="28">
         <v>25</v>
       </c>
-      <c r="D121" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E121" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F121" s="32" t="s">
-        <v>104</v>
+      <c r="D121" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4903,22 +4924,22 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G122" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
@@ -4928,22 +4949,22 @@
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A123" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
       <c r="C123" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D123" s="32" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E123" s="33" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -4956,22 +4977,22 @@
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B124" s="33" t="s">
-        <v>195</v>
+        <v>291</v>
       </c>
       <c r="C124" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="E124" s="33" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -4984,22 +5005,22 @@
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>193</v>
+        <v>292</v>
       </c>
       <c r="C125" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D125" s="32" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="E125" s="33" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="F125" s="32" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5011,23 +5032,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="32">
-        <v>30</v>
-      </c>
-      <c r="B126" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="C126" s="34">
-        <v>30</v>
-      </c>
-      <c r="D126" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E126" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" s="32" t="s">
-        <v>192</v>
+      <c r="A126" s="26">
+        <v>25</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C126" s="28">
+        <v>25</v>
+      </c>
+      <c r="D126" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>258</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5040,22 +5061,22 @@
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A127" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="C127" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D127" s="32" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="E127" s="33" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
       <c r="F127" s="32" t="s">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5067,26 +5088,26 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="32">
-        <v>30</v>
-      </c>
-      <c r="B128" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="C128" s="34">
-        <v>30</v>
-      </c>
-      <c r="D128" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E128" s="33" t="s">
+      <c r="A128" s="26">
+        <v>25</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C128" s="28">
+        <v>25</v>
+      </c>
+      <c r="D128" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E128" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="F128" s="32" t="s">
-        <v>189</v>
+      <c r="F128" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G128" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
@@ -5099,19 +5120,19 @@
         <v>30</v>
       </c>
       <c r="B129" s="33" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C129" s="34">
         <v>30</v>
       </c>
       <c r="D129" s="32" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E129" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F129" s="32" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5127,19 +5148,19 @@
         <v>30</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C130" s="34">
         <v>30</v>
       </c>
       <c r="D130" s="32" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E130" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F130" s="32" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5151,23 +5172,23 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="26">
-        <v>40</v>
-      </c>
-      <c r="B131" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C131" s="28">
-        <v>40</v>
-      </c>
-      <c r="D131" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E131" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="F131" s="26" t="s">
-        <v>203</v>
+      <c r="A131" s="32">
+        <v>30</v>
+      </c>
+      <c r="B131" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C131" s="34">
+        <v>30</v>
+      </c>
+      <c r="D131" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="E131" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F131" s="32" t="s">
+        <v>194</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5179,23 +5200,23 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="26">
-        <v>40</v>
-      </c>
-      <c r="B132" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="C132" s="28">
-        <v>40</v>
-      </c>
-      <c r="D132" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="E132" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F132" s="26" t="s">
-        <v>200</v>
+      <c r="A132" s="32">
+        <v>30</v>
+      </c>
+      <c r="B132" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="C132" s="34">
+        <v>30</v>
+      </c>
+      <c r="D132" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E132" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" s="32" t="s">
+        <v>192</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5207,23 +5228,23 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="26">
-        <v>40</v>
-      </c>
-      <c r="B133" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C133" s="28">
-        <v>40</v>
-      </c>
-      <c r="D133" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E133" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="F133" s="26" t="s">
-        <v>256</v>
+      <c r="A133" s="32">
+        <v>30</v>
+      </c>
+      <c r="B133" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C133" s="34">
+        <v>30</v>
+      </c>
+      <c r="D133" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E133" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F133" s="32" t="s">
+        <v>191</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5235,23 +5256,23 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="26">
-        <v>45</v>
-      </c>
-      <c r="B134" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C134" s="28">
-        <v>45</v>
-      </c>
-      <c r="D134" s="26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E134" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="F134" s="26" t="s">
-        <v>301</v>
+      <c r="A134" s="32">
+        <v>30</v>
+      </c>
+      <c r="B134" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C134" s="34">
+        <v>30</v>
+      </c>
+      <c r="D134" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E134" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F134" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5263,58 +5284,172 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="30"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="30"/>
-      <c r="D135" s="30"/>
-      <c r="E135" s="31"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="31"/>
+      <c r="A135" s="32">
+        <v>30</v>
+      </c>
+      <c r="B135" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C135" s="34">
+        <v>30</v>
+      </c>
+      <c r="D135" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E135" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F135" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G135" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H135" s="21" t="b">
+        <f>A135=C135</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="30"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="30"/>
-      <c r="D136" s="30"/>
-      <c r="E136" s="31"/>
-      <c r="F136" s="30"/>
-      <c r="G136" s="31"/>
+      <c r="A136" s="32">
+        <v>30</v>
+      </c>
+      <c r="B136" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C136" s="34">
+        <v>30</v>
+      </c>
+      <c r="D136" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E136" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F136" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G136" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H136" s="21" t="b">
+        <f>A136=C136</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="30"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="30"/>
-      <c r="D137" s="30"/>
-      <c r="E137" s="31"/>
-      <c r="F137" s="30"/>
-      <c r="G137" s="31"/>
+      <c r="A137" s="26">
+        <v>40</v>
+      </c>
+      <c r="B137" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C137" s="28">
+        <v>40</v>
+      </c>
+      <c r="D137" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E137" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F137" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="G137" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H137" s="21" t="b">
+        <f>A137=C137</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="30"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="30"/>
-      <c r="D138" s="30"/>
-      <c r="E138" s="31"/>
-      <c r="F138" s="30"/>
-      <c r="G138" s="31"/>
+      <c r="A138" s="26">
+        <v>40</v>
+      </c>
+      <c r="B138" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C138" s="28">
+        <v>40</v>
+      </c>
+      <c r="D138" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E138" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F138" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="G138" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H138" s="21" t="b">
+        <f>A138=C138</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="30"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="30"/>
-      <c r="E139" s="31"/>
-      <c r="F139" s="30"/>
-      <c r="G139" s="31"/>
+      <c r="A139" s="26">
+        <v>40</v>
+      </c>
+      <c r="B139" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C139" s="28">
+        <v>40</v>
+      </c>
+      <c r="D139" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E139" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="F139" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="G139" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H139" s="21" t="b">
+        <f>A139=C139</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="30"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="30"/>
-      <c r="D140" s="30"/>
-      <c r="E140" s="31"/>
-      <c r="F140" s="30"/>
-      <c r="G140" s="31"/>
+      <c r="A140" s="26">
+        <v>45</v>
+      </c>
+      <c r="B140" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C140" s="28">
+        <v>45</v>
+      </c>
+      <c r="D140" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E140" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F140" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="G140" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H140" s="21" t="b">
+        <f>A140=C140</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="30"/>
@@ -10652,10 +10787,10 @@
       <sortCondition ref="D2:D127"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H134">
-    <sortCondition ref="A2:A134"/>
-    <sortCondition ref="B2:B134"/>
-    <sortCondition ref="D2:D134"/>
+  <sortState ref="A2:H140">
+    <sortCondition ref="A2:A140"/>
+    <sortCondition ref="B2:B140"/>
+    <sortCondition ref="D2:D140"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
